--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340A7A47-225E-4B71-B5CA-459FE5A61885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E360E248-CFAA-40CB-92B2-5A03712201E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="78510" yWindow="735" windowWidth="17280" windowHeight="18765" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58260" yWindow="660" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P541"/>
+  <dimension ref="A1:P549"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="17" max="17" width="11.69140625" customWidth="1"/>
@@ -27535,19 +27535,418 @@
         <v>25</v>
       </c>
     </row>
+    <row r="542" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A542">
+        <v>3612</v>
+      </c>
+      <c r="B542">
+        <v>4</v>
+      </c>
+      <c r="C542">
+        <v>6</v>
+      </c>
+      <c r="D542">
+        <v>8</v>
+      </c>
+      <c r="E542">
+        <v>9</v>
+      </c>
+      <c r="F542">
+        <v>11</v>
+      </c>
+      <c r="G542">
+        <v>14</v>
+      </c>
+      <c r="H542">
+        <v>15</v>
+      </c>
+      <c r="I542">
+        <v>16</v>
+      </c>
+      <c r="J542">
+        <v>17</v>
+      </c>
+      <c r="K542">
+        <v>18</v>
+      </c>
+      <c r="L542">
+        <v>19</v>
+      </c>
+      <c r="M542">
+        <v>20</v>
+      </c>
+      <c r="N542">
+        <v>21</v>
+      </c>
+      <c r="O542">
+        <v>22</v>
+      </c>
+      <c r="P542">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="543" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A543">
+        <v>3613</v>
+      </c>
+      <c r="B543">
+        <v>1</v>
+      </c>
+      <c r="C543">
+        <v>3</v>
+      </c>
+      <c r="D543">
+        <v>4</v>
+      </c>
+      <c r="E543">
+        <v>7</v>
+      </c>
+      <c r="F543">
+        <v>9</v>
+      </c>
+      <c r="G543">
+        <v>10</v>
+      </c>
+      <c r="H543">
+        <v>11</v>
+      </c>
+      <c r="I543">
+        <v>12</v>
+      </c>
+      <c r="J543">
+        <v>15</v>
+      </c>
+      <c r="K543">
+        <v>16</v>
+      </c>
+      <c r="L543">
+        <v>18</v>
+      </c>
+      <c r="M543">
+        <v>20</v>
+      </c>
+      <c r="N543">
+        <v>21</v>
+      </c>
+      <c r="O543">
+        <v>22</v>
+      </c>
+      <c r="P543">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="544" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A544">
+        <v>3614</v>
+      </c>
+      <c r="B544">
+        <v>2</v>
+      </c>
+      <c r="C544">
+        <v>4</v>
+      </c>
+      <c r="D544">
+        <v>5</v>
+      </c>
+      <c r="E544">
+        <v>6</v>
+      </c>
+      <c r="F544">
+        <v>9</v>
+      </c>
+      <c r="G544">
+        <v>10</v>
+      </c>
+      <c r="H544">
+        <v>11</v>
+      </c>
+      <c r="I544">
+        <v>12</v>
+      </c>
+      <c r="J544">
+        <v>14</v>
+      </c>
+      <c r="K544">
+        <v>15</v>
+      </c>
+      <c r="L544">
+        <v>16</v>
+      </c>
+      <c r="M544">
+        <v>17</v>
+      </c>
+      <c r="N544">
+        <v>20</v>
+      </c>
+      <c r="O544">
+        <v>23</v>
+      </c>
+      <c r="P544">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="545" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A545">
+        <v>3615</v>
+      </c>
+      <c r="B545">
+        <v>2</v>
+      </c>
+      <c r="C545">
+        <v>3</v>
+      </c>
+      <c r="D545">
+        <v>6</v>
+      </c>
+      <c r="E545">
+        <v>7</v>
+      </c>
+      <c r="F545">
+        <v>8</v>
+      </c>
+      <c r="G545">
+        <v>9</v>
+      </c>
+      <c r="H545">
+        <v>10</v>
+      </c>
+      <c r="I545">
+        <v>11</v>
+      </c>
+      <c r="J545">
+        <v>14</v>
+      </c>
+      <c r="K545">
+        <v>15</v>
+      </c>
+      <c r="L545">
+        <v>17</v>
+      </c>
+      <c r="M545">
+        <v>18</v>
+      </c>
+      <c r="N545">
+        <v>21</v>
+      </c>
+      <c r="O545">
+        <v>23</v>
+      </c>
+      <c r="P545">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="546" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A546">
+        <v>3616</v>
+      </c>
+      <c r="B546">
+        <v>1</v>
+      </c>
+      <c r="C546">
+        <v>4</v>
+      </c>
+      <c r="D546">
+        <v>5</v>
+      </c>
+      <c r="E546">
+        <v>6</v>
+      </c>
+      <c r="F546">
+        <v>10</v>
+      </c>
+      <c r="G546">
+        <v>11</v>
+      </c>
+      <c r="H546">
+        <v>13</v>
+      </c>
+      <c r="I546">
+        <v>14</v>
+      </c>
+      <c r="J546">
+        <v>16</v>
+      </c>
+      <c r="K546">
+        <v>18</v>
+      </c>
+      <c r="L546">
+        <v>19</v>
+      </c>
+      <c r="M546">
+        <v>20</v>
+      </c>
+      <c r="N546">
+        <v>21</v>
+      </c>
+      <c r="O546">
+        <v>23</v>
+      </c>
+      <c r="P546">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="547" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A547">
+        <v>3617</v>
+      </c>
+      <c r="B547">
+        <v>2</v>
+      </c>
+      <c r="C547">
+        <v>4</v>
+      </c>
+      <c r="D547">
+        <v>7</v>
+      </c>
+      <c r="E547">
+        <v>8</v>
+      </c>
+      <c r="F547">
+        <v>10</v>
+      </c>
+      <c r="G547">
+        <v>11</v>
+      </c>
+      <c r="H547">
+        <v>12</v>
+      </c>
+      <c r="I547">
+        <v>13</v>
+      </c>
+      <c r="J547">
+        <v>16</v>
+      </c>
+      <c r="K547">
+        <v>19</v>
+      </c>
+      <c r="L547">
+        <v>20</v>
+      </c>
+      <c r="M547">
+        <v>21</v>
+      </c>
+      <c r="N547">
+        <v>22</v>
+      </c>
+      <c r="O547">
+        <v>23</v>
+      </c>
+      <c r="P547">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="548" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A548">
+        <v>3618</v>
+      </c>
+      <c r="B548">
+        <v>1</v>
+      </c>
+      <c r="C548">
+        <v>3</v>
+      </c>
+      <c r="D548">
+        <v>4</v>
+      </c>
+      <c r="E548">
+        <v>5</v>
+      </c>
+      <c r="F548">
+        <v>9</v>
+      </c>
+      <c r="G548">
+        <v>10</v>
+      </c>
+      <c r="H548">
+        <v>11</v>
+      </c>
+      <c r="I548">
+        <v>12</v>
+      </c>
+      <c r="J548">
+        <v>14</v>
+      </c>
+      <c r="K548">
+        <v>15</v>
+      </c>
+      <c r="L548">
+        <v>20</v>
+      </c>
+      <c r="M548">
+        <v>21</v>
+      </c>
+      <c r="N548">
+        <v>22</v>
+      </c>
+      <c r="O548">
+        <v>23</v>
+      </c>
+      <c r="P548">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="549" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A549">
+        <v>3619</v>
+      </c>
+      <c r="B549">
+        <v>1</v>
+      </c>
+      <c r="C549">
+        <v>2</v>
+      </c>
+      <c r="D549">
+        <v>7</v>
+      </c>
+      <c r="E549">
+        <v>8</v>
+      </c>
+      <c r="F549">
+        <v>10</v>
+      </c>
+      <c r="G549">
+        <v>11</v>
+      </c>
+      <c r="H549">
+        <v>13</v>
+      </c>
+      <c r="I549">
+        <v>14</v>
+      </c>
+      <c r="J549">
+        <v>16</v>
+      </c>
+      <c r="K549">
+        <v>18</v>
+      </c>
+      <c r="L549">
+        <v>19</v>
+      </c>
+      <c r="M549">
+        <v>20</v>
+      </c>
+      <c r="N549">
+        <v>23</v>
+      </c>
+      <c r="O549">
+        <v>24</v>
+      </c>
+      <c r="P549">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27719,21 +28118,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27759,9 +28156,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E360E248-CFAA-40CB-92B2-5A03712201E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D498C76-72EC-4110-B264-5DA0FD04AD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58260" yWindow="660" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57795" yWindow="195" windowWidth="22140" windowHeight="17235" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,6 +156,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,16 +478,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P549"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P583"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="17" max="17" width="11.69140625" customWidth="1"/>
-    <col min="18" max="18" width="12.69140625" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" customWidth="1"/>
+    <col min="18" max="18" width="12.6640625" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="16.07421875" customWidth="1"/>
+    <col min="20" max="20" width="16.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -535,7 +537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>3072</v>
       </c>
@@ -585,7 +587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>3073</v>
       </c>
@@ -635,7 +637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3074</v>
       </c>
@@ -685,7 +687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>3075</v>
       </c>
@@ -735,7 +737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>3076</v>
       </c>
@@ -785,7 +787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>3077</v>
       </c>
@@ -835,7 +837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>3078</v>
       </c>
@@ -885,7 +887,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>3079</v>
       </c>
@@ -935,7 +937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>3080</v>
       </c>
@@ -985,7 +987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>3081</v>
       </c>
@@ -1035,7 +1037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>3082</v>
       </c>
@@ -1085,7 +1087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>3083</v>
       </c>
@@ -1135,7 +1137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>3084</v>
       </c>
@@ -1185,7 +1187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>3085</v>
       </c>
@@ -1235,7 +1237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>3086</v>
       </c>
@@ -1285,7 +1287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>3087</v>
       </c>
@@ -1335,7 +1337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>3088</v>
       </c>
@@ -1385,7 +1387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>3089</v>
       </c>
@@ -1435,7 +1437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>3090</v>
       </c>
@@ -1485,7 +1487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>3091</v>
       </c>
@@ -1535,7 +1537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>3092</v>
       </c>
@@ -1585,7 +1587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>3093</v>
       </c>
@@ -1635,7 +1637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>3094</v>
       </c>
@@ -1685,7 +1687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>3095</v>
       </c>
@@ -1735,7 +1737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>3096</v>
       </c>
@@ -1785,7 +1787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>3097</v>
       </c>
@@ -1835,7 +1837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>3098</v>
       </c>
@@ -1885,7 +1887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>3099</v>
       </c>
@@ -1935,7 +1937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>3100</v>
       </c>
@@ -1985,7 +1987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>3101</v>
       </c>
@@ -2035,7 +2037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>3102</v>
       </c>
@@ -2085,7 +2087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>3103</v>
       </c>
@@ -2135,7 +2137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>3104</v>
       </c>
@@ -2185,7 +2187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>3105</v>
       </c>
@@ -2235,7 +2237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>3106</v>
       </c>
@@ -2285,7 +2287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>3107</v>
       </c>
@@ -2335,7 +2337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>3108</v>
       </c>
@@ -2385,7 +2387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>3109</v>
       </c>
@@ -2435,7 +2437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>3110</v>
       </c>
@@ -2485,7 +2487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>3111</v>
       </c>
@@ -2535,7 +2537,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>3112</v>
       </c>
@@ -2585,7 +2587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>3113</v>
       </c>
@@ -2635,7 +2637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>3114</v>
       </c>
@@ -2685,7 +2687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>3115</v>
       </c>
@@ -2735,7 +2737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>3116</v>
       </c>
@@ -2785,7 +2787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>3117</v>
       </c>
@@ -2835,7 +2837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>3118</v>
       </c>
@@ -2885,7 +2887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>3119</v>
       </c>
@@ -2935,7 +2937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>3120</v>
       </c>
@@ -2985,7 +2987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>3121</v>
       </c>
@@ -3035,7 +3037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>3122</v>
       </c>
@@ -3085,7 +3087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>3123</v>
       </c>
@@ -3135,7 +3137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>3124</v>
       </c>
@@ -3185,7 +3187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>3125</v>
       </c>
@@ -3235,7 +3237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>3126</v>
       </c>
@@ -3285,7 +3287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>3127</v>
       </c>
@@ -3335,7 +3337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>3128</v>
       </c>
@@ -3385,7 +3387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>3129</v>
       </c>
@@ -3435,7 +3437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>3130</v>
       </c>
@@ -3485,7 +3487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>3131</v>
       </c>
@@ -3535,7 +3537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>3132</v>
       </c>
@@ -3585,7 +3587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>3133</v>
       </c>
@@ -3635,7 +3637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>3134</v>
       </c>
@@ -3685,7 +3687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>3135</v>
       </c>
@@ -3735,7 +3737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>3136</v>
       </c>
@@ -3785,7 +3787,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>3137</v>
       </c>
@@ -3835,7 +3837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>3138</v>
       </c>
@@ -3885,7 +3887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>3139</v>
       </c>
@@ -3935,7 +3937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>3140</v>
       </c>
@@ -3985,7 +3987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>3141</v>
       </c>
@@ -4035,7 +4037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>3142</v>
       </c>
@@ -4085,7 +4087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>3143</v>
       </c>
@@ -4135,7 +4137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>3144</v>
       </c>
@@ -4185,7 +4187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>3145</v>
       </c>
@@ -4235,7 +4237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>3146</v>
       </c>
@@ -4285,7 +4287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>3147</v>
       </c>
@@ -4335,7 +4337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>3148</v>
       </c>
@@ -4385,7 +4387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>3149</v>
       </c>
@@ -4435,7 +4437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>3150</v>
       </c>
@@ -4485,7 +4487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>3151</v>
       </c>
@@ -4535,7 +4537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>3152</v>
       </c>
@@ -4585,7 +4587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>3153</v>
       </c>
@@ -4635,7 +4637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>3154</v>
       </c>
@@ -4685,7 +4687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>3155</v>
       </c>
@@ -4735,7 +4737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>3156</v>
       </c>
@@ -4785,7 +4787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>3157</v>
       </c>
@@ -4835,7 +4837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>3158</v>
       </c>
@@ -4885,7 +4887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>3159</v>
       </c>
@@ -4935,7 +4937,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>3160</v>
       </c>
@@ -4985,7 +4987,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>3161</v>
       </c>
@@ -5035,7 +5037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>3162</v>
       </c>
@@ -5085,7 +5087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>3163</v>
       </c>
@@ -5135,7 +5137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>3164</v>
       </c>
@@ -5185,7 +5187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>3165</v>
       </c>
@@ -5235,7 +5237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>3166</v>
       </c>
@@ -5285,7 +5287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>3167</v>
       </c>
@@ -5335,7 +5337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>3168</v>
       </c>
@@ -5385,7 +5387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>3169</v>
       </c>
@@ -5435,7 +5437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>3170</v>
       </c>
@@ -5485,7 +5487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>3171</v>
       </c>
@@ -5535,7 +5537,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>3172</v>
       </c>
@@ -5585,7 +5587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>3173</v>
       </c>
@@ -5635,7 +5637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>3174</v>
       </c>
@@ -5685,7 +5687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>3175</v>
       </c>
@@ -5735,7 +5737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>3176</v>
       </c>
@@ -5785,7 +5787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>3177</v>
       </c>
@@ -5835,7 +5837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>3178</v>
       </c>
@@ -5885,7 +5887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>3179</v>
       </c>
@@ -5935,7 +5937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>3180</v>
       </c>
@@ -5985,7 +5987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>3181</v>
       </c>
@@ -6035,7 +6037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>3182</v>
       </c>
@@ -6085,7 +6087,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>3183</v>
       </c>
@@ -6135,7 +6137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>3184</v>
       </c>
@@ -6185,7 +6187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>3185</v>
       </c>
@@ -6235,7 +6237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>3186</v>
       </c>
@@ -6285,7 +6287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>3187</v>
       </c>
@@ -6335,7 +6337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>3188</v>
       </c>
@@ -6385,7 +6387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>3189</v>
       </c>
@@ -6435,7 +6437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>3190</v>
       </c>
@@ -6485,7 +6487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>3191</v>
       </c>
@@ -6535,7 +6537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>3192</v>
       </c>
@@ -6585,7 +6587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>3193</v>
       </c>
@@ -6635,7 +6637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>3194</v>
       </c>
@@ -6685,7 +6687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>3195</v>
       </c>
@@ -6735,7 +6737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>3196</v>
       </c>
@@ -6785,7 +6787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>3197</v>
       </c>
@@ -6835,7 +6837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>3198</v>
       </c>
@@ -6885,7 +6887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>3199</v>
       </c>
@@ -6935,7 +6937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>3200</v>
       </c>
@@ -6985,7 +6987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>3201</v>
       </c>
@@ -7035,7 +7037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>3202</v>
       </c>
@@ -7085,7 +7087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>3203</v>
       </c>
@@ -7135,7 +7137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>3204</v>
       </c>
@@ -7185,7 +7187,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>3205</v>
       </c>
@@ -7235,7 +7237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>3206</v>
       </c>
@@ -7285,7 +7287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>3207</v>
       </c>
@@ -7335,7 +7337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>3208</v>
       </c>
@@ -7385,7 +7387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>3209</v>
       </c>
@@ -7435,7 +7437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>3210</v>
       </c>
@@ -7485,7 +7487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>3211</v>
       </c>
@@ -7535,7 +7537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>3212</v>
       </c>
@@ -7585,7 +7587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>3213</v>
       </c>
@@ -7635,7 +7637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>3214</v>
       </c>
@@ -7685,7 +7687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>3215</v>
       </c>
@@ -7735,7 +7737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>3216</v>
       </c>
@@ -7785,7 +7787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>3217</v>
       </c>
@@ -7835,7 +7837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>3218</v>
       </c>
@@ -7885,7 +7887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>3219</v>
       </c>
@@ -7935,7 +7937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>3220</v>
       </c>
@@ -7985,7 +7987,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>3221</v>
       </c>
@@ -8035,7 +8037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>3222</v>
       </c>
@@ -8085,7 +8087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>3223</v>
       </c>
@@ -8135,7 +8137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>3224</v>
       </c>
@@ -8185,7 +8187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>3225</v>
       </c>
@@ -8235,7 +8237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>3226</v>
       </c>
@@ -8285,7 +8287,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>3227</v>
       </c>
@@ -8335,7 +8337,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>3228</v>
       </c>
@@ -8385,7 +8387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>3229</v>
       </c>
@@ -8435,7 +8437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>3230</v>
       </c>
@@ -8485,7 +8487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>3231</v>
       </c>
@@ -8535,7 +8537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>3232</v>
       </c>
@@ -8585,7 +8587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>3233</v>
       </c>
@@ -8635,7 +8637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>3234</v>
       </c>
@@ -8685,7 +8687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>3235</v>
       </c>
@@ -8735,7 +8737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>3236</v>
       </c>
@@ -8785,7 +8787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>3237</v>
       </c>
@@ -8835,7 +8837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>3238</v>
       </c>
@@ -8885,7 +8887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>3239</v>
       </c>
@@ -8935,7 +8937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>3240</v>
       </c>
@@ -8985,7 +8987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>3241</v>
       </c>
@@ -9035,7 +9037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>3242</v>
       </c>
@@ -9085,7 +9087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>3243</v>
       </c>
@@ -9135,7 +9137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>3244</v>
       </c>
@@ -9185,7 +9187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>3245</v>
       </c>
@@ -9235,7 +9237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>3246</v>
       </c>
@@ -9285,7 +9287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>3247</v>
       </c>
@@ -9335,7 +9337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>3248</v>
       </c>
@@ -9385,7 +9387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>3249</v>
       </c>
@@ -9435,7 +9437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>3250</v>
       </c>
@@ -9485,7 +9487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>3251</v>
       </c>
@@ -9535,7 +9537,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>3252</v>
       </c>
@@ -9585,7 +9587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>3253</v>
       </c>
@@ -9635,7 +9637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>3254</v>
       </c>
@@ -9685,7 +9687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>3255</v>
       </c>
@@ -9735,7 +9737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>3256</v>
       </c>
@@ -9785,7 +9787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>3257</v>
       </c>
@@ -9835,7 +9837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>3258</v>
       </c>
@@ -9885,7 +9887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>3259</v>
       </c>
@@ -9935,7 +9937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>3260</v>
       </c>
@@ -9985,7 +9987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>3261</v>
       </c>
@@ -10035,7 +10037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>3262</v>
       </c>
@@ -10085,7 +10087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>3263</v>
       </c>
@@ -10135,7 +10137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>3264</v>
       </c>
@@ -10185,7 +10187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>3265</v>
       </c>
@@ -10235,7 +10237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>3266</v>
       </c>
@@ -10285,7 +10287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>3267</v>
       </c>
@@ -10335,7 +10337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>3268</v>
       </c>
@@ -10385,7 +10387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>3269</v>
       </c>
@@ -10435,7 +10437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>3270</v>
       </c>
@@ -10485,7 +10487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>3271</v>
       </c>
@@ -10535,7 +10537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>3272</v>
       </c>
@@ -10585,7 +10587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>3273</v>
       </c>
@@ -10635,7 +10637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>3274</v>
       </c>
@@ -10685,7 +10687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>3275</v>
       </c>
@@ -10735,7 +10737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>3276</v>
       </c>
@@ -10785,7 +10787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>3277</v>
       </c>
@@ -10835,7 +10837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>3278</v>
       </c>
@@ -10885,7 +10887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>3279</v>
       </c>
@@ -10935,7 +10937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>3280</v>
       </c>
@@ -10985,7 +10987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>3281</v>
       </c>
@@ -11035,7 +11037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>3282</v>
       </c>
@@ -11085,7 +11087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>3283</v>
       </c>
@@ -11135,7 +11137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>3284</v>
       </c>
@@ -11185,7 +11187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>3285</v>
       </c>
@@ -11235,7 +11237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>3286</v>
       </c>
@@ -11285,7 +11287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>3287</v>
       </c>
@@ -11335,7 +11337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>3288</v>
       </c>
@@ -11385,7 +11387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>3289</v>
       </c>
@@ -11435,7 +11437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>3290</v>
       </c>
@@ -11485,7 +11487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>3291</v>
       </c>
@@ -11535,7 +11537,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>3292</v>
       </c>
@@ -11585,7 +11587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>3293</v>
       </c>
@@ -11635,7 +11637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>3294</v>
       </c>
@@ -11685,7 +11687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>3295</v>
       </c>
@@ -11735,7 +11737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>3296</v>
       </c>
@@ -11785,7 +11787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>3297</v>
       </c>
@@ -11835,7 +11837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>3298</v>
       </c>
@@ -11885,7 +11887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>3299</v>
       </c>
@@ -11935,7 +11937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>3300</v>
       </c>
@@ -11985,7 +11987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>3301</v>
       </c>
@@ -12035,7 +12037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>3302</v>
       </c>
@@ -12085,7 +12087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>3303</v>
       </c>
@@ -12135,7 +12137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>3304</v>
       </c>
@@ -12185,7 +12187,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>3305</v>
       </c>
@@ -12235,7 +12237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>3306</v>
       </c>
@@ -12285,7 +12287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>3307</v>
       </c>
@@ -12335,7 +12337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>3308</v>
       </c>
@@ -12385,7 +12387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>3309</v>
       </c>
@@ -12435,7 +12437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>3310</v>
       </c>
@@ -12485,7 +12487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>3311</v>
       </c>
@@ -12535,7 +12537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>3312</v>
       </c>
@@ -12585,7 +12587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>3313</v>
       </c>
@@ -12635,7 +12637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>3314</v>
       </c>
@@ -12685,7 +12687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>3315</v>
       </c>
@@ -12735,7 +12737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>3316</v>
       </c>
@@ -12785,7 +12787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>3317</v>
       </c>
@@ -12835,7 +12837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>3318</v>
       </c>
@@ -12885,7 +12887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>3319</v>
       </c>
@@ -12935,7 +12937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>3320</v>
       </c>
@@ -12985,7 +12987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>3321</v>
       </c>
@@ -13035,7 +13037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>3322</v>
       </c>
@@ -13085,7 +13087,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>3323</v>
       </c>
@@ -13135,7 +13137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>3324</v>
       </c>
@@ -13185,7 +13187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>3325</v>
       </c>
@@ -13235,7 +13237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>3326</v>
       </c>
@@ -13285,7 +13287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>3327</v>
       </c>
@@ -13335,7 +13337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>3328</v>
       </c>
@@ -13385,7 +13387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>3329</v>
       </c>
@@ -13435,7 +13437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>3330</v>
       </c>
@@ -13485,7 +13487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>3331</v>
       </c>
@@ -13535,7 +13537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>3332</v>
       </c>
@@ -13585,7 +13587,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>3333</v>
       </c>
@@ -13635,7 +13637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>3334</v>
       </c>
@@ -13685,7 +13687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>3335</v>
       </c>
@@ -13735,7 +13737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>3336</v>
       </c>
@@ -13785,7 +13787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>3337</v>
       </c>
@@ -13835,7 +13837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>3338</v>
       </c>
@@ -13885,7 +13887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>3339</v>
       </c>
@@ -13935,7 +13937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>3340</v>
       </c>
@@ -13985,7 +13987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>3341</v>
       </c>
@@ -14035,7 +14037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>3342</v>
       </c>
@@ -14085,7 +14087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>3343</v>
       </c>
@@ -14135,7 +14137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>3344</v>
       </c>
@@ -14185,7 +14187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>3345</v>
       </c>
@@ -14235,7 +14237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>3346</v>
       </c>
@@ -14285,7 +14287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>3347</v>
       </c>
@@ -14335,7 +14337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>3348</v>
       </c>
@@ -14385,7 +14387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>3349</v>
       </c>
@@ -14435,7 +14437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>3350</v>
       </c>
@@ -14485,7 +14487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>3351</v>
       </c>
@@ -14535,7 +14537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>3352</v>
       </c>
@@ -14585,7 +14587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>3353</v>
       </c>
@@ -14635,7 +14637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>3354</v>
       </c>
@@ -14685,7 +14687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>3355</v>
       </c>
@@ -14735,7 +14737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>3356</v>
       </c>
@@ -14785,7 +14787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>3357</v>
       </c>
@@ -14835,7 +14837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>3358</v>
       </c>
@@ -14885,7 +14887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>3359</v>
       </c>
@@ -14935,7 +14937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>3360</v>
       </c>
@@ -14985,7 +14987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>3361</v>
       </c>
@@ -15035,7 +15037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>3362</v>
       </c>
@@ -15085,7 +15087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>3363</v>
       </c>
@@ -15135,7 +15137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>3364</v>
       </c>
@@ -15185,7 +15187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>3365</v>
       </c>
@@ -15235,7 +15237,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>3366</v>
       </c>
@@ -15285,7 +15287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>3367</v>
       </c>
@@ -15335,7 +15337,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>3368</v>
       </c>
@@ -15385,7 +15387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>3369</v>
       </c>
@@ -15435,7 +15437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>3370</v>
       </c>
@@ -15485,7 +15487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>3371</v>
       </c>
@@ -15535,7 +15537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>3372</v>
       </c>
@@ -15585,7 +15587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>3373</v>
       </c>
@@ -15635,7 +15637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>3374</v>
       </c>
@@ -15685,7 +15687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>3375</v>
       </c>
@@ -15735,7 +15737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>3376</v>
       </c>
@@ -15785,7 +15787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>3377</v>
       </c>
@@ -15835,7 +15837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>3378</v>
       </c>
@@ -15885,7 +15887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>3379</v>
       </c>
@@ -15935,7 +15937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>3380</v>
       </c>
@@ -15985,7 +15987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>3381</v>
       </c>
@@ -16035,7 +16037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>3382</v>
       </c>
@@ -16085,7 +16087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>3383</v>
       </c>
@@ -16135,7 +16137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>3384</v>
       </c>
@@ -16185,7 +16187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>3385</v>
       </c>
@@ -16235,7 +16237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>3386</v>
       </c>
@@ -16285,7 +16287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>3387</v>
       </c>
@@ -16335,7 +16337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>3388</v>
       </c>
@@ -16385,7 +16387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>3389</v>
       </c>
@@ -16435,7 +16437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>3390</v>
       </c>
@@ -16485,7 +16487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>3391</v>
       </c>
@@ -16535,7 +16537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>3392</v>
       </c>
@@ -16585,7 +16587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>3393</v>
       </c>
@@ -16635,7 +16637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>3394</v>
       </c>
@@ -16685,7 +16687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>3395</v>
       </c>
@@ -16735,7 +16737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>3396</v>
       </c>
@@ -16785,7 +16787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>3397</v>
       </c>
@@ -16835,7 +16837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>3398</v>
       </c>
@@ -16885,7 +16887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>3399</v>
       </c>
@@ -16935,7 +16937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>3400</v>
       </c>
@@ -16985,7 +16987,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>3401</v>
       </c>
@@ -17035,7 +17037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>3402</v>
       </c>
@@ -17085,7 +17087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>3403</v>
       </c>
@@ -17135,7 +17137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>3404</v>
       </c>
@@ -17185,7 +17187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>3405</v>
       </c>
@@ -17235,7 +17237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>3406</v>
       </c>
@@ -17285,7 +17287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>3407</v>
       </c>
@@ -17335,7 +17337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>3408</v>
       </c>
@@ -17385,7 +17387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>3409</v>
       </c>
@@ -17435,7 +17437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>3410</v>
       </c>
@@ -17485,7 +17487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>3411</v>
       </c>
@@ -17535,7 +17537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>3412</v>
       </c>
@@ -17585,7 +17587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>3413</v>
       </c>
@@ -17635,7 +17637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>3414</v>
       </c>
@@ -17685,7 +17687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>3415</v>
       </c>
@@ -17735,7 +17737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>3416</v>
       </c>
@@ -17785,7 +17787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>3417</v>
       </c>
@@ -17835,7 +17837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>3418</v>
       </c>
@@ -17885,7 +17887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>3419</v>
       </c>
@@ -17935,7 +17937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>3420</v>
       </c>
@@ -17985,7 +17987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>3421</v>
       </c>
@@ -18035,7 +18037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>3422</v>
       </c>
@@ -18085,7 +18087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>3423</v>
       </c>
@@ -18135,7 +18137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>3424</v>
       </c>
@@ -18185,7 +18187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>3425</v>
       </c>
@@ -18235,7 +18237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>3426</v>
       </c>
@@ -18285,7 +18287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>3427</v>
       </c>
@@ -18335,7 +18337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>3428</v>
       </c>
@@ -18385,7 +18387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>3429</v>
       </c>
@@ -18435,7 +18437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>3430</v>
       </c>
@@ -18485,7 +18487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>3431</v>
       </c>
@@ -18535,7 +18537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>3432</v>
       </c>
@@ -18585,7 +18587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>3433</v>
       </c>
@@ -18635,7 +18637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>3434</v>
       </c>
@@ -18685,7 +18687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>3435</v>
       </c>
@@ -18735,7 +18737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>3436</v>
       </c>
@@ -18785,7 +18787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>3437</v>
       </c>
@@ -18835,7 +18837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>3438</v>
       </c>
@@ -18885,7 +18887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>3439</v>
       </c>
@@ -18935,7 +18937,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>3440</v>
       </c>
@@ -18985,7 +18987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>3441</v>
       </c>
@@ -19035,7 +19037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>3442</v>
       </c>
@@ -19085,7 +19087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>3443</v>
       </c>
@@ -19135,7 +19137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>3444</v>
       </c>
@@ -19185,7 +19187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>3445</v>
       </c>
@@ -19235,7 +19237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>3446</v>
       </c>
@@ -19285,7 +19287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>3447</v>
       </c>
@@ -19335,7 +19337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>3448</v>
       </c>
@@ -19385,7 +19387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>3449</v>
       </c>
@@ -19435,7 +19437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>3450</v>
       </c>
@@ -19485,7 +19487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>3451</v>
       </c>
@@ -19535,7 +19537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>3452</v>
       </c>
@@ -19585,7 +19587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>3453</v>
       </c>
@@ -19635,7 +19637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>3454</v>
       </c>
@@ -19685,7 +19687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>3455</v>
       </c>
@@ -19735,7 +19737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>3456</v>
       </c>
@@ -19785,7 +19787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>3457</v>
       </c>
@@ -19835,7 +19837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>3458</v>
       </c>
@@ -19885,7 +19887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>3459</v>
       </c>
@@ -19935,7 +19937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>3460</v>
       </c>
@@ -19985,7 +19987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>3461</v>
       </c>
@@ -20035,7 +20037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>3462</v>
       </c>
@@ -20085,7 +20087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>3463</v>
       </c>
@@ -20135,7 +20137,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>3464</v>
       </c>
@@ -20185,7 +20187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>3465</v>
       </c>
@@ -20235,7 +20237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>3466</v>
       </c>
@@ -20285,7 +20287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>3467</v>
       </c>
@@ -20335,7 +20337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>3468</v>
       </c>
@@ -20385,7 +20387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>3469</v>
       </c>
@@ -20435,7 +20437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="400" spans="1:16" ht="15.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:16" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A400">
         <v>3470</v>
       </c>
@@ -20485,7 +20487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A401">
         <v>3471</v>
       </c>
@@ -20535,7 +20537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A402">
         <v>3472</v>
       </c>
@@ -20585,7 +20587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A403">
         <v>3473</v>
       </c>
@@ -20635,7 +20637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A404">
         <v>3474</v>
       </c>
@@ -20685,7 +20687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A405">
         <v>3475</v>
       </c>
@@ -20735,7 +20737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A406">
         <v>3476</v>
       </c>
@@ -20785,7 +20787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A407">
         <v>3477</v>
       </c>
@@ -20835,7 +20837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A408">
         <v>3478</v>
       </c>
@@ -20885,7 +20887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A409">
         <v>3479</v>
       </c>
@@ -20935,7 +20937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A410">
         <v>3480</v>
       </c>
@@ -20985,7 +20987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A411">
         <v>3481</v>
       </c>
@@ -21035,7 +21037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A412">
         <v>3482</v>
       </c>
@@ -21085,7 +21087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A413">
         <v>3483</v>
       </c>
@@ -21135,7 +21137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A414">
         <v>3484</v>
       </c>
@@ -21185,7 +21187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A415">
         <v>3485</v>
       </c>
@@ -21235,7 +21237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A416">
         <v>3486</v>
       </c>
@@ -21285,7 +21287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A417">
         <v>3487</v>
       </c>
@@ -21335,7 +21337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A418">
         <v>3488</v>
       </c>
@@ -21385,7 +21387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A419">
         <v>3489</v>
       </c>
@@ -21435,7 +21437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A420">
         <v>3490</v>
       </c>
@@ -21485,7 +21487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A421">
         <v>3491</v>
       </c>
@@ -21535,7 +21537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A422">
         <v>3492</v>
       </c>
@@ -21585,7 +21587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A423">
         <v>3493</v>
       </c>
@@ -21635,7 +21637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A424">
         <v>3494</v>
       </c>
@@ -21685,7 +21687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A425">
         <v>3495</v>
       </c>
@@ -21735,7 +21737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A426">
         <v>3496</v>
       </c>
@@ -21785,7 +21787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A427">
         <v>3497</v>
       </c>
@@ -21835,7 +21837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A428">
         <v>3498</v>
       </c>
@@ -21885,7 +21887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A429">
         <v>3499</v>
       </c>
@@ -21935,7 +21937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A430">
         <v>3500</v>
       </c>
@@ -21985,7 +21987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A431">
         <v>3501</v>
       </c>
@@ -22035,7 +22037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A432">
         <v>3502</v>
       </c>
@@ -22085,7 +22087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A433">
         <v>3503</v>
       </c>
@@ -22135,7 +22137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A434">
         <v>3504</v>
       </c>
@@ -22185,7 +22187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A435">
         <v>3505</v>
       </c>
@@ -22235,7 +22237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A436">
         <v>3506</v>
       </c>
@@ -22285,7 +22287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A437">
         <v>3507</v>
       </c>
@@ -22335,7 +22337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A438">
         <v>3508</v>
       </c>
@@ -22385,7 +22387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A439">
         <v>3509</v>
       </c>
@@ -22435,7 +22437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A440">
         <v>3510</v>
       </c>
@@ -22485,7 +22487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A441">
         <v>3511</v>
       </c>
@@ -22535,7 +22537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A442">
         <v>3512</v>
       </c>
@@ -22585,7 +22587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A443">
         <v>3513</v>
       </c>
@@ -22635,7 +22637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A444">
         <v>3514</v>
       </c>
@@ -22685,7 +22687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A445">
         <v>3515</v>
       </c>
@@ -22735,7 +22737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A446">
         <v>3516</v>
       </c>
@@ -22785,7 +22787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A447">
         <v>3517</v>
       </c>
@@ -22835,7 +22837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A448">
         <v>3518</v>
       </c>
@@ -22885,7 +22887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="449" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A449">
         <v>3519</v>
       </c>
@@ -22935,7 +22937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A450">
         <v>3520</v>
       </c>
@@ -22985,7 +22987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A451">
         <v>3521</v>
       </c>
@@ -23035,7 +23037,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="452" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A452">
         <v>3522</v>
       </c>
@@ -23085,7 +23087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="453" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A453">
         <v>3523</v>
       </c>
@@ -23135,7 +23137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A454">
         <v>3524</v>
       </c>
@@ -23185,7 +23187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A455">
         <v>3525</v>
       </c>
@@ -23235,7 +23237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="456" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A456">
         <v>3526</v>
       </c>
@@ -23285,7 +23287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A457">
         <v>3527</v>
       </c>
@@ -23335,7 +23337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A458">
         <v>3528</v>
       </c>
@@ -23385,7 +23387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A459">
         <v>3529</v>
       </c>
@@ -23435,7 +23437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A460">
         <v>3530</v>
       </c>
@@ -23485,7 +23487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A461">
         <v>3531</v>
       </c>
@@ -23535,7 +23537,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A462">
         <v>3532</v>
       </c>
@@ -23585,7 +23587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="463" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A463">
         <v>3533</v>
       </c>
@@ -23635,7 +23637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="464" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A464">
         <v>3534</v>
       </c>
@@ -23685,7 +23687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="465" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A465">
         <v>3535</v>
       </c>
@@ -23735,7 +23737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="466" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A466">
         <v>3536</v>
       </c>
@@ -23785,7 +23787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A467">
         <v>3537</v>
       </c>
@@ -23835,7 +23837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="468" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A468">
         <v>3538</v>
       </c>
@@ -23885,7 +23887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="469" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A469">
         <v>3539</v>
       </c>
@@ -23935,7 +23937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="470" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A470">
         <v>3540</v>
       </c>
@@ -23985,7 +23987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="471" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A471">
         <v>3541</v>
       </c>
@@ -24035,7 +24037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="472" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A472">
         <v>3542</v>
       </c>
@@ -24085,7 +24087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="473" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A473">
         <v>3543</v>
       </c>
@@ -24135,7 +24137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A474">
         <v>3544</v>
       </c>
@@ -24185,7 +24187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="475" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A475">
         <v>3545</v>
       </c>
@@ -24235,7 +24237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A476">
         <v>3546</v>
       </c>
@@ -24285,7 +24287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="477" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A477">
         <v>3547</v>
       </c>
@@ -24335,7 +24337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="478" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A478">
         <v>3548</v>
       </c>
@@ -24385,7 +24387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="479" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A479">
         <v>3549</v>
       </c>
@@ -24435,7 +24437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A480">
         <v>3550</v>
       </c>
@@ -24485,7 +24487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="481" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A481">
         <v>3551</v>
       </c>
@@ -24535,7 +24537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="482" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A482">
         <v>3552</v>
       </c>
@@ -24585,7 +24587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="483" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A483">
         <v>3553</v>
       </c>
@@ -24635,7 +24637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="484" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A484">
         <v>3554</v>
       </c>
@@ -24685,7 +24687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="485" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A485">
         <v>3555</v>
       </c>
@@ -24735,7 +24737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A486">
         <v>3556</v>
       </c>
@@ -24785,7 +24787,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A487">
         <v>3557</v>
       </c>
@@ -24835,7 +24837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A488">
         <v>3558</v>
       </c>
@@ -24885,7 +24887,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A489">
         <v>3559</v>
       </c>
@@ -24935,7 +24937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A490">
         <v>3560</v>
       </c>
@@ -24985,7 +24987,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A491">
         <v>3561</v>
       </c>
@@ -25035,7 +25037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="492" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A492">
         <v>3562</v>
       </c>
@@ -25085,7 +25087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="493" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A493">
         <v>3563</v>
       </c>
@@ -25135,7 +25137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="494" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A494">
         <v>3564</v>
       </c>
@@ -25185,7 +25187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A495">
         <v>3565</v>
       </c>
@@ -25235,7 +25237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A496">
         <v>3566</v>
       </c>
@@ -25285,7 +25287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="497" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A497">
         <v>3567</v>
       </c>
@@ -25335,7 +25337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A498">
         <v>3568</v>
       </c>
@@ -25385,7 +25387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A499">
         <v>3569</v>
       </c>
@@ -25435,7 +25437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A500">
         <v>3570</v>
       </c>
@@ -25485,7 +25487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A501">
         <v>3571</v>
       </c>
@@ -25535,7 +25537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A502">
         <v>3572</v>
       </c>
@@ -25585,7 +25587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A503">
         <v>3573</v>
       </c>
@@ -25635,7 +25637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A504">
         <v>3574</v>
       </c>
@@ -25685,7 +25687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A505">
         <v>3575</v>
       </c>
@@ -25735,7 +25737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A506">
         <v>3576</v>
       </c>
@@ -25785,7 +25787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="507" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A507">
         <v>3577</v>
       </c>
@@ -25835,7 +25837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="508" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A508">
         <v>3578</v>
       </c>
@@ -25885,7 +25887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="509" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A509">
         <v>3579</v>
       </c>
@@ -25935,7 +25937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A510">
         <v>3580</v>
       </c>
@@ -25985,7 +25987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A511">
         <v>3581</v>
       </c>
@@ -26035,7 +26037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A512">
         <v>3582</v>
       </c>
@@ -26085,7 +26087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A513">
         <v>3583</v>
       </c>
@@ -26135,7 +26137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A514">
         <v>3584</v>
       </c>
@@ -26185,7 +26187,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="515" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A515">
         <v>3585</v>
       </c>
@@ -26235,7 +26237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="516" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A516">
         <v>3586</v>
       </c>
@@ -26285,7 +26287,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="517" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A517">
         <v>3587</v>
       </c>
@@ -26335,7 +26337,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A518">
         <v>3588</v>
       </c>
@@ -26385,7 +26387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A519">
         <v>3589</v>
       </c>
@@ -26435,7 +26437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A520">
         <v>3590</v>
       </c>
@@ -26485,7 +26487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A521">
         <v>3591</v>
       </c>
@@ -26535,7 +26537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="522" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A522">
         <v>3592</v>
       </c>
@@ -26585,7 +26587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A523">
         <v>3593</v>
       </c>
@@ -26635,7 +26637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A524">
         <v>3594</v>
       </c>
@@ -26685,7 +26687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A525">
         <v>3595</v>
       </c>
@@ -26735,7 +26737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A526">
         <v>3596</v>
       </c>
@@ -26785,7 +26787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A527">
         <v>3597</v>
       </c>
@@ -26835,7 +26837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A528">
         <v>3598</v>
       </c>
@@ -26885,7 +26887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A529">
         <v>3599</v>
       </c>
@@ -26935,7 +26937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A530">
         <v>3600</v>
       </c>
@@ -26985,7 +26987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="531" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A531">
         <v>3601</v>
       </c>
@@ -27035,7 +27037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A532">
         <v>3602</v>
       </c>
@@ -27085,7 +27087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="533" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A533">
         <v>3603</v>
       </c>
@@ -27135,7 +27137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A534">
         <v>3604</v>
       </c>
@@ -27185,7 +27187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A535">
         <v>3605</v>
       </c>
@@ -27235,7 +27237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A536">
         <v>3606</v>
       </c>
@@ -27285,7 +27287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A537">
         <v>3607</v>
       </c>
@@ -27335,7 +27337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A538">
         <v>3608</v>
       </c>
@@ -27385,7 +27387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="539" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A539">
         <v>3609</v>
       </c>
@@ -27435,7 +27437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A540">
         <v>3610</v>
       </c>
@@ -27485,7 +27487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="541" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A541">
         <v>3611</v>
       </c>
@@ -27535,7 +27537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A542">
         <v>3612</v>
       </c>
@@ -27585,7 +27587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A543">
         <v>3613</v>
       </c>
@@ -27635,7 +27637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A544">
         <v>3614</v>
       </c>
@@ -27685,7 +27687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A545">
         <v>3615</v>
       </c>
@@ -27735,7 +27737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A546">
         <v>3616</v>
       </c>
@@ -27785,7 +27787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A547">
         <v>3617</v>
       </c>
@@ -27835,7 +27837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A548">
         <v>3618</v>
       </c>
@@ -27885,7 +27887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A549">
         <v>3619</v>
       </c>
@@ -27933,6 +27935,1706 @@
       </c>
       <c r="P549">
         <v>25</v>
+      </c>
+    </row>
+    <row r="550" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A550" s="5">
+        <v>3620</v>
+      </c>
+      <c r="B550" s="6">
+        <v>1</v>
+      </c>
+      <c r="C550" s="6">
+        <v>2</v>
+      </c>
+      <c r="D550" s="6">
+        <v>4</v>
+      </c>
+      <c r="E550" s="6">
+        <v>7</v>
+      </c>
+      <c r="F550" s="6">
+        <v>9</v>
+      </c>
+      <c r="G550" s="6">
+        <v>11</v>
+      </c>
+      <c r="H550" s="6">
+        <v>12</v>
+      </c>
+      <c r="I550" s="6">
+        <v>15</v>
+      </c>
+      <c r="J550" s="6">
+        <v>16</v>
+      </c>
+      <c r="K550" s="6">
+        <v>18</v>
+      </c>
+      <c r="L550" s="6">
+        <v>19</v>
+      </c>
+      <c r="M550" s="6">
+        <v>20</v>
+      </c>
+      <c r="N550" s="6">
+        <v>21</v>
+      </c>
+      <c r="O550" s="6">
+        <v>24</v>
+      </c>
+      <c r="P550" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="551" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A551" s="5">
+        <v>3621</v>
+      </c>
+      <c r="B551" s="6">
+        <v>1</v>
+      </c>
+      <c r="C551" s="6">
+        <v>2</v>
+      </c>
+      <c r="D551" s="6">
+        <v>4</v>
+      </c>
+      <c r="E551" s="6">
+        <v>6</v>
+      </c>
+      <c r="F551" s="6">
+        <v>7</v>
+      </c>
+      <c r="G551" s="6">
+        <v>9</v>
+      </c>
+      <c r="H551" s="6">
+        <v>10</v>
+      </c>
+      <c r="I551" s="6">
+        <v>11</v>
+      </c>
+      <c r="J551" s="6">
+        <v>13</v>
+      </c>
+      <c r="K551" s="6">
+        <v>15</v>
+      </c>
+      <c r="L551" s="6">
+        <v>18</v>
+      </c>
+      <c r="M551" s="6">
+        <v>22</v>
+      </c>
+      <c r="N551" s="6">
+        <v>23</v>
+      </c>
+      <c r="O551" s="6">
+        <v>24</v>
+      </c>
+      <c r="P551" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="552" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A552" s="5">
+        <v>3622</v>
+      </c>
+      <c r="B552" s="6">
+        <v>2</v>
+      </c>
+      <c r="C552" s="6">
+        <v>3</v>
+      </c>
+      <c r="D552" s="6">
+        <v>6</v>
+      </c>
+      <c r="E552" s="6">
+        <v>7</v>
+      </c>
+      <c r="F552" s="6">
+        <v>9</v>
+      </c>
+      <c r="G552" s="6">
+        <v>10</v>
+      </c>
+      <c r="H552" s="6">
+        <v>11</v>
+      </c>
+      <c r="I552" s="6">
+        <v>12</v>
+      </c>
+      <c r="J552" s="6">
+        <v>14</v>
+      </c>
+      <c r="K552" s="6">
+        <v>15</v>
+      </c>
+      <c r="L552" s="6">
+        <v>16</v>
+      </c>
+      <c r="M552" s="6">
+        <v>18</v>
+      </c>
+      <c r="N552" s="6">
+        <v>19</v>
+      </c>
+      <c r="O552" s="6">
+        <v>20</v>
+      </c>
+      <c r="P552" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="553" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A553" s="5">
+        <v>3623</v>
+      </c>
+      <c r="B553" s="6">
+        <v>2</v>
+      </c>
+      <c r="C553" s="6">
+        <v>4</v>
+      </c>
+      <c r="D553" s="6">
+        <v>6</v>
+      </c>
+      <c r="E553" s="6">
+        <v>7</v>
+      </c>
+      <c r="F553" s="6">
+        <v>9</v>
+      </c>
+      <c r="G553" s="6">
+        <v>10</v>
+      </c>
+      <c r="H553" s="6">
+        <v>11</v>
+      </c>
+      <c r="I553" s="6">
+        <v>12</v>
+      </c>
+      <c r="J553" s="6">
+        <v>13</v>
+      </c>
+      <c r="K553" s="6">
+        <v>14</v>
+      </c>
+      <c r="L553" s="6">
+        <v>16</v>
+      </c>
+      <c r="M553" s="6">
+        <v>19</v>
+      </c>
+      <c r="N553" s="6">
+        <v>20</v>
+      </c>
+      <c r="O553" s="6">
+        <v>22</v>
+      </c>
+      <c r="P553" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="554" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A554" s="5">
+        <v>3624</v>
+      </c>
+      <c r="B554" s="6">
+        <v>1</v>
+      </c>
+      <c r="C554" s="6">
+        <v>2</v>
+      </c>
+      <c r="D554" s="6">
+        <v>4</v>
+      </c>
+      <c r="E554" s="6">
+        <v>5</v>
+      </c>
+      <c r="F554" s="6">
+        <v>6</v>
+      </c>
+      <c r="G554" s="6">
+        <v>9</v>
+      </c>
+      <c r="H554" s="6">
+        <v>11</v>
+      </c>
+      <c r="I554" s="6">
+        <v>12</v>
+      </c>
+      <c r="J554" s="6">
+        <v>13</v>
+      </c>
+      <c r="K554" s="6">
+        <v>16</v>
+      </c>
+      <c r="L554" s="6">
+        <v>18</v>
+      </c>
+      <c r="M554" s="6">
+        <v>22</v>
+      </c>
+      <c r="N554" s="6">
+        <v>23</v>
+      </c>
+      <c r="O554" s="6">
+        <v>24</v>
+      </c>
+      <c r="P554" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="555" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A555" s="5">
+        <v>3625</v>
+      </c>
+      <c r="B555" s="6">
+        <v>1</v>
+      </c>
+      <c r="C555" s="6">
+        <v>4</v>
+      </c>
+      <c r="D555" s="6">
+        <v>8</v>
+      </c>
+      <c r="E555" s="6">
+        <v>9</v>
+      </c>
+      <c r="F555" s="6">
+        <v>10</v>
+      </c>
+      <c r="G555" s="6">
+        <v>13</v>
+      </c>
+      <c r="H555" s="6">
+        <v>15</v>
+      </c>
+      <c r="I555" s="6">
+        <v>16</v>
+      </c>
+      <c r="J555" s="6">
+        <v>17</v>
+      </c>
+      <c r="K555" s="6">
+        <v>18</v>
+      </c>
+      <c r="L555" s="6">
+        <v>19</v>
+      </c>
+      <c r="M555" s="6">
+        <v>21</v>
+      </c>
+      <c r="N555" s="6">
+        <v>23</v>
+      </c>
+      <c r="O555" s="6">
+        <v>24</v>
+      </c>
+      <c r="P555" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="556" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A556" s="5">
+        <v>3626</v>
+      </c>
+      <c r="B556" s="6">
+        <v>1</v>
+      </c>
+      <c r="C556" s="6">
+        <v>2</v>
+      </c>
+      <c r="D556" s="6">
+        <v>3</v>
+      </c>
+      <c r="E556" s="6">
+        <v>6</v>
+      </c>
+      <c r="F556" s="6">
+        <v>7</v>
+      </c>
+      <c r="G556" s="6">
+        <v>9</v>
+      </c>
+      <c r="H556" s="6">
+        <v>10</v>
+      </c>
+      <c r="I556" s="6">
+        <v>13</v>
+      </c>
+      <c r="J556" s="6">
+        <v>15</v>
+      </c>
+      <c r="K556" s="6">
+        <v>16</v>
+      </c>
+      <c r="L556" s="6">
+        <v>17</v>
+      </c>
+      <c r="M556" s="6">
+        <v>18</v>
+      </c>
+      <c r="N556" s="6">
+        <v>20</v>
+      </c>
+      <c r="O556" s="6">
+        <v>21</v>
+      </c>
+      <c r="P556" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="557" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A557" s="5">
+        <v>3627</v>
+      </c>
+      <c r="B557" s="6">
+        <v>1</v>
+      </c>
+      <c r="C557" s="6">
+        <v>2</v>
+      </c>
+      <c r="D557" s="6">
+        <v>6</v>
+      </c>
+      <c r="E557" s="6">
+        <v>7</v>
+      </c>
+      <c r="F557" s="6">
+        <v>8</v>
+      </c>
+      <c r="G557" s="6">
+        <v>9</v>
+      </c>
+      <c r="H557" s="6">
+        <v>10</v>
+      </c>
+      <c r="I557" s="6">
+        <v>12</v>
+      </c>
+      <c r="J557" s="6">
+        <v>13</v>
+      </c>
+      <c r="K557" s="6">
+        <v>14</v>
+      </c>
+      <c r="L557" s="6">
+        <v>15</v>
+      </c>
+      <c r="M557" s="6">
+        <v>16</v>
+      </c>
+      <c r="N557" s="6">
+        <v>17</v>
+      </c>
+      <c r="O557" s="6">
+        <v>19</v>
+      </c>
+      <c r="P557" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="558" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A558" s="5">
+        <v>3628</v>
+      </c>
+      <c r="B558" s="6">
+        <v>2</v>
+      </c>
+      <c r="C558" s="6">
+        <v>3</v>
+      </c>
+      <c r="D558" s="6">
+        <v>4</v>
+      </c>
+      <c r="E558" s="6">
+        <v>6</v>
+      </c>
+      <c r="F558" s="6">
+        <v>9</v>
+      </c>
+      <c r="G558" s="6">
+        <v>10</v>
+      </c>
+      <c r="H558" s="6">
+        <v>13</v>
+      </c>
+      <c r="I558" s="6">
+        <v>15</v>
+      </c>
+      <c r="J558" s="6">
+        <v>16</v>
+      </c>
+      <c r="K558" s="6">
+        <v>17</v>
+      </c>
+      <c r="L558" s="6">
+        <v>20</v>
+      </c>
+      <c r="M558" s="6">
+        <v>21</v>
+      </c>
+      <c r="N558" s="6">
+        <v>23</v>
+      </c>
+      <c r="O558" s="6">
+        <v>24</v>
+      </c>
+      <c r="P558" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="559" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A559" s="5">
+        <v>3629</v>
+      </c>
+      <c r="B559" s="6">
+        <v>1</v>
+      </c>
+      <c r="C559" s="6">
+        <v>4</v>
+      </c>
+      <c r="D559" s="6">
+        <v>7</v>
+      </c>
+      <c r="E559" s="6">
+        <v>13</v>
+      </c>
+      <c r="F559" s="6">
+        <v>14</v>
+      </c>
+      <c r="G559" s="6">
+        <v>15</v>
+      </c>
+      <c r="H559" s="6">
+        <v>16</v>
+      </c>
+      <c r="I559" s="6">
+        <v>17</v>
+      </c>
+      <c r="J559" s="6">
+        <v>19</v>
+      </c>
+      <c r="K559" s="6">
+        <v>20</v>
+      </c>
+      <c r="L559" s="6">
+        <v>21</v>
+      </c>
+      <c r="M559" s="6">
+        <v>22</v>
+      </c>
+      <c r="N559" s="6">
+        <v>23</v>
+      </c>
+      <c r="O559" s="6">
+        <v>24</v>
+      </c>
+      <c r="P559" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="560" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A560" s="5">
+        <v>3630</v>
+      </c>
+      <c r="B560" s="6">
+        <v>2</v>
+      </c>
+      <c r="C560" s="6">
+        <v>3</v>
+      </c>
+      <c r="D560" s="6">
+        <v>4</v>
+      </c>
+      <c r="E560" s="6">
+        <v>5</v>
+      </c>
+      <c r="F560" s="6">
+        <v>6</v>
+      </c>
+      <c r="G560" s="6">
+        <v>7</v>
+      </c>
+      <c r="H560" s="6">
+        <v>8</v>
+      </c>
+      <c r="I560" s="6">
+        <v>11</v>
+      </c>
+      <c r="J560" s="6">
+        <v>12</v>
+      </c>
+      <c r="K560" s="6">
+        <v>14</v>
+      </c>
+      <c r="L560" s="6">
+        <v>15</v>
+      </c>
+      <c r="M560" s="6">
+        <v>17</v>
+      </c>
+      <c r="N560" s="6">
+        <v>19</v>
+      </c>
+      <c r="O560" s="6">
+        <v>23</v>
+      </c>
+      <c r="P560" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="561" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A561" s="5">
+        <v>3631</v>
+      </c>
+      <c r="B561" s="6">
+        <v>4</v>
+      </c>
+      <c r="C561" s="6">
+        <v>7</v>
+      </c>
+      <c r="D561" s="6">
+        <v>8</v>
+      </c>
+      <c r="E561" s="6">
+        <v>9</v>
+      </c>
+      <c r="F561" s="6">
+        <v>12</v>
+      </c>
+      <c r="G561" s="6">
+        <v>13</v>
+      </c>
+      <c r="H561" s="6">
+        <v>14</v>
+      </c>
+      <c r="I561" s="6">
+        <v>15</v>
+      </c>
+      <c r="J561" s="6">
+        <v>16</v>
+      </c>
+      <c r="K561" s="6">
+        <v>17</v>
+      </c>
+      <c r="L561" s="6">
+        <v>19</v>
+      </c>
+      <c r="M561" s="6">
+        <v>20</v>
+      </c>
+      <c r="N561" s="6">
+        <v>21</v>
+      </c>
+      <c r="O561" s="6">
+        <v>23</v>
+      </c>
+      <c r="P561" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="562" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A562" s="5">
+        <v>3632</v>
+      </c>
+      <c r="B562" s="6">
+        <v>1</v>
+      </c>
+      <c r="C562" s="6">
+        <v>2</v>
+      </c>
+      <c r="D562" s="6">
+        <v>3</v>
+      </c>
+      <c r="E562" s="6">
+        <v>5</v>
+      </c>
+      <c r="F562" s="6">
+        <v>6</v>
+      </c>
+      <c r="G562" s="6">
+        <v>9</v>
+      </c>
+      <c r="H562" s="6">
+        <v>10</v>
+      </c>
+      <c r="I562" s="6">
+        <v>15</v>
+      </c>
+      <c r="J562" s="6">
+        <v>17</v>
+      </c>
+      <c r="K562" s="6">
+        <v>19</v>
+      </c>
+      <c r="L562" s="6">
+        <v>20</v>
+      </c>
+      <c r="M562" s="6">
+        <v>21</v>
+      </c>
+      <c r="N562" s="6">
+        <v>22</v>
+      </c>
+      <c r="O562" s="6">
+        <v>23</v>
+      </c>
+      <c r="P562" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="563" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A563" s="5">
+        <v>3633</v>
+      </c>
+      <c r="B563" s="6">
+        <v>1</v>
+      </c>
+      <c r="C563" s="6">
+        <v>5</v>
+      </c>
+      <c r="D563" s="6">
+        <v>6</v>
+      </c>
+      <c r="E563" s="6">
+        <v>7</v>
+      </c>
+      <c r="F563" s="6">
+        <v>10</v>
+      </c>
+      <c r="G563" s="6">
+        <v>11</v>
+      </c>
+      <c r="H563" s="6">
+        <v>13</v>
+      </c>
+      <c r="I563" s="6">
+        <v>17</v>
+      </c>
+      <c r="J563" s="6">
+        <v>18</v>
+      </c>
+      <c r="K563" s="6">
+        <v>20</v>
+      </c>
+      <c r="L563" s="6">
+        <v>21</v>
+      </c>
+      <c r="M563" s="6">
+        <v>22</v>
+      </c>
+      <c r="N563" s="6">
+        <v>23</v>
+      </c>
+      <c r="O563" s="6">
+        <v>24</v>
+      </c>
+      <c r="P563" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="564" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A564" s="5">
+        <v>3634</v>
+      </c>
+      <c r="B564" s="6">
+        <v>3</v>
+      </c>
+      <c r="C564" s="6">
+        <v>4</v>
+      </c>
+      <c r="D564" s="6">
+        <v>5</v>
+      </c>
+      <c r="E564" s="6">
+        <v>6</v>
+      </c>
+      <c r="F564" s="6">
+        <v>7</v>
+      </c>
+      <c r="G564" s="6">
+        <v>8</v>
+      </c>
+      <c r="H564" s="6">
+        <v>10</v>
+      </c>
+      <c r="I564" s="6">
+        <v>11</v>
+      </c>
+      <c r="J564" s="6">
+        <v>13</v>
+      </c>
+      <c r="K564" s="6">
+        <v>14</v>
+      </c>
+      <c r="L564" s="6">
+        <v>16</v>
+      </c>
+      <c r="M564" s="6">
+        <v>18</v>
+      </c>
+      <c r="N564" s="6">
+        <v>19</v>
+      </c>
+      <c r="O564" s="6">
+        <v>21</v>
+      </c>
+      <c r="P564" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="565" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A565" s="5">
+        <v>3635</v>
+      </c>
+      <c r="B565" s="6">
+        <v>1</v>
+      </c>
+      <c r="C565" s="6">
+        <v>2</v>
+      </c>
+      <c r="D565" s="6">
+        <v>3</v>
+      </c>
+      <c r="E565" s="6">
+        <v>5</v>
+      </c>
+      <c r="F565" s="6">
+        <v>11</v>
+      </c>
+      <c r="G565" s="6">
+        <v>12</v>
+      </c>
+      <c r="H565" s="6">
+        <v>14</v>
+      </c>
+      <c r="I565" s="6">
+        <v>15</v>
+      </c>
+      <c r="J565" s="6">
+        <v>16</v>
+      </c>
+      <c r="K565" s="6">
+        <v>19</v>
+      </c>
+      <c r="L565" s="6">
+        <v>20</v>
+      </c>
+      <c r="M565" s="6">
+        <v>22</v>
+      </c>
+      <c r="N565" s="6">
+        <v>23</v>
+      </c>
+      <c r="O565" s="6">
+        <v>24</v>
+      </c>
+      <c r="P565" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="566" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A566" s="5">
+        <v>3636</v>
+      </c>
+      <c r="B566" s="6">
+        <v>1</v>
+      </c>
+      <c r="C566" s="6">
+        <v>2</v>
+      </c>
+      <c r="D566" s="6">
+        <v>3</v>
+      </c>
+      <c r="E566" s="6">
+        <v>4</v>
+      </c>
+      <c r="F566" s="6">
+        <v>5</v>
+      </c>
+      <c r="G566" s="6">
+        <v>6</v>
+      </c>
+      <c r="H566" s="6">
+        <v>12</v>
+      </c>
+      <c r="I566" s="6">
+        <v>13</v>
+      </c>
+      <c r="J566" s="6">
+        <v>15</v>
+      </c>
+      <c r="K566" s="6">
+        <v>16</v>
+      </c>
+      <c r="L566" s="6">
+        <v>17</v>
+      </c>
+      <c r="M566" s="6">
+        <v>18</v>
+      </c>
+      <c r="N566" s="6">
+        <v>22</v>
+      </c>
+      <c r="O566" s="6">
+        <v>24</v>
+      </c>
+      <c r="P566" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="567" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A567" s="5">
+        <v>3637</v>
+      </c>
+      <c r="B567" s="6">
+        <v>3</v>
+      </c>
+      <c r="C567" s="6">
+        <v>4</v>
+      </c>
+      <c r="D567" s="6">
+        <v>6</v>
+      </c>
+      <c r="E567" s="6">
+        <v>7</v>
+      </c>
+      <c r="F567" s="6">
+        <v>8</v>
+      </c>
+      <c r="G567" s="6">
+        <v>9</v>
+      </c>
+      <c r="H567" s="6">
+        <v>10</v>
+      </c>
+      <c r="I567" s="6">
+        <v>11</v>
+      </c>
+      <c r="J567" s="6">
+        <v>12</v>
+      </c>
+      <c r="K567" s="6">
+        <v>16</v>
+      </c>
+      <c r="L567" s="6">
+        <v>17</v>
+      </c>
+      <c r="M567" s="6">
+        <v>20</v>
+      </c>
+      <c r="N567" s="6">
+        <v>21</v>
+      </c>
+      <c r="O567" s="6">
+        <v>22</v>
+      </c>
+      <c r="P567" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="568" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A568" s="5">
+        <v>3638</v>
+      </c>
+      <c r="B568" s="6">
+        <v>2</v>
+      </c>
+      <c r="C568" s="6">
+        <v>3</v>
+      </c>
+      <c r="D568" s="6">
+        <v>6</v>
+      </c>
+      <c r="E568" s="6">
+        <v>7</v>
+      </c>
+      <c r="F568" s="6">
+        <v>8</v>
+      </c>
+      <c r="G568" s="6">
+        <v>10</v>
+      </c>
+      <c r="H568" s="6">
+        <v>11</v>
+      </c>
+      <c r="I568" s="6">
+        <v>13</v>
+      </c>
+      <c r="J568" s="6">
+        <v>15</v>
+      </c>
+      <c r="K568" s="6">
+        <v>18</v>
+      </c>
+      <c r="L568" s="6">
+        <v>19</v>
+      </c>
+      <c r="M568" s="6">
+        <v>20</v>
+      </c>
+      <c r="N568" s="6">
+        <v>22</v>
+      </c>
+      <c r="O568" s="6">
+        <v>24</v>
+      </c>
+      <c r="P568" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="569" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A569" s="5">
+        <v>3639</v>
+      </c>
+      <c r="B569" s="6">
+        <v>1</v>
+      </c>
+      <c r="C569" s="6">
+        <v>3</v>
+      </c>
+      <c r="D569" s="6">
+        <v>4</v>
+      </c>
+      <c r="E569" s="6">
+        <v>5</v>
+      </c>
+      <c r="F569" s="6">
+        <v>6</v>
+      </c>
+      <c r="G569" s="6">
+        <v>7</v>
+      </c>
+      <c r="H569" s="6">
+        <v>9</v>
+      </c>
+      <c r="I569" s="6">
+        <v>10</v>
+      </c>
+      <c r="J569" s="6">
+        <v>11</v>
+      </c>
+      <c r="K569" s="6">
+        <v>12</v>
+      </c>
+      <c r="L569" s="6">
+        <v>13</v>
+      </c>
+      <c r="M569" s="6">
+        <v>15</v>
+      </c>
+      <c r="N569" s="6">
+        <v>18</v>
+      </c>
+      <c r="O569" s="6">
+        <v>23</v>
+      </c>
+      <c r="P569" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="570" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A570" s="5">
+        <v>3640</v>
+      </c>
+      <c r="B570" s="6">
+        <v>1</v>
+      </c>
+      <c r="C570" s="6">
+        <v>4</v>
+      </c>
+      <c r="D570" s="6">
+        <v>6</v>
+      </c>
+      <c r="E570" s="6">
+        <v>7</v>
+      </c>
+      <c r="F570" s="6">
+        <v>9</v>
+      </c>
+      <c r="G570" s="6">
+        <v>10</v>
+      </c>
+      <c r="H570" s="6">
+        <v>11</v>
+      </c>
+      <c r="I570" s="6">
+        <v>13</v>
+      </c>
+      <c r="J570" s="6">
+        <v>14</v>
+      </c>
+      <c r="K570" s="6">
+        <v>15</v>
+      </c>
+      <c r="L570" s="6">
+        <v>16</v>
+      </c>
+      <c r="M570" s="6">
+        <v>18</v>
+      </c>
+      <c r="N570" s="6">
+        <v>19</v>
+      </c>
+      <c r="O570" s="6">
+        <v>22</v>
+      </c>
+      <c r="P570" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="571" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A571" s="5">
+        <v>3641</v>
+      </c>
+      <c r="B571" s="6">
+        <v>1</v>
+      </c>
+      <c r="C571" s="6">
+        <v>2</v>
+      </c>
+      <c r="D571" s="6">
+        <v>3</v>
+      </c>
+      <c r="E571" s="6">
+        <v>5</v>
+      </c>
+      <c r="F571" s="6">
+        <v>6</v>
+      </c>
+      <c r="G571" s="6">
+        <v>9</v>
+      </c>
+      <c r="H571" s="6">
+        <v>10</v>
+      </c>
+      <c r="I571" s="6">
+        <v>13</v>
+      </c>
+      <c r="J571" s="6">
+        <v>14</v>
+      </c>
+      <c r="K571" s="6">
+        <v>16</v>
+      </c>
+      <c r="L571" s="6">
+        <v>19</v>
+      </c>
+      <c r="M571" s="6">
+        <v>20</v>
+      </c>
+      <c r="N571" s="6">
+        <v>21</v>
+      </c>
+      <c r="O571" s="6">
+        <v>22</v>
+      </c>
+      <c r="P571" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="572" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A572" s="5">
+        <v>3642</v>
+      </c>
+      <c r="B572" s="6">
+        <v>1</v>
+      </c>
+      <c r="C572" s="6">
+        <v>2</v>
+      </c>
+      <c r="D572" s="6">
+        <v>4</v>
+      </c>
+      <c r="E572" s="6">
+        <v>5</v>
+      </c>
+      <c r="F572" s="6">
+        <v>6</v>
+      </c>
+      <c r="G572" s="6">
+        <v>7</v>
+      </c>
+      <c r="H572" s="6">
+        <v>9</v>
+      </c>
+      <c r="I572" s="6">
+        <v>10</v>
+      </c>
+      <c r="J572" s="6">
+        <v>12</v>
+      </c>
+      <c r="K572" s="6">
+        <v>13</v>
+      </c>
+      <c r="L572" s="6">
+        <v>14</v>
+      </c>
+      <c r="M572" s="6">
+        <v>18</v>
+      </c>
+      <c r="N572" s="6">
+        <v>20</v>
+      </c>
+      <c r="O572" s="6">
+        <v>23</v>
+      </c>
+      <c r="P572" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="573" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A573" s="5">
+        <v>3643</v>
+      </c>
+      <c r="B573" s="6">
+        <v>3</v>
+      </c>
+      <c r="C573" s="6">
+        <v>4</v>
+      </c>
+      <c r="D573" s="6">
+        <v>5</v>
+      </c>
+      <c r="E573" s="6">
+        <v>6</v>
+      </c>
+      <c r="F573" s="6">
+        <v>8</v>
+      </c>
+      <c r="G573" s="6">
+        <v>9</v>
+      </c>
+      <c r="H573" s="6">
+        <v>10</v>
+      </c>
+      <c r="I573" s="6">
+        <v>13</v>
+      </c>
+      <c r="J573" s="6">
+        <v>17</v>
+      </c>
+      <c r="K573" s="6">
+        <v>19</v>
+      </c>
+      <c r="L573" s="6">
+        <v>20</v>
+      </c>
+      <c r="M573" s="6">
+        <v>22</v>
+      </c>
+      <c r="N573" s="6">
+        <v>23</v>
+      </c>
+      <c r="O573" s="6">
+        <v>24</v>
+      </c>
+      <c r="P573" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="574" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A574" s="5">
+        <v>3644</v>
+      </c>
+      <c r="B574" s="6">
+        <v>1</v>
+      </c>
+      <c r="C574" s="6">
+        <v>4</v>
+      </c>
+      <c r="D574" s="6">
+        <v>5</v>
+      </c>
+      <c r="E574" s="6">
+        <v>9</v>
+      </c>
+      <c r="F574" s="6">
+        <v>10</v>
+      </c>
+      <c r="G574" s="6">
+        <v>11</v>
+      </c>
+      <c r="H574" s="6">
+        <v>13</v>
+      </c>
+      <c r="I574" s="6">
+        <v>14</v>
+      </c>
+      <c r="J574" s="6">
+        <v>19</v>
+      </c>
+      <c r="K574" s="6">
+        <v>20</v>
+      </c>
+      <c r="L574" s="6">
+        <v>21</v>
+      </c>
+      <c r="M574" s="6">
+        <v>22</v>
+      </c>
+      <c r="N574" s="6">
+        <v>23</v>
+      </c>
+      <c r="O574" s="6">
+        <v>24</v>
+      </c>
+      <c r="P574" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="575" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A575" s="5">
+        <v>3645</v>
+      </c>
+      <c r="B575" s="6">
+        <v>1</v>
+      </c>
+      <c r="C575" s="6">
+        <v>3</v>
+      </c>
+      <c r="D575" s="6">
+        <v>6</v>
+      </c>
+      <c r="E575" s="6">
+        <v>7</v>
+      </c>
+      <c r="F575" s="6">
+        <v>8</v>
+      </c>
+      <c r="G575" s="6">
+        <v>9</v>
+      </c>
+      <c r="H575" s="6">
+        <v>10</v>
+      </c>
+      <c r="I575" s="6">
+        <v>12</v>
+      </c>
+      <c r="J575" s="6">
+        <v>13</v>
+      </c>
+      <c r="K575" s="6">
+        <v>15</v>
+      </c>
+      <c r="L575" s="6">
+        <v>17</v>
+      </c>
+      <c r="M575" s="6">
+        <v>18</v>
+      </c>
+      <c r="N575" s="6">
+        <v>19</v>
+      </c>
+      <c r="O575" s="6">
+        <v>21</v>
+      </c>
+      <c r="P575" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="576" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A576" s="5">
+        <v>3646</v>
+      </c>
+      <c r="B576" s="6">
+        <v>1</v>
+      </c>
+      <c r="C576" s="6">
+        <v>3</v>
+      </c>
+      <c r="D576" s="6">
+        <v>5</v>
+      </c>
+      <c r="E576" s="6">
+        <v>7</v>
+      </c>
+      <c r="F576" s="6">
+        <v>8</v>
+      </c>
+      <c r="G576" s="6">
+        <v>11</v>
+      </c>
+      <c r="H576" s="6">
+        <v>13</v>
+      </c>
+      <c r="I576" s="6">
+        <v>15</v>
+      </c>
+      <c r="J576" s="6">
+        <v>16</v>
+      </c>
+      <c r="K576" s="6">
+        <v>18</v>
+      </c>
+      <c r="L576" s="6">
+        <v>19</v>
+      </c>
+      <c r="M576" s="6">
+        <v>20</v>
+      </c>
+      <c r="N576" s="6">
+        <v>23</v>
+      </c>
+      <c r="O576" s="6">
+        <v>24</v>
+      </c>
+      <c r="P576" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="577" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A577" s="5">
+        <v>3647</v>
+      </c>
+      <c r="B577" s="6">
+        <v>2</v>
+      </c>
+      <c r="C577" s="6">
+        <v>4</v>
+      </c>
+      <c r="D577" s="6">
+        <v>5</v>
+      </c>
+      <c r="E577" s="6">
+        <v>8</v>
+      </c>
+      <c r="F577" s="6">
+        <v>10</v>
+      </c>
+      <c r="G577" s="6">
+        <v>12</v>
+      </c>
+      <c r="H577" s="6">
+        <v>15</v>
+      </c>
+      <c r="I577" s="6">
+        <v>16</v>
+      </c>
+      <c r="J577" s="6">
+        <v>17</v>
+      </c>
+      <c r="K577" s="6">
+        <v>19</v>
+      </c>
+      <c r="L577" s="6">
+        <v>20</v>
+      </c>
+      <c r="M577" s="6">
+        <v>21</v>
+      </c>
+      <c r="N577" s="6">
+        <v>22</v>
+      </c>
+      <c r="O577" s="6">
+        <v>24</v>
+      </c>
+      <c r="P577" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="578" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A578" s="5">
+        <v>3648</v>
+      </c>
+      <c r="B578" s="6">
+        <v>1</v>
+      </c>
+      <c r="C578" s="6">
+        <v>2</v>
+      </c>
+      <c r="D578" s="6">
+        <v>5</v>
+      </c>
+      <c r="E578" s="6">
+        <v>7</v>
+      </c>
+      <c r="F578" s="6">
+        <v>8</v>
+      </c>
+      <c r="G578" s="6">
+        <v>9</v>
+      </c>
+      <c r="H578" s="6">
+        <v>10</v>
+      </c>
+      <c r="I578" s="6">
+        <v>11</v>
+      </c>
+      <c r="J578" s="6">
+        <v>13</v>
+      </c>
+      <c r="K578" s="6">
+        <v>14</v>
+      </c>
+      <c r="L578" s="6">
+        <v>15</v>
+      </c>
+      <c r="M578" s="6">
+        <v>18</v>
+      </c>
+      <c r="N578" s="6">
+        <v>19</v>
+      </c>
+      <c r="O578" s="6">
+        <v>20</v>
+      </c>
+      <c r="P578" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="579" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A579" s="5">
+        <v>3649</v>
+      </c>
+      <c r="B579" s="6">
+        <v>6</v>
+      </c>
+      <c r="C579" s="6">
+        <v>8</v>
+      </c>
+      <c r="D579" s="6">
+        <v>9</v>
+      </c>
+      <c r="E579" s="6">
+        <v>10</v>
+      </c>
+      <c r="F579" s="6">
+        <v>11</v>
+      </c>
+      <c r="G579" s="6">
+        <v>12</v>
+      </c>
+      <c r="H579" s="6">
+        <v>13</v>
+      </c>
+      <c r="I579" s="6">
+        <v>14</v>
+      </c>
+      <c r="J579" s="6">
+        <v>15</v>
+      </c>
+      <c r="K579" s="6">
+        <v>17</v>
+      </c>
+      <c r="L579" s="6">
+        <v>18</v>
+      </c>
+      <c r="M579" s="6">
+        <v>20</v>
+      </c>
+      <c r="N579" s="6">
+        <v>21</v>
+      </c>
+      <c r="O579" s="6">
+        <v>24</v>
+      </c>
+      <c r="P579" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="580" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A580" s="5">
+        <v>3650</v>
+      </c>
+      <c r="B580" s="6">
+        <v>2</v>
+      </c>
+      <c r="C580" s="6">
+        <v>5</v>
+      </c>
+      <c r="D580" s="6">
+        <v>6</v>
+      </c>
+      <c r="E580" s="6">
+        <v>7</v>
+      </c>
+      <c r="F580" s="6">
+        <v>8</v>
+      </c>
+      <c r="G580" s="6">
+        <v>10</v>
+      </c>
+      <c r="H580" s="6">
+        <v>11</v>
+      </c>
+      <c r="I580" s="6">
+        <v>12</v>
+      </c>
+      <c r="J580" s="6">
+        <v>13</v>
+      </c>
+      <c r="K580" s="6">
+        <v>16</v>
+      </c>
+      <c r="L580" s="6">
+        <v>17</v>
+      </c>
+      <c r="M580" s="6">
+        <v>20</v>
+      </c>
+      <c r="N580" s="6">
+        <v>21</v>
+      </c>
+      <c r="O580" s="6">
+        <v>22</v>
+      </c>
+      <c r="P580" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="581" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A581" s="5">
+        <v>3651</v>
+      </c>
+      <c r="B581" s="6">
+        <v>2</v>
+      </c>
+      <c r="C581" s="6">
+        <v>3</v>
+      </c>
+      <c r="D581" s="6">
+        <v>5</v>
+      </c>
+      <c r="E581" s="6">
+        <v>8</v>
+      </c>
+      <c r="F581" s="6">
+        <v>10</v>
+      </c>
+      <c r="G581" s="6">
+        <v>12</v>
+      </c>
+      <c r="H581" s="6">
+        <v>13</v>
+      </c>
+      <c r="I581" s="6">
+        <v>14</v>
+      </c>
+      <c r="J581" s="6">
+        <v>16</v>
+      </c>
+      <c r="K581" s="6">
+        <v>17</v>
+      </c>
+      <c r="L581" s="6">
+        <v>18</v>
+      </c>
+      <c r="M581" s="6">
+        <v>20</v>
+      </c>
+      <c r="N581" s="6">
+        <v>21</v>
+      </c>
+      <c r="O581" s="6">
+        <v>24</v>
+      </c>
+      <c r="P581" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="582" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A582" s="5">
+        <v>3652</v>
+      </c>
+      <c r="B582" s="6">
+        <v>1</v>
+      </c>
+      <c r="C582" s="6">
+        <v>3</v>
+      </c>
+      <c r="D582" s="6">
+        <v>6</v>
+      </c>
+      <c r="E582" s="6">
+        <v>7</v>
+      </c>
+      <c r="F582" s="6">
+        <v>11</v>
+      </c>
+      <c r="G582" s="6">
+        <v>12</v>
+      </c>
+      <c r="H582" s="6">
+        <v>13</v>
+      </c>
+      <c r="I582" s="6">
+        <v>15</v>
+      </c>
+      <c r="J582" s="6">
+        <v>16</v>
+      </c>
+      <c r="K582" s="6">
+        <v>18</v>
+      </c>
+      <c r="L582" s="6">
+        <v>19</v>
+      </c>
+      <c r="M582" s="6">
+        <v>20</v>
+      </c>
+      <c r="N582" s="6">
+        <v>21</v>
+      </c>
+      <c r="O582" s="6">
+        <v>23</v>
+      </c>
+      <c r="P582" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="583" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A583" s="5">
+        <v>3653</v>
+      </c>
+      <c r="B583" s="6">
+        <v>2</v>
+      </c>
+      <c r="C583" s="6">
+        <v>3</v>
+      </c>
+      <c r="D583" s="6">
+        <v>4</v>
+      </c>
+      <c r="E583" s="6">
+        <v>6</v>
+      </c>
+      <c r="F583" s="6">
+        <v>7</v>
+      </c>
+      <c r="G583" s="6">
+        <v>8</v>
+      </c>
+      <c r="H583" s="6">
+        <v>10</v>
+      </c>
+      <c r="I583" s="6">
+        <v>11</v>
+      </c>
+      <c r="J583" s="6">
+        <v>13</v>
+      </c>
+      <c r="K583" s="6">
+        <v>14</v>
+      </c>
+      <c r="L583" s="6">
+        <v>16</v>
+      </c>
+      <c r="M583" s="6">
+        <v>18</v>
+      </c>
+      <c r="N583" s="6">
+        <v>19</v>
+      </c>
+      <c r="O583" s="6">
+        <v>20</v>
+      </c>
+      <c r="P583" s="6">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -27941,15 +29643,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -28117,6 +29810,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -28128,14 +29830,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28155,6 +29849,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D498C76-72EC-4110-B264-5DA0FD04AD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDCB27B-F5B4-4F66-B6A9-76A06A00045C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57795" yWindow="195" windowWidth="22140" windowHeight="17235" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57585" yWindow="1395" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P583"/>
+  <dimension ref="A1:P598"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -27938,1703 +27938,2453 @@
       </c>
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A550" s="5">
+      <c r="A550">
         <v>3620</v>
       </c>
-      <c r="B550" s="6">
-        <v>1</v>
-      </c>
-      <c r="C550" s="6">
-        <v>2</v>
-      </c>
-      <c r="D550" s="6">
-        <v>4</v>
-      </c>
-      <c r="E550" s="6">
-        <v>7</v>
-      </c>
-      <c r="F550" s="6">
-        <v>9</v>
-      </c>
-      <c r="G550" s="6">
-        <v>11</v>
-      </c>
-      <c r="H550" s="6">
-        <v>12</v>
-      </c>
-      <c r="I550" s="6">
-        <v>15</v>
-      </c>
-      <c r="J550" s="6">
-        <v>16</v>
-      </c>
-      <c r="K550" s="6">
-        <v>18</v>
-      </c>
-      <c r="L550" s="6">
-        <v>19</v>
-      </c>
-      <c r="M550" s="6">
-        <v>20</v>
-      </c>
-      <c r="N550" s="6">
-        <v>21</v>
-      </c>
-      <c r="O550" s="6">
-        <v>24</v>
-      </c>
-      <c r="P550" s="6">
+      <c r="B550">
+        <v>1</v>
+      </c>
+      <c r="C550">
+        <v>2</v>
+      </c>
+      <c r="D550">
+        <v>4</v>
+      </c>
+      <c r="E550">
+        <v>7</v>
+      </c>
+      <c r="F550">
+        <v>9</v>
+      </c>
+      <c r="G550">
+        <v>11</v>
+      </c>
+      <c r="H550">
+        <v>12</v>
+      </c>
+      <c r="I550">
+        <v>15</v>
+      </c>
+      <c r="J550">
+        <v>16</v>
+      </c>
+      <c r="K550">
+        <v>18</v>
+      </c>
+      <c r="L550">
+        <v>19</v>
+      </c>
+      <c r="M550">
+        <v>20</v>
+      </c>
+      <c r="N550">
+        <v>21</v>
+      </c>
+      <c r="O550">
+        <v>24</v>
+      </c>
+      <c r="P550">
         <v>25</v>
       </c>
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A551" s="5">
+      <c r="A551">
         <v>3621</v>
       </c>
-      <c r="B551" s="6">
-        <v>1</v>
-      </c>
-      <c r="C551" s="6">
-        <v>2</v>
-      </c>
-      <c r="D551" s="6">
-        <v>4</v>
-      </c>
-      <c r="E551" s="6">
-        <v>6</v>
-      </c>
-      <c r="F551" s="6">
-        <v>7</v>
-      </c>
-      <c r="G551" s="6">
-        <v>9</v>
-      </c>
-      <c r="H551" s="6">
-        <v>10</v>
-      </c>
-      <c r="I551" s="6">
-        <v>11</v>
-      </c>
-      <c r="J551" s="6">
-        <v>13</v>
-      </c>
-      <c r="K551" s="6">
-        <v>15</v>
-      </c>
-      <c r="L551" s="6">
-        <v>18</v>
-      </c>
-      <c r="M551" s="6">
-        <v>22</v>
-      </c>
-      <c r="N551" s="6">
-        <v>23</v>
-      </c>
-      <c r="O551" s="6">
-        <v>24</v>
-      </c>
-      <c r="P551" s="6">
+      <c r="B551">
+        <v>1</v>
+      </c>
+      <c r="C551">
+        <v>2</v>
+      </c>
+      <c r="D551">
+        <v>4</v>
+      </c>
+      <c r="E551">
+        <v>6</v>
+      </c>
+      <c r="F551">
+        <v>7</v>
+      </c>
+      <c r="G551">
+        <v>9</v>
+      </c>
+      <c r="H551">
+        <v>10</v>
+      </c>
+      <c r="I551">
+        <v>11</v>
+      </c>
+      <c r="J551">
+        <v>13</v>
+      </c>
+      <c r="K551">
+        <v>15</v>
+      </c>
+      <c r="L551">
+        <v>18</v>
+      </c>
+      <c r="M551">
+        <v>22</v>
+      </c>
+      <c r="N551">
+        <v>23</v>
+      </c>
+      <c r="O551">
+        <v>24</v>
+      </c>
+      <c r="P551">
         <v>25</v>
       </c>
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A552" s="5">
+      <c r="A552">
         <v>3622</v>
       </c>
-      <c r="B552" s="6">
-        <v>2</v>
-      </c>
-      <c r="C552" s="6">
-        <v>3</v>
-      </c>
-      <c r="D552" s="6">
-        <v>6</v>
-      </c>
-      <c r="E552" s="6">
-        <v>7</v>
-      </c>
-      <c r="F552" s="6">
-        <v>9</v>
-      </c>
-      <c r="G552" s="6">
-        <v>10</v>
-      </c>
-      <c r="H552" s="6">
-        <v>11</v>
-      </c>
-      <c r="I552" s="6">
-        <v>12</v>
-      </c>
-      <c r="J552" s="6">
-        <v>14</v>
-      </c>
-      <c r="K552" s="6">
-        <v>15</v>
-      </c>
-      <c r="L552" s="6">
-        <v>16</v>
-      </c>
-      <c r="M552" s="6">
-        <v>18</v>
-      </c>
-      <c r="N552" s="6">
-        <v>19</v>
-      </c>
-      <c r="O552" s="6">
-        <v>20</v>
-      </c>
-      <c r="P552" s="6">
+      <c r="B552">
+        <v>2</v>
+      </c>
+      <c r="C552">
+        <v>3</v>
+      </c>
+      <c r="D552">
+        <v>6</v>
+      </c>
+      <c r="E552">
+        <v>7</v>
+      </c>
+      <c r="F552">
+        <v>9</v>
+      </c>
+      <c r="G552">
+        <v>10</v>
+      </c>
+      <c r="H552">
+        <v>11</v>
+      </c>
+      <c r="I552">
+        <v>12</v>
+      </c>
+      <c r="J552">
+        <v>14</v>
+      </c>
+      <c r="K552">
+        <v>15</v>
+      </c>
+      <c r="L552">
+        <v>16</v>
+      </c>
+      <c r="M552">
+        <v>18</v>
+      </c>
+      <c r="N552">
+        <v>19</v>
+      </c>
+      <c r="O552">
+        <v>20</v>
+      </c>
+      <c r="P552">
         <v>21</v>
       </c>
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A553" s="5">
+      <c r="A553">
         <v>3623</v>
       </c>
-      <c r="B553" s="6">
-        <v>2</v>
-      </c>
-      <c r="C553" s="6">
-        <v>4</v>
-      </c>
-      <c r="D553" s="6">
-        <v>6</v>
-      </c>
-      <c r="E553" s="6">
-        <v>7</v>
-      </c>
-      <c r="F553" s="6">
-        <v>9</v>
-      </c>
-      <c r="G553" s="6">
-        <v>10</v>
-      </c>
-      <c r="H553" s="6">
-        <v>11</v>
-      </c>
-      <c r="I553" s="6">
-        <v>12</v>
-      </c>
-      <c r="J553" s="6">
-        <v>13</v>
-      </c>
-      <c r="K553" s="6">
-        <v>14</v>
-      </c>
-      <c r="L553" s="6">
-        <v>16</v>
-      </c>
-      <c r="M553" s="6">
-        <v>19</v>
-      </c>
-      <c r="N553" s="6">
-        <v>20</v>
-      </c>
-      <c r="O553" s="6">
-        <v>22</v>
-      </c>
-      <c r="P553" s="6">
+      <c r="B553">
+        <v>2</v>
+      </c>
+      <c r="C553">
+        <v>4</v>
+      </c>
+      <c r="D553">
+        <v>6</v>
+      </c>
+      <c r="E553">
+        <v>7</v>
+      </c>
+      <c r="F553">
+        <v>9</v>
+      </c>
+      <c r="G553">
+        <v>10</v>
+      </c>
+      <c r="H553">
+        <v>11</v>
+      </c>
+      <c r="I553">
+        <v>12</v>
+      </c>
+      <c r="J553">
+        <v>13</v>
+      </c>
+      <c r="K553">
+        <v>14</v>
+      </c>
+      <c r="L553">
+        <v>16</v>
+      </c>
+      <c r="M553">
+        <v>19</v>
+      </c>
+      <c r="N553">
+        <v>20</v>
+      </c>
+      <c r="O553">
+        <v>22</v>
+      </c>
+      <c r="P553">
         <v>24</v>
       </c>
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A554" s="5">
+      <c r="A554">
         <v>3624</v>
       </c>
-      <c r="B554" s="6">
-        <v>1</v>
-      </c>
-      <c r="C554" s="6">
-        <v>2</v>
-      </c>
-      <c r="D554" s="6">
-        <v>4</v>
-      </c>
-      <c r="E554" s="6">
-        <v>5</v>
-      </c>
-      <c r="F554" s="6">
-        <v>6</v>
-      </c>
-      <c r="G554" s="6">
-        <v>9</v>
-      </c>
-      <c r="H554" s="6">
-        <v>11</v>
-      </c>
-      <c r="I554" s="6">
-        <v>12</v>
-      </c>
-      <c r="J554" s="6">
-        <v>13</v>
-      </c>
-      <c r="K554" s="6">
-        <v>16</v>
-      </c>
-      <c r="L554" s="6">
-        <v>18</v>
-      </c>
-      <c r="M554" s="6">
-        <v>22</v>
-      </c>
-      <c r="N554" s="6">
-        <v>23</v>
-      </c>
-      <c r="O554" s="6">
-        <v>24</v>
-      </c>
-      <c r="P554" s="6">
+      <c r="B554">
+        <v>1</v>
+      </c>
+      <c r="C554">
+        <v>2</v>
+      </c>
+      <c r="D554">
+        <v>4</v>
+      </c>
+      <c r="E554">
+        <v>5</v>
+      </c>
+      <c r="F554">
+        <v>6</v>
+      </c>
+      <c r="G554">
+        <v>9</v>
+      </c>
+      <c r="H554">
+        <v>11</v>
+      </c>
+      <c r="I554">
+        <v>12</v>
+      </c>
+      <c r="J554">
+        <v>13</v>
+      </c>
+      <c r="K554">
+        <v>16</v>
+      </c>
+      <c r="L554">
+        <v>18</v>
+      </c>
+      <c r="M554">
+        <v>22</v>
+      </c>
+      <c r="N554">
+        <v>23</v>
+      </c>
+      <c r="O554">
+        <v>24</v>
+      </c>
+      <c r="P554">
         <v>25</v>
       </c>
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A555" s="5">
+      <c r="A555">
         <v>3625</v>
       </c>
-      <c r="B555" s="6">
-        <v>1</v>
-      </c>
-      <c r="C555" s="6">
-        <v>4</v>
-      </c>
-      <c r="D555" s="6">
-        <v>8</v>
-      </c>
-      <c r="E555" s="6">
-        <v>9</v>
-      </c>
-      <c r="F555" s="6">
-        <v>10</v>
-      </c>
-      <c r="G555" s="6">
-        <v>13</v>
-      </c>
-      <c r="H555" s="6">
-        <v>15</v>
-      </c>
-      <c r="I555" s="6">
-        <v>16</v>
-      </c>
-      <c r="J555" s="6">
-        <v>17</v>
-      </c>
-      <c r="K555" s="6">
-        <v>18</v>
-      </c>
-      <c r="L555" s="6">
-        <v>19</v>
-      </c>
-      <c r="M555" s="6">
-        <v>21</v>
-      </c>
-      <c r="N555" s="6">
-        <v>23</v>
-      </c>
-      <c r="O555" s="6">
-        <v>24</v>
-      </c>
-      <c r="P555" s="6">
+      <c r="B555">
+        <v>1</v>
+      </c>
+      <c r="C555">
+        <v>4</v>
+      </c>
+      <c r="D555">
+        <v>8</v>
+      </c>
+      <c r="E555">
+        <v>9</v>
+      </c>
+      <c r="F555">
+        <v>10</v>
+      </c>
+      <c r="G555">
+        <v>13</v>
+      </c>
+      <c r="H555">
+        <v>15</v>
+      </c>
+      <c r="I555">
+        <v>16</v>
+      </c>
+      <c r="J555">
+        <v>17</v>
+      </c>
+      <c r="K555">
+        <v>18</v>
+      </c>
+      <c r="L555">
+        <v>19</v>
+      </c>
+      <c r="M555">
+        <v>21</v>
+      </c>
+      <c r="N555">
+        <v>23</v>
+      </c>
+      <c r="O555">
+        <v>24</v>
+      </c>
+      <c r="P555">
         <v>25</v>
       </c>
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A556" s="5">
+      <c r="A556">
         <v>3626</v>
       </c>
-      <c r="B556" s="6">
-        <v>1</v>
-      </c>
-      <c r="C556" s="6">
-        <v>2</v>
-      </c>
-      <c r="D556" s="6">
-        <v>3</v>
-      </c>
-      <c r="E556" s="6">
-        <v>6</v>
-      </c>
-      <c r="F556" s="6">
-        <v>7</v>
-      </c>
-      <c r="G556" s="6">
-        <v>9</v>
-      </c>
-      <c r="H556" s="6">
-        <v>10</v>
-      </c>
-      <c r="I556" s="6">
-        <v>13</v>
-      </c>
-      <c r="J556" s="6">
-        <v>15</v>
-      </c>
-      <c r="K556" s="6">
-        <v>16</v>
-      </c>
-      <c r="L556" s="6">
-        <v>17</v>
-      </c>
-      <c r="M556" s="6">
-        <v>18</v>
-      </c>
-      <c r="N556" s="6">
-        <v>20</v>
-      </c>
-      <c r="O556" s="6">
-        <v>21</v>
-      </c>
-      <c r="P556" s="6">
+      <c r="B556">
+        <v>1</v>
+      </c>
+      <c r="C556">
+        <v>2</v>
+      </c>
+      <c r="D556">
+        <v>3</v>
+      </c>
+      <c r="E556">
+        <v>6</v>
+      </c>
+      <c r="F556">
+        <v>7</v>
+      </c>
+      <c r="G556">
+        <v>9</v>
+      </c>
+      <c r="H556">
+        <v>10</v>
+      </c>
+      <c r="I556">
+        <v>13</v>
+      </c>
+      <c r="J556">
+        <v>15</v>
+      </c>
+      <c r="K556">
+        <v>16</v>
+      </c>
+      <c r="L556">
+        <v>17</v>
+      </c>
+      <c r="M556">
+        <v>18</v>
+      </c>
+      <c r="N556">
+        <v>20</v>
+      </c>
+      <c r="O556">
+        <v>21</v>
+      </c>
+      <c r="P556">
         <v>25</v>
       </c>
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A557" s="5">
+      <c r="A557">
         <v>3627</v>
       </c>
-      <c r="B557" s="6">
-        <v>1</v>
-      </c>
-      <c r="C557" s="6">
-        <v>2</v>
-      </c>
-      <c r="D557" s="6">
-        <v>6</v>
-      </c>
-      <c r="E557" s="6">
-        <v>7</v>
-      </c>
-      <c r="F557" s="6">
-        <v>8</v>
-      </c>
-      <c r="G557" s="6">
-        <v>9</v>
-      </c>
-      <c r="H557" s="6">
-        <v>10</v>
-      </c>
-      <c r="I557" s="6">
-        <v>12</v>
-      </c>
-      <c r="J557" s="6">
-        <v>13</v>
-      </c>
-      <c r="K557" s="6">
-        <v>14</v>
-      </c>
-      <c r="L557" s="6">
-        <v>15</v>
-      </c>
-      <c r="M557" s="6">
-        <v>16</v>
-      </c>
-      <c r="N557" s="6">
-        <v>17</v>
-      </c>
-      <c r="O557" s="6">
-        <v>19</v>
-      </c>
-      <c r="P557" s="6">
+      <c r="B557">
+        <v>1</v>
+      </c>
+      <c r="C557">
+        <v>2</v>
+      </c>
+      <c r="D557">
+        <v>6</v>
+      </c>
+      <c r="E557">
+        <v>7</v>
+      </c>
+      <c r="F557">
+        <v>8</v>
+      </c>
+      <c r="G557">
+        <v>9</v>
+      </c>
+      <c r="H557">
+        <v>10</v>
+      </c>
+      <c r="I557">
+        <v>12</v>
+      </c>
+      <c r="J557">
+        <v>13</v>
+      </c>
+      <c r="K557">
+        <v>14</v>
+      </c>
+      <c r="L557">
+        <v>15</v>
+      </c>
+      <c r="M557">
+        <v>16</v>
+      </c>
+      <c r="N557">
+        <v>17</v>
+      </c>
+      <c r="O557">
+        <v>19</v>
+      </c>
+      <c r="P557">
         <v>21</v>
       </c>
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A558" s="5">
+      <c r="A558">
         <v>3628</v>
       </c>
-      <c r="B558" s="6">
-        <v>2</v>
-      </c>
-      <c r="C558" s="6">
-        <v>3</v>
-      </c>
-      <c r="D558" s="6">
-        <v>4</v>
-      </c>
-      <c r="E558" s="6">
-        <v>6</v>
-      </c>
-      <c r="F558" s="6">
-        <v>9</v>
-      </c>
-      <c r="G558" s="6">
-        <v>10</v>
-      </c>
-      <c r="H558" s="6">
-        <v>13</v>
-      </c>
-      <c r="I558" s="6">
-        <v>15</v>
-      </c>
-      <c r="J558" s="6">
-        <v>16</v>
-      </c>
-      <c r="K558" s="6">
-        <v>17</v>
-      </c>
-      <c r="L558" s="6">
-        <v>20</v>
-      </c>
-      <c r="M558" s="6">
-        <v>21</v>
-      </c>
-      <c r="N558" s="6">
-        <v>23</v>
-      </c>
-      <c r="O558" s="6">
-        <v>24</v>
-      </c>
-      <c r="P558" s="6">
+      <c r="B558">
+        <v>2</v>
+      </c>
+      <c r="C558">
+        <v>3</v>
+      </c>
+      <c r="D558">
+        <v>4</v>
+      </c>
+      <c r="E558">
+        <v>6</v>
+      </c>
+      <c r="F558">
+        <v>9</v>
+      </c>
+      <c r="G558">
+        <v>10</v>
+      </c>
+      <c r="H558">
+        <v>13</v>
+      </c>
+      <c r="I558">
+        <v>15</v>
+      </c>
+      <c r="J558">
+        <v>16</v>
+      </c>
+      <c r="K558">
+        <v>17</v>
+      </c>
+      <c r="L558">
+        <v>20</v>
+      </c>
+      <c r="M558">
+        <v>21</v>
+      </c>
+      <c r="N558">
+        <v>23</v>
+      </c>
+      <c r="O558">
+        <v>24</v>
+      </c>
+      <c r="P558">
         <v>25</v>
       </c>
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A559" s="5">
+      <c r="A559">
         <v>3629</v>
       </c>
-      <c r="B559" s="6">
-        <v>1</v>
-      </c>
-      <c r="C559" s="6">
-        <v>4</v>
-      </c>
-      <c r="D559" s="6">
-        <v>7</v>
-      </c>
-      <c r="E559" s="6">
-        <v>13</v>
-      </c>
-      <c r="F559" s="6">
-        <v>14</v>
-      </c>
-      <c r="G559" s="6">
-        <v>15</v>
-      </c>
-      <c r="H559" s="6">
-        <v>16</v>
-      </c>
-      <c r="I559" s="6">
-        <v>17</v>
-      </c>
-      <c r="J559" s="6">
-        <v>19</v>
-      </c>
-      <c r="K559" s="6">
-        <v>20</v>
-      </c>
-      <c r="L559" s="6">
-        <v>21</v>
-      </c>
-      <c r="M559" s="6">
-        <v>22</v>
-      </c>
-      <c r="N559" s="6">
-        <v>23</v>
-      </c>
-      <c r="O559" s="6">
-        <v>24</v>
-      </c>
-      <c r="P559" s="6">
+      <c r="B559">
+        <v>1</v>
+      </c>
+      <c r="C559">
+        <v>4</v>
+      </c>
+      <c r="D559">
+        <v>7</v>
+      </c>
+      <c r="E559">
+        <v>13</v>
+      </c>
+      <c r="F559">
+        <v>14</v>
+      </c>
+      <c r="G559">
+        <v>15</v>
+      </c>
+      <c r="H559">
+        <v>16</v>
+      </c>
+      <c r="I559">
+        <v>17</v>
+      </c>
+      <c r="J559">
+        <v>19</v>
+      </c>
+      <c r="K559">
+        <v>20</v>
+      </c>
+      <c r="L559">
+        <v>21</v>
+      </c>
+      <c r="M559">
+        <v>22</v>
+      </c>
+      <c r="N559">
+        <v>23</v>
+      </c>
+      <c r="O559">
+        <v>24</v>
+      </c>
+      <c r="P559">
         <v>25</v>
       </c>
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A560" s="5">
+      <c r="A560">
         <v>3630</v>
       </c>
-      <c r="B560" s="6">
-        <v>2</v>
-      </c>
-      <c r="C560" s="6">
-        <v>3</v>
-      </c>
-      <c r="D560" s="6">
-        <v>4</v>
-      </c>
-      <c r="E560" s="6">
-        <v>5</v>
-      </c>
-      <c r="F560" s="6">
-        <v>6</v>
-      </c>
-      <c r="G560" s="6">
-        <v>7</v>
-      </c>
-      <c r="H560" s="6">
-        <v>8</v>
-      </c>
-      <c r="I560" s="6">
-        <v>11</v>
-      </c>
-      <c r="J560" s="6">
-        <v>12</v>
-      </c>
-      <c r="K560" s="6">
-        <v>14</v>
-      </c>
-      <c r="L560" s="6">
-        <v>15</v>
-      </c>
-      <c r="M560" s="6">
-        <v>17</v>
-      </c>
-      <c r="N560" s="6">
-        <v>19</v>
-      </c>
-      <c r="O560" s="6">
-        <v>23</v>
-      </c>
-      <c r="P560" s="6">
+      <c r="B560">
+        <v>2</v>
+      </c>
+      <c r="C560">
+        <v>3</v>
+      </c>
+      <c r="D560">
+        <v>4</v>
+      </c>
+      <c r="E560">
+        <v>5</v>
+      </c>
+      <c r="F560">
+        <v>6</v>
+      </c>
+      <c r="G560">
+        <v>7</v>
+      </c>
+      <c r="H560">
+        <v>8</v>
+      </c>
+      <c r="I560">
+        <v>11</v>
+      </c>
+      <c r="J560">
+        <v>12</v>
+      </c>
+      <c r="K560">
+        <v>14</v>
+      </c>
+      <c r="L560">
+        <v>15</v>
+      </c>
+      <c r="M560">
+        <v>17</v>
+      </c>
+      <c r="N560">
+        <v>19</v>
+      </c>
+      <c r="O560">
+        <v>23</v>
+      </c>
+      <c r="P560">
         <v>24</v>
       </c>
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A561" s="5">
+      <c r="A561">
         <v>3631</v>
       </c>
-      <c r="B561" s="6">
-        <v>4</v>
-      </c>
-      <c r="C561" s="6">
-        <v>7</v>
-      </c>
-      <c r="D561" s="6">
-        <v>8</v>
-      </c>
-      <c r="E561" s="6">
-        <v>9</v>
-      </c>
-      <c r="F561" s="6">
-        <v>12</v>
-      </c>
-      <c r="G561" s="6">
-        <v>13</v>
-      </c>
-      <c r="H561" s="6">
-        <v>14</v>
-      </c>
-      <c r="I561" s="6">
-        <v>15</v>
-      </c>
-      <c r="J561" s="6">
-        <v>16</v>
-      </c>
-      <c r="K561" s="6">
-        <v>17</v>
-      </c>
-      <c r="L561" s="6">
-        <v>19</v>
-      </c>
-      <c r="M561" s="6">
-        <v>20</v>
-      </c>
-      <c r="N561" s="6">
-        <v>21</v>
-      </c>
-      <c r="O561" s="6">
-        <v>23</v>
-      </c>
-      <c r="P561" s="6">
+      <c r="B561">
+        <v>4</v>
+      </c>
+      <c r="C561">
+        <v>7</v>
+      </c>
+      <c r="D561">
+        <v>8</v>
+      </c>
+      <c r="E561">
+        <v>9</v>
+      </c>
+      <c r="F561">
+        <v>12</v>
+      </c>
+      <c r="G561">
+        <v>13</v>
+      </c>
+      <c r="H561">
+        <v>14</v>
+      </c>
+      <c r="I561">
+        <v>15</v>
+      </c>
+      <c r="J561">
+        <v>16</v>
+      </c>
+      <c r="K561">
+        <v>17</v>
+      </c>
+      <c r="L561">
+        <v>19</v>
+      </c>
+      <c r="M561">
+        <v>20</v>
+      </c>
+      <c r="N561">
+        <v>21</v>
+      </c>
+      <c r="O561">
+        <v>23</v>
+      </c>
+      <c r="P561">
         <v>25</v>
       </c>
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A562" s="5">
+      <c r="A562">
         <v>3632</v>
       </c>
-      <c r="B562" s="6">
-        <v>1</v>
-      </c>
-      <c r="C562" s="6">
-        <v>2</v>
-      </c>
-      <c r="D562" s="6">
-        <v>3</v>
-      </c>
-      <c r="E562" s="6">
-        <v>5</v>
-      </c>
-      <c r="F562" s="6">
-        <v>6</v>
-      </c>
-      <c r="G562" s="6">
-        <v>9</v>
-      </c>
-      <c r="H562" s="6">
-        <v>10</v>
-      </c>
-      <c r="I562" s="6">
-        <v>15</v>
-      </c>
-      <c r="J562" s="6">
-        <v>17</v>
-      </c>
-      <c r="K562" s="6">
-        <v>19</v>
-      </c>
-      <c r="L562" s="6">
-        <v>20</v>
-      </c>
-      <c r="M562" s="6">
-        <v>21</v>
-      </c>
-      <c r="N562" s="6">
-        <v>22</v>
-      </c>
-      <c r="O562" s="6">
-        <v>23</v>
-      </c>
-      <c r="P562" s="6">
+      <c r="B562">
+        <v>1</v>
+      </c>
+      <c r="C562">
+        <v>2</v>
+      </c>
+      <c r="D562">
+        <v>3</v>
+      </c>
+      <c r="E562">
+        <v>5</v>
+      </c>
+      <c r="F562">
+        <v>6</v>
+      </c>
+      <c r="G562">
+        <v>9</v>
+      </c>
+      <c r="H562">
+        <v>10</v>
+      </c>
+      <c r="I562">
+        <v>15</v>
+      </c>
+      <c r="J562">
+        <v>17</v>
+      </c>
+      <c r="K562">
+        <v>19</v>
+      </c>
+      <c r="L562">
+        <v>20</v>
+      </c>
+      <c r="M562">
+        <v>21</v>
+      </c>
+      <c r="N562">
+        <v>22</v>
+      </c>
+      <c r="O562">
+        <v>23</v>
+      </c>
+      <c r="P562">
         <v>25</v>
       </c>
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A563" s="5">
+      <c r="A563">
         <v>3633</v>
       </c>
-      <c r="B563" s="6">
-        <v>1</v>
-      </c>
-      <c r="C563" s="6">
-        <v>5</v>
-      </c>
-      <c r="D563" s="6">
-        <v>6</v>
-      </c>
-      <c r="E563" s="6">
-        <v>7</v>
-      </c>
-      <c r="F563" s="6">
-        <v>10</v>
-      </c>
-      <c r="G563" s="6">
-        <v>11</v>
-      </c>
-      <c r="H563" s="6">
-        <v>13</v>
-      </c>
-      <c r="I563" s="6">
-        <v>17</v>
-      </c>
-      <c r="J563" s="6">
-        <v>18</v>
-      </c>
-      <c r="K563" s="6">
-        <v>20</v>
-      </c>
-      <c r="L563" s="6">
-        <v>21</v>
-      </c>
-      <c r="M563" s="6">
-        <v>22</v>
-      </c>
-      <c r="N563" s="6">
-        <v>23</v>
-      </c>
-      <c r="O563" s="6">
-        <v>24</v>
-      </c>
-      <c r="P563" s="6">
+      <c r="B563">
+        <v>1</v>
+      </c>
+      <c r="C563">
+        <v>5</v>
+      </c>
+      <c r="D563">
+        <v>6</v>
+      </c>
+      <c r="E563">
+        <v>7</v>
+      </c>
+      <c r="F563">
+        <v>10</v>
+      </c>
+      <c r="G563">
+        <v>11</v>
+      </c>
+      <c r="H563">
+        <v>13</v>
+      </c>
+      <c r="I563">
+        <v>17</v>
+      </c>
+      <c r="J563">
+        <v>18</v>
+      </c>
+      <c r="K563">
+        <v>20</v>
+      </c>
+      <c r="L563">
+        <v>21</v>
+      </c>
+      <c r="M563">
+        <v>22</v>
+      </c>
+      <c r="N563">
+        <v>23</v>
+      </c>
+      <c r="O563">
+        <v>24</v>
+      </c>
+      <c r="P563">
         <v>25</v>
       </c>
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A564" s="5">
+      <c r="A564">
         <v>3634</v>
       </c>
-      <c r="B564" s="6">
-        <v>3</v>
-      </c>
-      <c r="C564" s="6">
-        <v>4</v>
-      </c>
-      <c r="D564" s="6">
-        <v>5</v>
-      </c>
-      <c r="E564" s="6">
-        <v>6</v>
-      </c>
-      <c r="F564" s="6">
-        <v>7</v>
-      </c>
-      <c r="G564" s="6">
-        <v>8</v>
-      </c>
-      <c r="H564" s="6">
-        <v>10</v>
-      </c>
-      <c r="I564" s="6">
-        <v>11</v>
-      </c>
-      <c r="J564" s="6">
-        <v>13</v>
-      </c>
-      <c r="K564" s="6">
-        <v>14</v>
-      </c>
-      <c r="L564" s="6">
-        <v>16</v>
-      </c>
-      <c r="M564" s="6">
-        <v>18</v>
-      </c>
-      <c r="N564" s="6">
-        <v>19</v>
-      </c>
-      <c r="O564" s="6">
-        <v>21</v>
-      </c>
-      <c r="P564" s="6">
+      <c r="B564">
+        <v>3</v>
+      </c>
+      <c r="C564">
+        <v>4</v>
+      </c>
+      <c r="D564">
+        <v>5</v>
+      </c>
+      <c r="E564">
+        <v>6</v>
+      </c>
+      <c r="F564">
+        <v>7</v>
+      </c>
+      <c r="G564">
+        <v>8</v>
+      </c>
+      <c r="H564">
+        <v>10</v>
+      </c>
+      <c r="I564">
+        <v>11</v>
+      </c>
+      <c r="J564">
+        <v>13</v>
+      </c>
+      <c r="K564">
+        <v>14</v>
+      </c>
+      <c r="L564">
+        <v>16</v>
+      </c>
+      <c r="M564">
+        <v>18</v>
+      </c>
+      <c r="N564">
+        <v>19</v>
+      </c>
+      <c r="O564">
+        <v>21</v>
+      </c>
+      <c r="P564">
         <v>25</v>
       </c>
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A565" s="5">
+      <c r="A565">
         <v>3635</v>
       </c>
-      <c r="B565" s="6">
-        <v>1</v>
-      </c>
-      <c r="C565" s="6">
-        <v>2</v>
-      </c>
-      <c r="D565" s="6">
-        <v>3</v>
-      </c>
-      <c r="E565" s="6">
-        <v>5</v>
-      </c>
-      <c r="F565" s="6">
-        <v>11</v>
-      </c>
-      <c r="G565" s="6">
-        <v>12</v>
-      </c>
-      <c r="H565" s="6">
-        <v>14</v>
-      </c>
-      <c r="I565" s="6">
-        <v>15</v>
-      </c>
-      <c r="J565" s="6">
-        <v>16</v>
-      </c>
-      <c r="K565" s="6">
-        <v>19</v>
-      </c>
-      <c r="L565" s="6">
-        <v>20</v>
-      </c>
-      <c r="M565" s="6">
-        <v>22</v>
-      </c>
-      <c r="N565" s="6">
-        <v>23</v>
-      </c>
-      <c r="O565" s="6">
-        <v>24</v>
-      </c>
-      <c r="P565" s="6">
+      <c r="B565">
+        <v>1</v>
+      </c>
+      <c r="C565">
+        <v>2</v>
+      </c>
+      <c r="D565">
+        <v>3</v>
+      </c>
+      <c r="E565">
+        <v>5</v>
+      </c>
+      <c r="F565">
+        <v>11</v>
+      </c>
+      <c r="G565">
+        <v>12</v>
+      </c>
+      <c r="H565">
+        <v>14</v>
+      </c>
+      <c r="I565">
+        <v>15</v>
+      </c>
+      <c r="J565">
+        <v>16</v>
+      </c>
+      <c r="K565">
+        <v>19</v>
+      </c>
+      <c r="L565">
+        <v>20</v>
+      </c>
+      <c r="M565">
+        <v>22</v>
+      </c>
+      <c r="N565">
+        <v>23</v>
+      </c>
+      <c r="O565">
+        <v>24</v>
+      </c>
+      <c r="P565">
         <v>25</v>
       </c>
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A566" s="5">
+      <c r="A566">
         <v>3636</v>
       </c>
-      <c r="B566" s="6">
-        <v>1</v>
-      </c>
-      <c r="C566" s="6">
-        <v>2</v>
-      </c>
-      <c r="D566" s="6">
-        <v>3</v>
-      </c>
-      <c r="E566" s="6">
-        <v>4</v>
-      </c>
-      <c r="F566" s="6">
-        <v>5</v>
-      </c>
-      <c r="G566" s="6">
-        <v>6</v>
-      </c>
-      <c r="H566" s="6">
-        <v>12</v>
-      </c>
-      <c r="I566" s="6">
-        <v>13</v>
-      </c>
-      <c r="J566" s="6">
-        <v>15</v>
-      </c>
-      <c r="K566" s="6">
-        <v>16</v>
-      </c>
-      <c r="L566" s="6">
-        <v>17</v>
-      </c>
-      <c r="M566" s="6">
-        <v>18</v>
-      </c>
-      <c r="N566" s="6">
-        <v>22</v>
-      </c>
-      <c r="O566" s="6">
-        <v>24</v>
-      </c>
-      <c r="P566" s="6">
+      <c r="B566">
+        <v>1</v>
+      </c>
+      <c r="C566">
+        <v>2</v>
+      </c>
+      <c r="D566">
+        <v>3</v>
+      </c>
+      <c r="E566">
+        <v>4</v>
+      </c>
+      <c r="F566">
+        <v>5</v>
+      </c>
+      <c r="G566">
+        <v>6</v>
+      </c>
+      <c r="H566">
+        <v>12</v>
+      </c>
+      <c r="I566">
+        <v>13</v>
+      </c>
+      <c r="J566">
+        <v>15</v>
+      </c>
+      <c r="K566">
+        <v>16</v>
+      </c>
+      <c r="L566">
+        <v>17</v>
+      </c>
+      <c r="M566">
+        <v>18</v>
+      </c>
+      <c r="N566">
+        <v>22</v>
+      </c>
+      <c r="O566">
+        <v>24</v>
+      </c>
+      <c r="P566">
         <v>25</v>
       </c>
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A567" s="5">
+      <c r="A567">
         <v>3637</v>
       </c>
-      <c r="B567" s="6">
-        <v>3</v>
-      </c>
-      <c r="C567" s="6">
-        <v>4</v>
-      </c>
-      <c r="D567" s="6">
-        <v>6</v>
-      </c>
-      <c r="E567" s="6">
-        <v>7</v>
-      </c>
-      <c r="F567" s="6">
-        <v>8</v>
-      </c>
-      <c r="G567" s="6">
-        <v>9</v>
-      </c>
-      <c r="H567" s="6">
-        <v>10</v>
-      </c>
-      <c r="I567" s="6">
-        <v>11</v>
-      </c>
-      <c r="J567" s="6">
-        <v>12</v>
-      </c>
-      <c r="K567" s="6">
-        <v>16</v>
-      </c>
-      <c r="L567" s="6">
-        <v>17</v>
-      </c>
-      <c r="M567" s="6">
-        <v>20</v>
-      </c>
-      <c r="N567" s="6">
-        <v>21</v>
-      </c>
-      <c r="O567" s="6">
-        <v>22</v>
-      </c>
-      <c r="P567" s="6">
+      <c r="B567">
+        <v>3</v>
+      </c>
+      <c r="C567">
+        <v>4</v>
+      </c>
+      <c r="D567">
+        <v>6</v>
+      </c>
+      <c r="E567">
+        <v>7</v>
+      </c>
+      <c r="F567">
+        <v>8</v>
+      </c>
+      <c r="G567">
+        <v>9</v>
+      </c>
+      <c r="H567">
+        <v>10</v>
+      </c>
+      <c r="I567">
+        <v>11</v>
+      </c>
+      <c r="J567">
+        <v>12</v>
+      </c>
+      <c r="K567">
+        <v>16</v>
+      </c>
+      <c r="L567">
+        <v>17</v>
+      </c>
+      <c r="M567">
+        <v>20</v>
+      </c>
+      <c r="N567">
+        <v>21</v>
+      </c>
+      <c r="O567">
+        <v>22</v>
+      </c>
+      <c r="P567">
         <v>25</v>
       </c>
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A568" s="5">
+      <c r="A568">
         <v>3638</v>
       </c>
-      <c r="B568" s="6">
-        <v>2</v>
-      </c>
-      <c r="C568" s="6">
-        <v>3</v>
-      </c>
-      <c r="D568" s="6">
-        <v>6</v>
-      </c>
-      <c r="E568" s="6">
-        <v>7</v>
-      </c>
-      <c r="F568" s="6">
-        <v>8</v>
-      </c>
-      <c r="G568" s="6">
-        <v>10</v>
-      </c>
-      <c r="H568" s="6">
-        <v>11</v>
-      </c>
-      <c r="I568" s="6">
-        <v>13</v>
-      </c>
-      <c r="J568" s="6">
-        <v>15</v>
-      </c>
-      <c r="K568" s="6">
-        <v>18</v>
-      </c>
-      <c r="L568" s="6">
-        <v>19</v>
-      </c>
-      <c r="M568" s="6">
-        <v>20</v>
-      </c>
-      <c r="N568" s="6">
-        <v>22</v>
-      </c>
-      <c r="O568" s="6">
-        <v>24</v>
-      </c>
-      <c r="P568" s="6">
+      <c r="B568">
+        <v>2</v>
+      </c>
+      <c r="C568">
+        <v>3</v>
+      </c>
+      <c r="D568">
+        <v>6</v>
+      </c>
+      <c r="E568">
+        <v>7</v>
+      </c>
+      <c r="F568">
+        <v>8</v>
+      </c>
+      <c r="G568">
+        <v>10</v>
+      </c>
+      <c r="H568">
+        <v>11</v>
+      </c>
+      <c r="I568">
+        <v>13</v>
+      </c>
+      <c r="J568">
+        <v>15</v>
+      </c>
+      <c r="K568">
+        <v>18</v>
+      </c>
+      <c r="L568">
+        <v>19</v>
+      </c>
+      <c r="M568">
+        <v>20</v>
+      </c>
+      <c r="N568">
+        <v>22</v>
+      </c>
+      <c r="O568">
+        <v>24</v>
+      </c>
+      <c r="P568">
         <v>25</v>
       </c>
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A569" s="5">
+      <c r="A569">
         <v>3639</v>
       </c>
-      <c r="B569" s="6">
-        <v>1</v>
-      </c>
-      <c r="C569" s="6">
-        <v>3</v>
-      </c>
-      <c r="D569" s="6">
-        <v>4</v>
-      </c>
-      <c r="E569" s="6">
-        <v>5</v>
-      </c>
-      <c r="F569" s="6">
-        <v>6</v>
-      </c>
-      <c r="G569" s="6">
-        <v>7</v>
-      </c>
-      <c r="H569" s="6">
-        <v>9</v>
-      </c>
-      <c r="I569" s="6">
-        <v>10</v>
-      </c>
-      <c r="J569" s="6">
-        <v>11</v>
-      </c>
-      <c r="K569" s="6">
-        <v>12</v>
-      </c>
-      <c r="L569" s="6">
-        <v>13</v>
-      </c>
-      <c r="M569" s="6">
-        <v>15</v>
-      </c>
-      <c r="N569" s="6">
-        <v>18</v>
-      </c>
-      <c r="O569" s="6">
-        <v>23</v>
-      </c>
-      <c r="P569" s="6">
+      <c r="B569">
+        <v>1</v>
+      </c>
+      <c r="C569">
+        <v>3</v>
+      </c>
+      <c r="D569">
+        <v>4</v>
+      </c>
+      <c r="E569">
+        <v>5</v>
+      </c>
+      <c r="F569">
+        <v>6</v>
+      </c>
+      <c r="G569">
+        <v>7</v>
+      </c>
+      <c r="H569">
+        <v>9</v>
+      </c>
+      <c r="I569">
+        <v>10</v>
+      </c>
+      <c r="J569">
+        <v>11</v>
+      </c>
+      <c r="K569">
+        <v>12</v>
+      </c>
+      <c r="L569">
+        <v>13</v>
+      </c>
+      <c r="M569">
+        <v>15</v>
+      </c>
+      <c r="N569">
+        <v>18</v>
+      </c>
+      <c r="O569">
+        <v>23</v>
+      </c>
+      <c r="P569">
         <v>25</v>
       </c>
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A570" s="5">
+      <c r="A570">
         <v>3640</v>
       </c>
-      <c r="B570" s="6">
-        <v>1</v>
-      </c>
-      <c r="C570" s="6">
-        <v>4</v>
-      </c>
-      <c r="D570" s="6">
-        <v>6</v>
-      </c>
-      <c r="E570" s="6">
-        <v>7</v>
-      </c>
-      <c r="F570" s="6">
-        <v>9</v>
-      </c>
-      <c r="G570" s="6">
-        <v>10</v>
-      </c>
-      <c r="H570" s="6">
-        <v>11</v>
-      </c>
-      <c r="I570" s="6">
-        <v>13</v>
-      </c>
-      <c r="J570" s="6">
-        <v>14</v>
-      </c>
-      <c r="K570" s="6">
-        <v>15</v>
-      </c>
-      <c r="L570" s="6">
-        <v>16</v>
-      </c>
-      <c r="M570" s="6">
-        <v>18</v>
-      </c>
-      <c r="N570" s="6">
-        <v>19</v>
-      </c>
-      <c r="O570" s="6">
-        <v>22</v>
-      </c>
-      <c r="P570" s="6">
+      <c r="B570">
+        <v>1</v>
+      </c>
+      <c r="C570">
+        <v>4</v>
+      </c>
+      <c r="D570">
+        <v>6</v>
+      </c>
+      <c r="E570">
+        <v>7</v>
+      </c>
+      <c r="F570">
+        <v>9</v>
+      </c>
+      <c r="G570">
+        <v>10</v>
+      </c>
+      <c r="H570">
+        <v>11</v>
+      </c>
+      <c r="I570">
+        <v>13</v>
+      </c>
+      <c r="J570">
+        <v>14</v>
+      </c>
+      <c r="K570">
+        <v>15</v>
+      </c>
+      <c r="L570">
+        <v>16</v>
+      </c>
+      <c r="M570">
+        <v>18</v>
+      </c>
+      <c r="N570">
+        <v>19</v>
+      </c>
+      <c r="O570">
+        <v>22</v>
+      </c>
+      <c r="P570">
         <v>24</v>
       </c>
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A571" s="5">
+      <c r="A571">
         <v>3641</v>
       </c>
-      <c r="B571" s="6">
-        <v>1</v>
-      </c>
-      <c r="C571" s="6">
-        <v>2</v>
-      </c>
-      <c r="D571" s="6">
-        <v>3</v>
-      </c>
-      <c r="E571" s="6">
-        <v>5</v>
-      </c>
-      <c r="F571" s="6">
-        <v>6</v>
-      </c>
-      <c r="G571" s="6">
-        <v>9</v>
-      </c>
-      <c r="H571" s="6">
-        <v>10</v>
-      </c>
-      <c r="I571" s="6">
-        <v>13</v>
-      </c>
-      <c r="J571" s="6">
-        <v>14</v>
-      </c>
-      <c r="K571" s="6">
-        <v>16</v>
-      </c>
-      <c r="L571" s="6">
-        <v>19</v>
-      </c>
-      <c r="M571" s="6">
-        <v>20</v>
-      </c>
-      <c r="N571" s="6">
-        <v>21</v>
-      </c>
-      <c r="O571" s="6">
-        <v>22</v>
-      </c>
-      <c r="P571" s="6">
+      <c r="B571">
+        <v>1</v>
+      </c>
+      <c r="C571">
+        <v>2</v>
+      </c>
+      <c r="D571">
+        <v>3</v>
+      </c>
+      <c r="E571">
+        <v>5</v>
+      </c>
+      <c r="F571">
+        <v>6</v>
+      </c>
+      <c r="G571">
+        <v>9</v>
+      </c>
+      <c r="H571">
+        <v>10</v>
+      </c>
+      <c r="I571">
+        <v>13</v>
+      </c>
+      <c r="J571">
+        <v>14</v>
+      </c>
+      <c r="K571">
+        <v>16</v>
+      </c>
+      <c r="L571">
+        <v>19</v>
+      </c>
+      <c r="M571">
+        <v>20</v>
+      </c>
+      <c r="N571">
+        <v>21</v>
+      </c>
+      <c r="O571">
+        <v>22</v>
+      </c>
+      <c r="P571">
         <v>25</v>
       </c>
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A572" s="5">
+      <c r="A572">
         <v>3642</v>
       </c>
-      <c r="B572" s="6">
-        <v>1</v>
-      </c>
-      <c r="C572" s="6">
-        <v>2</v>
-      </c>
-      <c r="D572" s="6">
-        <v>4</v>
-      </c>
-      <c r="E572" s="6">
-        <v>5</v>
-      </c>
-      <c r="F572" s="6">
-        <v>6</v>
-      </c>
-      <c r="G572" s="6">
-        <v>7</v>
-      </c>
-      <c r="H572" s="6">
-        <v>9</v>
-      </c>
-      <c r="I572" s="6">
-        <v>10</v>
-      </c>
-      <c r="J572" s="6">
-        <v>12</v>
-      </c>
-      <c r="K572" s="6">
-        <v>13</v>
-      </c>
-      <c r="L572" s="6">
-        <v>14</v>
-      </c>
-      <c r="M572" s="6">
-        <v>18</v>
-      </c>
-      <c r="N572" s="6">
-        <v>20</v>
-      </c>
-      <c r="O572" s="6">
-        <v>23</v>
-      </c>
-      <c r="P572" s="6">
+      <c r="B572">
+        <v>1</v>
+      </c>
+      <c r="C572">
+        <v>2</v>
+      </c>
+      <c r="D572">
+        <v>4</v>
+      </c>
+      <c r="E572">
+        <v>5</v>
+      </c>
+      <c r="F572">
+        <v>6</v>
+      </c>
+      <c r="G572">
+        <v>7</v>
+      </c>
+      <c r="H572">
+        <v>9</v>
+      </c>
+      <c r="I572">
+        <v>10</v>
+      </c>
+      <c r="J572">
+        <v>12</v>
+      </c>
+      <c r="K572">
+        <v>13</v>
+      </c>
+      <c r="L572">
+        <v>14</v>
+      </c>
+      <c r="M572">
+        <v>18</v>
+      </c>
+      <c r="N572">
+        <v>20</v>
+      </c>
+      <c r="O572">
+        <v>23</v>
+      </c>
+      <c r="P572">
         <v>25</v>
       </c>
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A573" s="5">
+      <c r="A573">
         <v>3643</v>
       </c>
-      <c r="B573" s="6">
-        <v>3</v>
-      </c>
-      <c r="C573" s="6">
-        <v>4</v>
-      </c>
-      <c r="D573" s="6">
-        <v>5</v>
-      </c>
-      <c r="E573" s="6">
-        <v>6</v>
-      </c>
-      <c r="F573" s="6">
-        <v>8</v>
-      </c>
-      <c r="G573" s="6">
-        <v>9</v>
-      </c>
-      <c r="H573" s="6">
-        <v>10</v>
-      </c>
-      <c r="I573" s="6">
-        <v>13</v>
-      </c>
-      <c r="J573" s="6">
-        <v>17</v>
-      </c>
-      <c r="K573" s="6">
-        <v>19</v>
-      </c>
-      <c r="L573" s="6">
-        <v>20</v>
-      </c>
-      <c r="M573" s="6">
-        <v>22</v>
-      </c>
-      <c r="N573" s="6">
-        <v>23</v>
-      </c>
-      <c r="O573" s="6">
-        <v>24</v>
-      </c>
-      <c r="P573" s="6">
+      <c r="B573">
+        <v>3</v>
+      </c>
+      <c r="C573">
+        <v>4</v>
+      </c>
+      <c r="D573">
+        <v>5</v>
+      </c>
+      <c r="E573">
+        <v>6</v>
+      </c>
+      <c r="F573">
+        <v>8</v>
+      </c>
+      <c r="G573">
+        <v>9</v>
+      </c>
+      <c r="H573">
+        <v>10</v>
+      </c>
+      <c r="I573">
+        <v>13</v>
+      </c>
+      <c r="J573">
+        <v>17</v>
+      </c>
+      <c r="K573">
+        <v>19</v>
+      </c>
+      <c r="L573">
+        <v>20</v>
+      </c>
+      <c r="M573">
+        <v>22</v>
+      </c>
+      <c r="N573">
+        <v>23</v>
+      </c>
+      <c r="O573">
+        <v>24</v>
+      </c>
+      <c r="P573">
         <v>25</v>
       </c>
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A574" s="5">
+      <c r="A574">
         <v>3644</v>
       </c>
-      <c r="B574" s="6">
-        <v>1</v>
-      </c>
-      <c r="C574" s="6">
-        <v>4</v>
-      </c>
-      <c r="D574" s="6">
-        <v>5</v>
-      </c>
-      <c r="E574" s="6">
-        <v>9</v>
-      </c>
-      <c r="F574" s="6">
-        <v>10</v>
-      </c>
-      <c r="G574" s="6">
-        <v>11</v>
-      </c>
-      <c r="H574" s="6">
-        <v>13</v>
-      </c>
-      <c r="I574" s="6">
-        <v>14</v>
-      </c>
-      <c r="J574" s="6">
-        <v>19</v>
-      </c>
-      <c r="K574" s="6">
-        <v>20</v>
-      </c>
-      <c r="L574" s="6">
-        <v>21</v>
-      </c>
-      <c r="M574" s="6">
-        <v>22</v>
-      </c>
-      <c r="N574" s="6">
-        <v>23</v>
-      </c>
-      <c r="O574" s="6">
-        <v>24</v>
-      </c>
-      <c r="P574" s="6">
+      <c r="B574">
+        <v>1</v>
+      </c>
+      <c r="C574">
+        <v>4</v>
+      </c>
+      <c r="D574">
+        <v>5</v>
+      </c>
+      <c r="E574">
+        <v>9</v>
+      </c>
+      <c r="F574">
+        <v>10</v>
+      </c>
+      <c r="G574">
+        <v>11</v>
+      </c>
+      <c r="H574">
+        <v>13</v>
+      </c>
+      <c r="I574">
+        <v>14</v>
+      </c>
+      <c r="J574">
+        <v>19</v>
+      </c>
+      <c r="K574">
+        <v>20</v>
+      </c>
+      <c r="L574">
+        <v>21</v>
+      </c>
+      <c r="M574">
+        <v>22</v>
+      </c>
+      <c r="N574">
+        <v>23</v>
+      </c>
+      <c r="O574">
+        <v>24</v>
+      </c>
+      <c r="P574">
         <v>25</v>
       </c>
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A575" s="5">
+      <c r="A575">
         <v>3645</v>
       </c>
-      <c r="B575" s="6">
-        <v>1</v>
-      </c>
-      <c r="C575" s="6">
-        <v>3</v>
-      </c>
-      <c r="D575" s="6">
-        <v>6</v>
-      </c>
-      <c r="E575" s="6">
-        <v>7</v>
-      </c>
-      <c r="F575" s="6">
-        <v>8</v>
-      </c>
-      <c r="G575" s="6">
-        <v>9</v>
-      </c>
-      <c r="H575" s="6">
-        <v>10</v>
-      </c>
-      <c r="I575" s="6">
-        <v>12</v>
-      </c>
-      <c r="J575" s="6">
-        <v>13</v>
-      </c>
-      <c r="K575" s="6">
-        <v>15</v>
-      </c>
-      <c r="L575" s="6">
-        <v>17</v>
-      </c>
-      <c r="M575" s="6">
-        <v>18</v>
-      </c>
-      <c r="N575" s="6">
-        <v>19</v>
-      </c>
-      <c r="O575" s="6">
-        <v>21</v>
-      </c>
-      <c r="P575" s="6">
+      <c r="B575">
+        <v>1</v>
+      </c>
+      <c r="C575">
+        <v>3</v>
+      </c>
+      <c r="D575">
+        <v>6</v>
+      </c>
+      <c r="E575">
+        <v>7</v>
+      </c>
+      <c r="F575">
+        <v>8</v>
+      </c>
+      <c r="G575">
+        <v>9</v>
+      </c>
+      <c r="H575">
+        <v>10</v>
+      </c>
+      <c r="I575">
+        <v>12</v>
+      </c>
+      <c r="J575">
+        <v>13</v>
+      </c>
+      <c r="K575">
+        <v>15</v>
+      </c>
+      <c r="L575">
+        <v>17</v>
+      </c>
+      <c r="M575">
+        <v>18</v>
+      </c>
+      <c r="N575">
+        <v>19</v>
+      </c>
+      <c r="O575">
+        <v>21</v>
+      </c>
+      <c r="P575">
         <v>25</v>
       </c>
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A576" s="5">
+      <c r="A576">
         <v>3646</v>
       </c>
-      <c r="B576" s="6">
-        <v>1</v>
-      </c>
-      <c r="C576" s="6">
-        <v>3</v>
-      </c>
-      <c r="D576" s="6">
-        <v>5</v>
-      </c>
-      <c r="E576" s="6">
-        <v>7</v>
-      </c>
-      <c r="F576" s="6">
-        <v>8</v>
-      </c>
-      <c r="G576" s="6">
-        <v>11</v>
-      </c>
-      <c r="H576" s="6">
-        <v>13</v>
-      </c>
-      <c r="I576" s="6">
-        <v>15</v>
-      </c>
-      <c r="J576" s="6">
-        <v>16</v>
-      </c>
-      <c r="K576" s="6">
-        <v>18</v>
-      </c>
-      <c r="L576" s="6">
-        <v>19</v>
-      </c>
-      <c r="M576" s="6">
-        <v>20</v>
-      </c>
-      <c r="N576" s="6">
-        <v>23</v>
-      </c>
-      <c r="O576" s="6">
-        <v>24</v>
-      </c>
-      <c r="P576" s="6">
+      <c r="B576">
+        <v>1</v>
+      </c>
+      <c r="C576">
+        <v>3</v>
+      </c>
+      <c r="D576">
+        <v>5</v>
+      </c>
+      <c r="E576">
+        <v>7</v>
+      </c>
+      <c r="F576">
+        <v>8</v>
+      </c>
+      <c r="G576">
+        <v>11</v>
+      </c>
+      <c r="H576">
+        <v>13</v>
+      </c>
+      <c r="I576">
+        <v>15</v>
+      </c>
+      <c r="J576">
+        <v>16</v>
+      </c>
+      <c r="K576">
+        <v>18</v>
+      </c>
+      <c r="L576">
+        <v>19</v>
+      </c>
+      <c r="M576">
+        <v>20</v>
+      </c>
+      <c r="N576">
+        <v>23</v>
+      </c>
+      <c r="O576">
+        <v>24</v>
+      </c>
+      <c r="P576">
         <v>25</v>
       </c>
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A577" s="5">
+      <c r="A577">
         <v>3647</v>
       </c>
-      <c r="B577" s="6">
-        <v>2</v>
-      </c>
-      <c r="C577" s="6">
-        <v>4</v>
-      </c>
-      <c r="D577" s="6">
-        <v>5</v>
-      </c>
-      <c r="E577" s="6">
-        <v>8</v>
-      </c>
-      <c r="F577" s="6">
-        <v>10</v>
-      </c>
-      <c r="G577" s="6">
-        <v>12</v>
-      </c>
-      <c r="H577" s="6">
-        <v>15</v>
-      </c>
-      <c r="I577" s="6">
-        <v>16</v>
-      </c>
-      <c r="J577" s="6">
-        <v>17</v>
-      </c>
-      <c r="K577" s="6">
-        <v>19</v>
-      </c>
-      <c r="L577" s="6">
-        <v>20</v>
-      </c>
-      <c r="M577" s="6">
-        <v>21</v>
-      </c>
-      <c r="N577" s="6">
-        <v>22</v>
-      </c>
-      <c r="O577" s="6">
-        <v>24</v>
-      </c>
-      <c r="P577" s="6">
+      <c r="B577">
+        <v>2</v>
+      </c>
+      <c r="C577">
+        <v>4</v>
+      </c>
+      <c r="D577">
+        <v>5</v>
+      </c>
+      <c r="E577">
+        <v>8</v>
+      </c>
+      <c r="F577">
+        <v>10</v>
+      </c>
+      <c r="G577">
+        <v>12</v>
+      </c>
+      <c r="H577">
+        <v>15</v>
+      </c>
+      <c r="I577">
+        <v>16</v>
+      </c>
+      <c r="J577">
+        <v>17</v>
+      </c>
+      <c r="K577">
+        <v>19</v>
+      </c>
+      <c r="L577">
+        <v>20</v>
+      </c>
+      <c r="M577">
+        <v>21</v>
+      </c>
+      <c r="N577">
+        <v>22</v>
+      </c>
+      <c r="O577">
+        <v>24</v>
+      </c>
+      <c r="P577">
         <v>25</v>
       </c>
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A578" s="5">
+      <c r="A578">
         <v>3648</v>
       </c>
-      <c r="B578" s="6">
-        <v>1</v>
-      </c>
-      <c r="C578" s="6">
-        <v>2</v>
-      </c>
-      <c r="D578" s="6">
-        <v>5</v>
-      </c>
-      <c r="E578" s="6">
-        <v>7</v>
-      </c>
-      <c r="F578" s="6">
-        <v>8</v>
-      </c>
-      <c r="G578" s="6">
-        <v>9</v>
-      </c>
-      <c r="H578" s="6">
-        <v>10</v>
-      </c>
-      <c r="I578" s="6">
-        <v>11</v>
-      </c>
-      <c r="J578" s="6">
-        <v>13</v>
-      </c>
-      <c r="K578" s="6">
-        <v>14</v>
-      </c>
-      <c r="L578" s="6">
-        <v>15</v>
-      </c>
-      <c r="M578" s="6">
-        <v>18</v>
-      </c>
-      <c r="N578" s="6">
-        <v>19</v>
-      </c>
-      <c r="O578" s="6">
-        <v>20</v>
-      </c>
-      <c r="P578" s="6">
+      <c r="B578">
+        <v>1</v>
+      </c>
+      <c r="C578">
+        <v>2</v>
+      </c>
+      <c r="D578">
+        <v>5</v>
+      </c>
+      <c r="E578">
+        <v>7</v>
+      </c>
+      <c r="F578">
+        <v>8</v>
+      </c>
+      <c r="G578">
+        <v>9</v>
+      </c>
+      <c r="H578">
+        <v>10</v>
+      </c>
+      <c r="I578">
+        <v>11</v>
+      </c>
+      <c r="J578">
+        <v>13</v>
+      </c>
+      <c r="K578">
+        <v>14</v>
+      </c>
+      <c r="L578">
+        <v>15</v>
+      </c>
+      <c r="M578">
+        <v>18</v>
+      </c>
+      <c r="N578">
+        <v>19</v>
+      </c>
+      <c r="O578">
+        <v>20</v>
+      </c>
+      <c r="P578">
         <v>22</v>
       </c>
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A579" s="5">
+      <c r="A579">
         <v>3649</v>
       </c>
-      <c r="B579" s="6">
-        <v>6</v>
-      </c>
-      <c r="C579" s="6">
-        <v>8</v>
-      </c>
-      <c r="D579" s="6">
-        <v>9</v>
-      </c>
-      <c r="E579" s="6">
-        <v>10</v>
-      </c>
-      <c r="F579" s="6">
-        <v>11</v>
-      </c>
-      <c r="G579" s="6">
-        <v>12</v>
-      </c>
-      <c r="H579" s="6">
-        <v>13</v>
-      </c>
-      <c r="I579" s="6">
-        <v>14</v>
-      </c>
-      <c r="J579" s="6">
-        <v>15</v>
-      </c>
-      <c r="K579" s="6">
-        <v>17</v>
-      </c>
-      <c r="L579" s="6">
-        <v>18</v>
-      </c>
-      <c r="M579" s="6">
-        <v>20</v>
-      </c>
-      <c r="N579" s="6">
-        <v>21</v>
-      </c>
-      <c r="O579" s="6">
-        <v>24</v>
-      </c>
-      <c r="P579" s="6">
+      <c r="B579">
+        <v>6</v>
+      </c>
+      <c r="C579">
+        <v>8</v>
+      </c>
+      <c r="D579">
+        <v>9</v>
+      </c>
+      <c r="E579">
+        <v>10</v>
+      </c>
+      <c r="F579">
+        <v>11</v>
+      </c>
+      <c r="G579">
+        <v>12</v>
+      </c>
+      <c r="H579">
+        <v>13</v>
+      </c>
+      <c r="I579">
+        <v>14</v>
+      </c>
+      <c r="J579">
+        <v>15</v>
+      </c>
+      <c r="K579">
+        <v>17</v>
+      </c>
+      <c r="L579">
+        <v>18</v>
+      </c>
+      <c r="M579">
+        <v>20</v>
+      </c>
+      <c r="N579">
+        <v>21</v>
+      </c>
+      <c r="O579">
+        <v>24</v>
+      </c>
+      <c r="P579">
         <v>25</v>
       </c>
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A580" s="5">
+      <c r="A580">
         <v>3650</v>
       </c>
-      <c r="B580" s="6">
-        <v>2</v>
-      </c>
-      <c r="C580" s="6">
-        <v>5</v>
-      </c>
-      <c r="D580" s="6">
-        <v>6</v>
-      </c>
-      <c r="E580" s="6">
-        <v>7</v>
-      </c>
-      <c r="F580" s="6">
-        <v>8</v>
-      </c>
-      <c r="G580" s="6">
-        <v>10</v>
-      </c>
-      <c r="H580" s="6">
-        <v>11</v>
-      </c>
-      <c r="I580" s="6">
-        <v>12</v>
-      </c>
-      <c r="J580" s="6">
-        <v>13</v>
-      </c>
-      <c r="K580" s="6">
-        <v>16</v>
-      </c>
-      <c r="L580" s="6">
-        <v>17</v>
-      </c>
-      <c r="M580" s="6">
-        <v>20</v>
-      </c>
-      <c r="N580" s="6">
-        <v>21</v>
-      </c>
-      <c r="O580" s="6">
-        <v>22</v>
-      </c>
-      <c r="P580" s="6">
+      <c r="B580">
+        <v>2</v>
+      </c>
+      <c r="C580">
+        <v>5</v>
+      </c>
+      <c r="D580">
+        <v>6</v>
+      </c>
+      <c r="E580">
+        <v>7</v>
+      </c>
+      <c r="F580">
+        <v>8</v>
+      </c>
+      <c r="G580">
+        <v>10</v>
+      </c>
+      <c r="H580">
+        <v>11</v>
+      </c>
+      <c r="I580">
+        <v>12</v>
+      </c>
+      <c r="J580">
+        <v>13</v>
+      </c>
+      <c r="K580">
+        <v>16</v>
+      </c>
+      <c r="L580">
+        <v>17</v>
+      </c>
+      <c r="M580">
+        <v>20</v>
+      </c>
+      <c r="N580">
+        <v>21</v>
+      </c>
+      <c r="O580">
+        <v>22</v>
+      </c>
+      <c r="P580">
         <v>25</v>
       </c>
     </row>
     <row r="581" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A581" s="5">
+      <c r="A581">
         <v>3651</v>
       </c>
-      <c r="B581" s="6">
-        <v>2</v>
-      </c>
-      <c r="C581" s="6">
-        <v>3</v>
-      </c>
-      <c r="D581" s="6">
-        <v>5</v>
-      </c>
-      <c r="E581" s="6">
-        <v>8</v>
-      </c>
-      <c r="F581" s="6">
-        <v>10</v>
-      </c>
-      <c r="G581" s="6">
-        <v>12</v>
-      </c>
-      <c r="H581" s="6">
-        <v>13</v>
-      </c>
-      <c r="I581" s="6">
-        <v>14</v>
-      </c>
-      <c r="J581" s="6">
-        <v>16</v>
-      </c>
-      <c r="K581" s="6">
-        <v>17</v>
-      </c>
-      <c r="L581" s="6">
-        <v>18</v>
-      </c>
-      <c r="M581" s="6">
-        <v>20</v>
-      </c>
-      <c r="N581" s="6">
-        <v>21</v>
-      </c>
-      <c r="O581" s="6">
-        <v>24</v>
-      </c>
-      <c r="P581" s="6">
+      <c r="B581">
+        <v>2</v>
+      </c>
+      <c r="C581">
+        <v>3</v>
+      </c>
+      <c r="D581">
+        <v>5</v>
+      </c>
+      <c r="E581">
+        <v>8</v>
+      </c>
+      <c r="F581">
+        <v>10</v>
+      </c>
+      <c r="G581">
+        <v>12</v>
+      </c>
+      <c r="H581">
+        <v>13</v>
+      </c>
+      <c r="I581">
+        <v>14</v>
+      </c>
+      <c r="J581">
+        <v>16</v>
+      </c>
+      <c r="K581">
+        <v>17</v>
+      </c>
+      <c r="L581">
+        <v>18</v>
+      </c>
+      <c r="M581">
+        <v>20</v>
+      </c>
+      <c r="N581">
+        <v>21</v>
+      </c>
+      <c r="O581">
+        <v>24</v>
+      </c>
+      <c r="P581">
         <v>25</v>
       </c>
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A582" s="5">
+      <c r="A582">
         <v>3652</v>
       </c>
-      <c r="B582" s="6">
-        <v>1</v>
-      </c>
-      <c r="C582" s="6">
-        <v>3</v>
-      </c>
-      <c r="D582" s="6">
-        <v>6</v>
-      </c>
-      <c r="E582" s="6">
-        <v>7</v>
-      </c>
-      <c r="F582" s="6">
-        <v>11</v>
-      </c>
-      <c r="G582" s="6">
-        <v>12</v>
-      </c>
-      <c r="H582" s="6">
-        <v>13</v>
-      </c>
-      <c r="I582" s="6">
-        <v>15</v>
-      </c>
-      <c r="J582" s="6">
-        <v>16</v>
-      </c>
-      <c r="K582" s="6">
-        <v>18</v>
-      </c>
-      <c r="L582" s="6">
-        <v>19</v>
-      </c>
-      <c r="M582" s="6">
-        <v>20</v>
-      </c>
-      <c r="N582" s="6">
-        <v>21</v>
-      </c>
-      <c r="O582" s="6">
-        <v>23</v>
-      </c>
-      <c r="P582" s="6">
+      <c r="B582">
+        <v>1</v>
+      </c>
+      <c r="C582">
+        <v>3</v>
+      </c>
+      <c r="D582">
+        <v>6</v>
+      </c>
+      <c r="E582">
+        <v>7</v>
+      </c>
+      <c r="F582">
+        <v>11</v>
+      </c>
+      <c r="G582">
+        <v>12</v>
+      </c>
+      <c r="H582">
+        <v>13</v>
+      </c>
+      <c r="I582">
+        <v>15</v>
+      </c>
+      <c r="J582">
+        <v>16</v>
+      </c>
+      <c r="K582">
+        <v>18</v>
+      </c>
+      <c r="L582">
+        <v>19</v>
+      </c>
+      <c r="M582">
+        <v>20</v>
+      </c>
+      <c r="N582">
+        <v>21</v>
+      </c>
+      <c r="O582">
+        <v>23</v>
+      </c>
+      <c r="P582">
         <v>24</v>
       </c>
     </row>
     <row r="583" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A583" s="5">
+      <c r="A583">
         <v>3653</v>
       </c>
-      <c r="B583" s="6">
-        <v>2</v>
-      </c>
-      <c r="C583" s="6">
-        <v>3</v>
-      </c>
-      <c r="D583" s="6">
-        <v>4</v>
-      </c>
-      <c r="E583" s="6">
-        <v>6</v>
-      </c>
-      <c r="F583" s="6">
-        <v>7</v>
-      </c>
-      <c r="G583" s="6">
-        <v>8</v>
-      </c>
-      <c r="H583" s="6">
-        <v>10</v>
-      </c>
-      <c r="I583" s="6">
-        <v>11</v>
-      </c>
-      <c r="J583" s="6">
-        <v>13</v>
-      </c>
-      <c r="K583" s="6">
-        <v>14</v>
-      </c>
-      <c r="L583" s="6">
-        <v>16</v>
-      </c>
-      <c r="M583" s="6">
-        <v>18</v>
-      </c>
-      <c r="N583" s="6">
-        <v>19</v>
-      </c>
-      <c r="O583" s="6">
-        <v>20</v>
-      </c>
-      <c r="P583" s="6">
-        <v>21</v>
+      <c r="B583">
+        <v>2</v>
+      </c>
+      <c r="C583">
+        <v>3</v>
+      </c>
+      <c r="D583">
+        <v>4</v>
+      </c>
+      <c r="E583">
+        <v>6</v>
+      </c>
+      <c r="F583">
+        <v>7</v>
+      </c>
+      <c r="G583">
+        <v>8</v>
+      </c>
+      <c r="H583">
+        <v>10</v>
+      </c>
+      <c r="I583">
+        <v>11</v>
+      </c>
+      <c r="J583">
+        <v>13</v>
+      </c>
+      <c r="K583">
+        <v>14</v>
+      </c>
+      <c r="L583">
+        <v>16</v>
+      </c>
+      <c r="M583">
+        <v>18</v>
+      </c>
+      <c r="N583">
+        <v>19</v>
+      </c>
+      <c r="O583">
+        <v>20</v>
+      </c>
+      <c r="P583">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="584" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A584" s="5">
+        <v>3654</v>
+      </c>
+      <c r="B584" s="6">
+        <v>1</v>
+      </c>
+      <c r="C584" s="6">
+        <v>2</v>
+      </c>
+      <c r="D584" s="6">
+        <v>3</v>
+      </c>
+      <c r="E584" s="6">
+        <v>4</v>
+      </c>
+      <c r="F584" s="6">
+        <v>6</v>
+      </c>
+      <c r="G584" s="6">
+        <v>7</v>
+      </c>
+      <c r="H584" s="6">
+        <v>11</v>
+      </c>
+      <c r="I584" s="6">
+        <v>15</v>
+      </c>
+      <c r="J584" s="6">
+        <v>17</v>
+      </c>
+      <c r="K584" s="6">
+        <v>19</v>
+      </c>
+      <c r="L584" s="6">
+        <v>20</v>
+      </c>
+      <c r="M584" s="6">
+        <v>22</v>
+      </c>
+      <c r="N584" s="6">
+        <v>23</v>
+      </c>
+      <c r="O584" s="6">
+        <v>24</v>
+      </c>
+      <c r="P584" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="585" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A585" s="5">
+        <v>3655</v>
+      </c>
+      <c r="B585" s="6">
+        <v>1</v>
+      </c>
+      <c r="C585" s="6">
+        <v>2</v>
+      </c>
+      <c r="D585" s="6">
+        <v>4</v>
+      </c>
+      <c r="E585" s="6">
+        <v>5</v>
+      </c>
+      <c r="F585" s="6">
+        <v>6</v>
+      </c>
+      <c r="G585" s="6">
+        <v>10</v>
+      </c>
+      <c r="H585" s="6">
+        <v>11</v>
+      </c>
+      <c r="I585" s="6">
+        <v>12</v>
+      </c>
+      <c r="J585" s="6">
+        <v>17</v>
+      </c>
+      <c r="K585" s="6">
+        <v>18</v>
+      </c>
+      <c r="L585" s="6">
+        <v>19</v>
+      </c>
+      <c r="M585" s="6">
+        <v>21</v>
+      </c>
+      <c r="N585" s="6">
+        <v>22</v>
+      </c>
+      <c r="O585" s="6">
+        <v>23</v>
+      </c>
+      <c r="P585" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="586" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A586" s="5">
+        <v>3656</v>
+      </c>
+      <c r="B586" s="6">
+        <v>3</v>
+      </c>
+      <c r="C586" s="6">
+        <v>4</v>
+      </c>
+      <c r="D586" s="6">
+        <v>6</v>
+      </c>
+      <c r="E586" s="6">
+        <v>7</v>
+      </c>
+      <c r="F586" s="6">
+        <v>8</v>
+      </c>
+      <c r="G586" s="6">
+        <v>11</v>
+      </c>
+      <c r="H586" s="6">
+        <v>12</v>
+      </c>
+      <c r="I586" s="6">
+        <v>14</v>
+      </c>
+      <c r="J586" s="6">
+        <v>15</v>
+      </c>
+      <c r="K586" s="6">
+        <v>18</v>
+      </c>
+      <c r="L586" s="6">
+        <v>19</v>
+      </c>
+      <c r="M586" s="6">
+        <v>20</v>
+      </c>
+      <c r="N586" s="6">
+        <v>21</v>
+      </c>
+      <c r="O586" s="6">
+        <v>24</v>
+      </c>
+      <c r="P586" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="587" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A587" s="5">
+        <v>3657</v>
+      </c>
+      <c r="B587" s="6">
+        <v>1</v>
+      </c>
+      <c r="C587" s="6">
+        <v>2</v>
+      </c>
+      <c r="D587" s="6">
+        <v>4</v>
+      </c>
+      <c r="E587" s="6">
+        <v>7</v>
+      </c>
+      <c r="F587" s="6">
+        <v>8</v>
+      </c>
+      <c r="G587" s="6">
+        <v>10</v>
+      </c>
+      <c r="H587" s="6">
+        <v>12</v>
+      </c>
+      <c r="I587" s="6">
+        <v>13</v>
+      </c>
+      <c r="J587" s="6">
+        <v>17</v>
+      </c>
+      <c r="K587" s="6">
+        <v>18</v>
+      </c>
+      <c r="L587" s="6">
+        <v>19</v>
+      </c>
+      <c r="M587" s="6">
+        <v>20</v>
+      </c>
+      <c r="N587" s="6">
+        <v>22</v>
+      </c>
+      <c r="O587" s="6">
+        <v>23</v>
+      </c>
+      <c r="P587" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="588" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A588" s="5">
+        <v>3658</v>
+      </c>
+      <c r="B588" s="6">
+        <v>2</v>
+      </c>
+      <c r="C588" s="6">
+        <v>3</v>
+      </c>
+      <c r="D588" s="6">
+        <v>4</v>
+      </c>
+      <c r="E588" s="6">
+        <v>5</v>
+      </c>
+      <c r="F588" s="6">
+        <v>9</v>
+      </c>
+      <c r="G588" s="6">
+        <v>10</v>
+      </c>
+      <c r="H588" s="6">
+        <v>11</v>
+      </c>
+      <c r="I588" s="6">
+        <v>12</v>
+      </c>
+      <c r="J588" s="6">
+        <v>13</v>
+      </c>
+      <c r="K588" s="6">
+        <v>16</v>
+      </c>
+      <c r="L588" s="6">
+        <v>18</v>
+      </c>
+      <c r="M588" s="6">
+        <v>20</v>
+      </c>
+      <c r="N588" s="6">
+        <v>22</v>
+      </c>
+      <c r="O588" s="6">
+        <v>23</v>
+      </c>
+      <c r="P588" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="589" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A589" s="5">
+        <v>3659</v>
+      </c>
+      <c r="B589" s="6">
+        <v>3</v>
+      </c>
+      <c r="C589" s="6">
+        <v>5</v>
+      </c>
+      <c r="D589" s="6">
+        <v>6</v>
+      </c>
+      <c r="E589" s="6">
+        <v>7</v>
+      </c>
+      <c r="F589" s="6">
+        <v>8</v>
+      </c>
+      <c r="G589" s="6">
+        <v>9</v>
+      </c>
+      <c r="H589" s="6">
+        <v>10</v>
+      </c>
+      <c r="I589" s="6">
+        <v>11</v>
+      </c>
+      <c r="J589" s="6">
+        <v>13</v>
+      </c>
+      <c r="K589" s="6">
+        <v>14</v>
+      </c>
+      <c r="L589" s="6">
+        <v>15</v>
+      </c>
+      <c r="M589" s="6">
+        <v>16</v>
+      </c>
+      <c r="N589" s="6">
+        <v>17</v>
+      </c>
+      <c r="O589" s="6">
+        <v>23</v>
+      </c>
+      <c r="P589" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="590" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A590" s="5">
+        <v>3660</v>
+      </c>
+      <c r="B590" s="6">
+        <v>1</v>
+      </c>
+      <c r="C590" s="6">
+        <v>2</v>
+      </c>
+      <c r="D590" s="6">
+        <v>5</v>
+      </c>
+      <c r="E590" s="6">
+        <v>6</v>
+      </c>
+      <c r="F590" s="6">
+        <v>7</v>
+      </c>
+      <c r="G590" s="6">
+        <v>8</v>
+      </c>
+      <c r="H590" s="6">
+        <v>10</v>
+      </c>
+      <c r="I590" s="6">
+        <v>11</v>
+      </c>
+      <c r="J590" s="6">
+        <v>12</v>
+      </c>
+      <c r="K590" s="6">
+        <v>14</v>
+      </c>
+      <c r="L590" s="6">
+        <v>17</v>
+      </c>
+      <c r="M590" s="6">
+        <v>18</v>
+      </c>
+      <c r="N590" s="6">
+        <v>22</v>
+      </c>
+      <c r="O590" s="6">
+        <v>23</v>
+      </c>
+      <c r="P590" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="591" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A591" s="5">
+        <v>3661</v>
+      </c>
+      <c r="B591" s="6">
+        <v>2</v>
+      </c>
+      <c r="C591" s="6">
+        <v>3</v>
+      </c>
+      <c r="D591" s="6">
+        <v>4</v>
+      </c>
+      <c r="E591" s="6">
+        <v>5</v>
+      </c>
+      <c r="F591" s="6">
+        <v>6</v>
+      </c>
+      <c r="G591" s="6">
+        <v>7</v>
+      </c>
+      <c r="H591" s="6">
+        <v>8</v>
+      </c>
+      <c r="I591" s="6">
+        <v>10</v>
+      </c>
+      <c r="J591" s="6">
+        <v>12</v>
+      </c>
+      <c r="K591" s="6">
+        <v>14</v>
+      </c>
+      <c r="L591" s="6">
+        <v>15</v>
+      </c>
+      <c r="M591" s="6">
+        <v>19</v>
+      </c>
+      <c r="N591" s="6">
+        <v>21</v>
+      </c>
+      <c r="O591" s="6">
+        <v>23</v>
+      </c>
+      <c r="P591" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="592" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A592" s="5">
+        <v>3662</v>
+      </c>
+      <c r="B592" s="6">
+        <v>4</v>
+      </c>
+      <c r="C592" s="6">
+        <v>5</v>
+      </c>
+      <c r="D592" s="6">
+        <v>6</v>
+      </c>
+      <c r="E592" s="6">
+        <v>7</v>
+      </c>
+      <c r="F592" s="6">
+        <v>8</v>
+      </c>
+      <c r="G592" s="6">
+        <v>9</v>
+      </c>
+      <c r="H592" s="6">
+        <v>10</v>
+      </c>
+      <c r="I592" s="6">
+        <v>11</v>
+      </c>
+      <c r="J592" s="6">
+        <v>12</v>
+      </c>
+      <c r="K592" s="6">
+        <v>13</v>
+      </c>
+      <c r="L592" s="6">
+        <v>15</v>
+      </c>
+      <c r="M592" s="6">
+        <v>18</v>
+      </c>
+      <c r="N592" s="6">
+        <v>20</v>
+      </c>
+      <c r="O592" s="6">
+        <v>23</v>
+      </c>
+      <c r="P592" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="593" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A593" s="5">
+        <v>3663</v>
+      </c>
+      <c r="B593" s="6">
+        <v>1</v>
+      </c>
+      <c r="C593" s="6">
+        <v>3</v>
+      </c>
+      <c r="D593" s="6">
+        <v>4</v>
+      </c>
+      <c r="E593" s="6">
+        <v>5</v>
+      </c>
+      <c r="F593" s="6">
+        <v>6</v>
+      </c>
+      <c r="G593" s="6">
+        <v>10</v>
+      </c>
+      <c r="H593" s="6">
+        <v>12</v>
+      </c>
+      <c r="I593" s="6">
+        <v>14</v>
+      </c>
+      <c r="J593" s="6">
+        <v>17</v>
+      </c>
+      <c r="K593" s="6">
+        <v>19</v>
+      </c>
+      <c r="L593" s="6">
+        <v>20</v>
+      </c>
+      <c r="M593" s="6">
+        <v>22</v>
+      </c>
+      <c r="N593" s="6">
+        <v>23</v>
+      </c>
+      <c r="O593" s="6">
+        <v>24</v>
+      </c>
+      <c r="P593" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="594" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A594" s="5">
+        <v>3664</v>
+      </c>
+      <c r="B594" s="6">
+        <v>1</v>
+      </c>
+      <c r="C594" s="6">
+        <v>2</v>
+      </c>
+      <c r="D594" s="6">
+        <v>4</v>
+      </c>
+      <c r="E594" s="6">
+        <v>5</v>
+      </c>
+      <c r="F594" s="6">
+        <v>6</v>
+      </c>
+      <c r="G594" s="6">
+        <v>7</v>
+      </c>
+      <c r="H594" s="6">
+        <v>10</v>
+      </c>
+      <c r="I594" s="6">
+        <v>11</v>
+      </c>
+      <c r="J594" s="6">
+        <v>12</v>
+      </c>
+      <c r="K594" s="6">
+        <v>16</v>
+      </c>
+      <c r="L594" s="6">
+        <v>18</v>
+      </c>
+      <c r="M594" s="6">
+        <v>19</v>
+      </c>
+      <c r="N594" s="6">
+        <v>20</v>
+      </c>
+      <c r="O594" s="6">
+        <v>22</v>
+      </c>
+      <c r="P594" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="595" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A595" s="5">
+        <v>3665</v>
+      </c>
+      <c r="B595" s="6">
+        <v>1</v>
+      </c>
+      <c r="C595" s="6">
+        <v>2</v>
+      </c>
+      <c r="D595" s="6">
+        <v>3</v>
+      </c>
+      <c r="E595" s="6">
+        <v>5</v>
+      </c>
+      <c r="F595" s="6">
+        <v>6</v>
+      </c>
+      <c r="G595" s="6">
+        <v>7</v>
+      </c>
+      <c r="H595" s="6">
+        <v>9</v>
+      </c>
+      <c r="I595" s="6">
+        <v>10</v>
+      </c>
+      <c r="J595" s="6">
+        <v>11</v>
+      </c>
+      <c r="K595" s="6">
+        <v>13</v>
+      </c>
+      <c r="L595" s="6">
+        <v>16</v>
+      </c>
+      <c r="M595" s="6">
+        <v>18</v>
+      </c>
+      <c r="N595" s="6">
+        <v>22</v>
+      </c>
+      <c r="O595" s="6">
+        <v>23</v>
+      </c>
+      <c r="P595" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="596" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A596" s="5">
+        <v>3666</v>
+      </c>
+      <c r="B596" s="6">
+        <v>1</v>
+      </c>
+      <c r="C596" s="6">
+        <v>4</v>
+      </c>
+      <c r="D596" s="6">
+        <v>6</v>
+      </c>
+      <c r="E596" s="6">
+        <v>7</v>
+      </c>
+      <c r="F596" s="6">
+        <v>9</v>
+      </c>
+      <c r="G596" s="6">
+        <v>12</v>
+      </c>
+      <c r="H596" s="6">
+        <v>14</v>
+      </c>
+      <c r="I596" s="6">
+        <v>15</v>
+      </c>
+      <c r="J596" s="6">
+        <v>16</v>
+      </c>
+      <c r="K596" s="6">
+        <v>17</v>
+      </c>
+      <c r="L596" s="6">
+        <v>19</v>
+      </c>
+      <c r="M596" s="6">
+        <v>20</v>
+      </c>
+      <c r="N596" s="6">
+        <v>21</v>
+      </c>
+      <c r="O596" s="6">
+        <v>22</v>
+      </c>
+      <c r="P596" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="597" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A597" s="5">
+        <v>3667</v>
+      </c>
+      <c r="B597" s="6">
+        <v>1</v>
+      </c>
+      <c r="C597" s="6">
+        <v>3</v>
+      </c>
+      <c r="D597" s="6">
+        <v>4</v>
+      </c>
+      <c r="E597" s="6">
+        <v>5</v>
+      </c>
+      <c r="F597" s="6">
+        <v>6</v>
+      </c>
+      <c r="G597" s="6">
+        <v>7</v>
+      </c>
+      <c r="H597" s="6">
+        <v>9</v>
+      </c>
+      <c r="I597" s="6">
+        <v>11</v>
+      </c>
+      <c r="J597" s="6">
+        <v>14</v>
+      </c>
+      <c r="K597" s="6">
+        <v>15</v>
+      </c>
+      <c r="L597" s="6">
+        <v>19</v>
+      </c>
+      <c r="M597" s="6">
+        <v>21</v>
+      </c>
+      <c r="N597" s="6">
+        <v>22</v>
+      </c>
+      <c r="O597" s="6">
+        <v>23</v>
+      </c>
+      <c r="P597" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="598" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A598" s="5">
+        <v>3668</v>
+      </c>
+      <c r="B598" s="6">
+        <v>1</v>
+      </c>
+      <c r="C598" s="6">
+        <v>2</v>
+      </c>
+      <c r="D598" s="6">
+        <v>3</v>
+      </c>
+      <c r="E598" s="6">
+        <v>5</v>
+      </c>
+      <c r="F598" s="6">
+        <v>7</v>
+      </c>
+      <c r="G598" s="6">
+        <v>8</v>
+      </c>
+      <c r="H598" s="6">
+        <v>9</v>
+      </c>
+      <c r="I598" s="6">
+        <v>10</v>
+      </c>
+      <c r="J598" s="6">
+        <v>11</v>
+      </c>
+      <c r="K598" s="6">
+        <v>13</v>
+      </c>
+      <c r="L598" s="6">
+        <v>15</v>
+      </c>
+      <c r="M598" s="6">
+        <v>17</v>
+      </c>
+      <c r="N598" s="6">
+        <v>18</v>
+      </c>
+      <c r="O598" s="6">
+        <v>21</v>
+      </c>
+      <c r="P598" s="6">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -29643,6 +30393,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -29810,15 +30569,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -29830,6 +30580,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -29849,14 +30607,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDCB27B-F5B4-4F66-B6A9-76A06A00045C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7464987B-B19E-4B52-8FFC-5A7A27FD9842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57585" yWindow="1395" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,8 +156,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P598"/>
+  <dimension ref="A1:P600"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -29638,752 +29636,852 @@
       </c>
     </row>
     <row r="584" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A584" s="5">
+      <c r="A584">
         <v>3654</v>
       </c>
-      <c r="B584" s="6">
-        <v>1</v>
-      </c>
-      <c r="C584" s="6">
-        <v>2</v>
-      </c>
-      <c r="D584" s="6">
-        <v>3</v>
-      </c>
-      <c r="E584" s="6">
-        <v>4</v>
-      </c>
-      <c r="F584" s="6">
-        <v>6</v>
-      </c>
-      <c r="G584" s="6">
-        <v>7</v>
-      </c>
-      <c r="H584" s="6">
-        <v>11</v>
-      </c>
-      <c r="I584" s="6">
-        <v>15</v>
-      </c>
-      <c r="J584" s="6">
-        <v>17</v>
-      </c>
-      <c r="K584" s="6">
-        <v>19</v>
-      </c>
-      <c r="L584" s="6">
-        <v>20</v>
-      </c>
-      <c r="M584" s="6">
-        <v>22</v>
-      </c>
-      <c r="N584" s="6">
-        <v>23</v>
-      </c>
-      <c r="O584" s="6">
-        <v>24</v>
-      </c>
-      <c r="P584" s="6">
+      <c r="B584">
+        <v>1</v>
+      </c>
+      <c r="C584">
+        <v>2</v>
+      </c>
+      <c r="D584">
+        <v>3</v>
+      </c>
+      <c r="E584">
+        <v>4</v>
+      </c>
+      <c r="F584">
+        <v>6</v>
+      </c>
+      <c r="G584">
+        <v>7</v>
+      </c>
+      <c r="H584">
+        <v>11</v>
+      </c>
+      <c r="I584">
+        <v>15</v>
+      </c>
+      <c r="J584">
+        <v>17</v>
+      </c>
+      <c r="K584">
+        <v>19</v>
+      </c>
+      <c r="L584">
+        <v>20</v>
+      </c>
+      <c r="M584">
+        <v>22</v>
+      </c>
+      <c r="N584">
+        <v>23</v>
+      </c>
+      <c r="O584">
+        <v>24</v>
+      </c>
+      <c r="P584">
         <v>25</v>
       </c>
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A585" s="5">
+      <c r="A585">
         <v>3655</v>
       </c>
-      <c r="B585" s="6">
-        <v>1</v>
-      </c>
-      <c r="C585" s="6">
-        <v>2</v>
-      </c>
-      <c r="D585" s="6">
-        <v>4</v>
-      </c>
-      <c r="E585" s="6">
-        <v>5</v>
-      </c>
-      <c r="F585" s="6">
-        <v>6</v>
-      </c>
-      <c r="G585" s="6">
-        <v>10</v>
-      </c>
-      <c r="H585" s="6">
-        <v>11</v>
-      </c>
-      <c r="I585" s="6">
-        <v>12</v>
-      </c>
-      <c r="J585" s="6">
-        <v>17</v>
-      </c>
-      <c r="K585" s="6">
-        <v>18</v>
-      </c>
-      <c r="L585" s="6">
-        <v>19</v>
-      </c>
-      <c r="M585" s="6">
-        <v>21</v>
-      </c>
-      <c r="N585" s="6">
-        <v>22</v>
-      </c>
-      <c r="O585" s="6">
-        <v>23</v>
-      </c>
-      <c r="P585" s="6">
+      <c r="B585">
+        <v>1</v>
+      </c>
+      <c r="C585">
+        <v>2</v>
+      </c>
+      <c r="D585">
+        <v>4</v>
+      </c>
+      <c r="E585">
+        <v>5</v>
+      </c>
+      <c r="F585">
+        <v>6</v>
+      </c>
+      <c r="G585">
+        <v>10</v>
+      </c>
+      <c r="H585">
+        <v>11</v>
+      </c>
+      <c r="I585">
+        <v>12</v>
+      </c>
+      <c r="J585">
+        <v>17</v>
+      </c>
+      <c r="K585">
+        <v>18</v>
+      </c>
+      <c r="L585">
+        <v>19</v>
+      </c>
+      <c r="M585">
+        <v>21</v>
+      </c>
+      <c r="N585">
+        <v>22</v>
+      </c>
+      <c r="O585">
+        <v>23</v>
+      </c>
+      <c r="P585">
         <v>24</v>
       </c>
     </row>
     <row r="586" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A586" s="5">
+      <c r="A586">
         <v>3656</v>
       </c>
-      <c r="B586" s="6">
-        <v>3</v>
-      </c>
-      <c r="C586" s="6">
-        <v>4</v>
-      </c>
-      <c r="D586" s="6">
-        <v>6</v>
-      </c>
-      <c r="E586" s="6">
-        <v>7</v>
-      </c>
-      <c r="F586" s="6">
-        <v>8</v>
-      </c>
-      <c r="G586" s="6">
-        <v>11</v>
-      </c>
-      <c r="H586" s="6">
-        <v>12</v>
-      </c>
-      <c r="I586" s="6">
-        <v>14</v>
-      </c>
-      <c r="J586" s="6">
-        <v>15</v>
-      </c>
-      <c r="K586" s="6">
-        <v>18</v>
-      </c>
-      <c r="L586" s="6">
-        <v>19</v>
-      </c>
-      <c r="M586" s="6">
-        <v>20</v>
-      </c>
-      <c r="N586" s="6">
-        <v>21</v>
-      </c>
-      <c r="O586" s="6">
-        <v>24</v>
-      </c>
-      <c r="P586" s="6">
+      <c r="B586">
+        <v>3</v>
+      </c>
+      <c r="C586">
+        <v>4</v>
+      </c>
+      <c r="D586">
+        <v>6</v>
+      </c>
+      <c r="E586">
+        <v>7</v>
+      </c>
+      <c r="F586">
+        <v>8</v>
+      </c>
+      <c r="G586">
+        <v>11</v>
+      </c>
+      <c r="H586">
+        <v>12</v>
+      </c>
+      <c r="I586">
+        <v>14</v>
+      </c>
+      <c r="J586">
+        <v>15</v>
+      </c>
+      <c r="K586">
+        <v>18</v>
+      </c>
+      <c r="L586">
+        <v>19</v>
+      </c>
+      <c r="M586">
+        <v>20</v>
+      </c>
+      <c r="N586">
+        <v>21</v>
+      </c>
+      <c r="O586">
+        <v>24</v>
+      </c>
+      <c r="P586">
         <v>25</v>
       </c>
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A587" s="5">
+      <c r="A587">
         <v>3657</v>
       </c>
-      <c r="B587" s="6">
-        <v>1</v>
-      </c>
-      <c r="C587" s="6">
-        <v>2</v>
-      </c>
-      <c r="D587" s="6">
-        <v>4</v>
-      </c>
-      <c r="E587" s="6">
-        <v>7</v>
-      </c>
-      <c r="F587" s="6">
-        <v>8</v>
-      </c>
-      <c r="G587" s="6">
-        <v>10</v>
-      </c>
-      <c r="H587" s="6">
-        <v>12</v>
-      </c>
-      <c r="I587" s="6">
-        <v>13</v>
-      </c>
-      <c r="J587" s="6">
-        <v>17</v>
-      </c>
-      <c r="K587" s="6">
-        <v>18</v>
-      </c>
-      <c r="L587" s="6">
-        <v>19</v>
-      </c>
-      <c r="M587" s="6">
-        <v>20</v>
-      </c>
-      <c r="N587" s="6">
-        <v>22</v>
-      </c>
-      <c r="O587" s="6">
-        <v>23</v>
-      </c>
-      <c r="P587" s="6">
+      <c r="B587">
+        <v>1</v>
+      </c>
+      <c r="C587">
+        <v>2</v>
+      </c>
+      <c r="D587">
+        <v>4</v>
+      </c>
+      <c r="E587">
+        <v>7</v>
+      </c>
+      <c r="F587">
+        <v>8</v>
+      </c>
+      <c r="G587">
+        <v>10</v>
+      </c>
+      <c r="H587">
+        <v>12</v>
+      </c>
+      <c r="I587">
+        <v>13</v>
+      </c>
+      <c r="J587">
+        <v>17</v>
+      </c>
+      <c r="K587">
+        <v>18</v>
+      </c>
+      <c r="L587">
+        <v>19</v>
+      </c>
+      <c r="M587">
+        <v>20</v>
+      </c>
+      <c r="N587">
+        <v>22</v>
+      </c>
+      <c r="O587">
+        <v>23</v>
+      </c>
+      <c r="P587">
         <v>24</v>
       </c>
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A588" s="5">
+      <c r="A588">
         <v>3658</v>
       </c>
-      <c r="B588" s="6">
-        <v>2</v>
-      </c>
-      <c r="C588" s="6">
-        <v>3</v>
-      </c>
-      <c r="D588" s="6">
-        <v>4</v>
-      </c>
-      <c r="E588" s="6">
-        <v>5</v>
-      </c>
-      <c r="F588" s="6">
-        <v>9</v>
-      </c>
-      <c r="G588" s="6">
-        <v>10</v>
-      </c>
-      <c r="H588" s="6">
-        <v>11</v>
-      </c>
-      <c r="I588" s="6">
-        <v>12</v>
-      </c>
-      <c r="J588" s="6">
-        <v>13</v>
-      </c>
-      <c r="K588" s="6">
-        <v>16</v>
-      </c>
-      <c r="L588" s="6">
-        <v>18</v>
-      </c>
-      <c r="M588" s="6">
-        <v>20</v>
-      </c>
-      <c r="N588" s="6">
-        <v>22</v>
-      </c>
-      <c r="O588" s="6">
-        <v>23</v>
-      </c>
-      <c r="P588" s="6">
+      <c r="B588">
+        <v>2</v>
+      </c>
+      <c r="C588">
+        <v>3</v>
+      </c>
+      <c r="D588">
+        <v>4</v>
+      </c>
+      <c r="E588">
+        <v>5</v>
+      </c>
+      <c r="F588">
+        <v>9</v>
+      </c>
+      <c r="G588">
+        <v>10</v>
+      </c>
+      <c r="H588">
+        <v>11</v>
+      </c>
+      <c r="I588">
+        <v>12</v>
+      </c>
+      <c r="J588">
+        <v>13</v>
+      </c>
+      <c r="K588">
+        <v>16</v>
+      </c>
+      <c r="L588">
+        <v>18</v>
+      </c>
+      <c r="M588">
+        <v>20</v>
+      </c>
+      <c r="N588">
+        <v>22</v>
+      </c>
+      <c r="O588">
+        <v>23</v>
+      </c>
+      <c r="P588">
         <v>24</v>
       </c>
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A589" s="5">
+      <c r="A589">
         <v>3659</v>
       </c>
-      <c r="B589" s="6">
-        <v>3</v>
-      </c>
-      <c r="C589" s="6">
-        <v>5</v>
-      </c>
-      <c r="D589" s="6">
-        <v>6</v>
-      </c>
-      <c r="E589" s="6">
-        <v>7</v>
-      </c>
-      <c r="F589" s="6">
-        <v>8</v>
-      </c>
-      <c r="G589" s="6">
-        <v>9</v>
-      </c>
-      <c r="H589" s="6">
-        <v>10</v>
-      </c>
-      <c r="I589" s="6">
-        <v>11</v>
-      </c>
-      <c r="J589" s="6">
-        <v>13</v>
-      </c>
-      <c r="K589" s="6">
-        <v>14</v>
-      </c>
-      <c r="L589" s="6">
-        <v>15</v>
-      </c>
-      <c r="M589" s="6">
-        <v>16</v>
-      </c>
-      <c r="N589" s="6">
-        <v>17</v>
-      </c>
-      <c r="O589" s="6">
-        <v>23</v>
-      </c>
-      <c r="P589" s="6">
+      <c r="B589">
+        <v>3</v>
+      </c>
+      <c r="C589">
+        <v>5</v>
+      </c>
+      <c r="D589">
+        <v>6</v>
+      </c>
+      <c r="E589">
+        <v>7</v>
+      </c>
+      <c r="F589">
+        <v>8</v>
+      </c>
+      <c r="G589">
+        <v>9</v>
+      </c>
+      <c r="H589">
+        <v>10</v>
+      </c>
+      <c r="I589">
+        <v>11</v>
+      </c>
+      <c r="J589">
+        <v>13</v>
+      </c>
+      <c r="K589">
+        <v>14</v>
+      </c>
+      <c r="L589">
+        <v>15</v>
+      </c>
+      <c r="M589">
+        <v>16</v>
+      </c>
+      <c r="N589">
+        <v>17</v>
+      </c>
+      <c r="O589">
+        <v>23</v>
+      </c>
+      <c r="P589">
         <v>25</v>
       </c>
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A590" s="5">
+      <c r="A590">
         <v>3660</v>
       </c>
-      <c r="B590" s="6">
-        <v>1</v>
-      </c>
-      <c r="C590" s="6">
-        <v>2</v>
-      </c>
-      <c r="D590" s="6">
-        <v>5</v>
-      </c>
-      <c r="E590" s="6">
-        <v>6</v>
-      </c>
-      <c r="F590" s="6">
-        <v>7</v>
-      </c>
-      <c r="G590" s="6">
-        <v>8</v>
-      </c>
-      <c r="H590" s="6">
-        <v>10</v>
-      </c>
-      <c r="I590" s="6">
-        <v>11</v>
-      </c>
-      <c r="J590" s="6">
-        <v>12</v>
-      </c>
-      <c r="K590" s="6">
-        <v>14</v>
-      </c>
-      <c r="L590" s="6">
-        <v>17</v>
-      </c>
-      <c r="M590" s="6">
-        <v>18</v>
-      </c>
-      <c r="N590" s="6">
-        <v>22</v>
-      </c>
-      <c r="O590" s="6">
-        <v>23</v>
-      </c>
-      <c r="P590" s="6">
+      <c r="B590">
+        <v>1</v>
+      </c>
+      <c r="C590">
+        <v>2</v>
+      </c>
+      <c r="D590">
+        <v>5</v>
+      </c>
+      <c r="E590">
+        <v>6</v>
+      </c>
+      <c r="F590">
+        <v>7</v>
+      </c>
+      <c r="G590">
+        <v>8</v>
+      </c>
+      <c r="H590">
+        <v>10</v>
+      </c>
+      <c r="I590">
+        <v>11</v>
+      </c>
+      <c r="J590">
+        <v>12</v>
+      </c>
+      <c r="K590">
+        <v>14</v>
+      </c>
+      <c r="L590">
+        <v>17</v>
+      </c>
+      <c r="M590">
+        <v>18</v>
+      </c>
+      <c r="N590">
+        <v>22</v>
+      </c>
+      <c r="O590">
+        <v>23</v>
+      </c>
+      <c r="P590">
         <v>24</v>
       </c>
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A591" s="5">
+      <c r="A591">
         <v>3661</v>
       </c>
-      <c r="B591" s="6">
-        <v>2</v>
-      </c>
-      <c r="C591" s="6">
-        <v>3</v>
-      </c>
-      <c r="D591" s="6">
-        <v>4</v>
-      </c>
-      <c r="E591" s="6">
-        <v>5</v>
-      </c>
-      <c r="F591" s="6">
-        <v>6</v>
-      </c>
-      <c r="G591" s="6">
-        <v>7</v>
-      </c>
-      <c r="H591" s="6">
-        <v>8</v>
-      </c>
-      <c r="I591" s="6">
-        <v>10</v>
-      </c>
-      <c r="J591" s="6">
-        <v>12</v>
-      </c>
-      <c r="K591" s="6">
-        <v>14</v>
-      </c>
-      <c r="L591" s="6">
-        <v>15</v>
-      </c>
-      <c r="M591" s="6">
-        <v>19</v>
-      </c>
-      <c r="N591" s="6">
-        <v>21</v>
-      </c>
-      <c r="O591" s="6">
-        <v>23</v>
-      </c>
-      <c r="P591" s="6">
+      <c r="B591">
+        <v>2</v>
+      </c>
+      <c r="C591">
+        <v>3</v>
+      </c>
+      <c r="D591">
+        <v>4</v>
+      </c>
+      <c r="E591">
+        <v>5</v>
+      </c>
+      <c r="F591">
+        <v>6</v>
+      </c>
+      <c r="G591">
+        <v>7</v>
+      </c>
+      <c r="H591">
+        <v>8</v>
+      </c>
+      <c r="I591">
+        <v>10</v>
+      </c>
+      <c r="J591">
+        <v>12</v>
+      </c>
+      <c r="K591">
+        <v>14</v>
+      </c>
+      <c r="L591">
+        <v>15</v>
+      </c>
+      <c r="M591">
+        <v>19</v>
+      </c>
+      <c r="N591">
+        <v>21</v>
+      </c>
+      <c r="O591">
+        <v>23</v>
+      </c>
+      <c r="P591">
         <v>24</v>
       </c>
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A592" s="5">
+      <c r="A592">
         <v>3662</v>
       </c>
-      <c r="B592" s="6">
-        <v>4</v>
-      </c>
-      <c r="C592" s="6">
-        <v>5</v>
-      </c>
-      <c r="D592" s="6">
-        <v>6</v>
-      </c>
-      <c r="E592" s="6">
-        <v>7</v>
-      </c>
-      <c r="F592" s="6">
-        <v>8</v>
-      </c>
-      <c r="G592" s="6">
-        <v>9</v>
-      </c>
-      <c r="H592" s="6">
-        <v>10</v>
-      </c>
-      <c r="I592" s="6">
-        <v>11</v>
-      </c>
-      <c r="J592" s="6">
-        <v>12</v>
-      </c>
-      <c r="K592" s="6">
-        <v>13</v>
-      </c>
-      <c r="L592" s="6">
-        <v>15</v>
-      </c>
-      <c r="M592" s="6">
-        <v>18</v>
-      </c>
-      <c r="N592" s="6">
-        <v>20</v>
-      </c>
-      <c r="O592" s="6">
-        <v>23</v>
-      </c>
-      <c r="P592" s="6">
+      <c r="B592">
+        <v>4</v>
+      </c>
+      <c r="C592">
+        <v>5</v>
+      </c>
+      <c r="D592">
+        <v>6</v>
+      </c>
+      <c r="E592">
+        <v>7</v>
+      </c>
+      <c r="F592">
+        <v>8</v>
+      </c>
+      <c r="G592">
+        <v>9</v>
+      </c>
+      <c r="H592">
+        <v>10</v>
+      </c>
+      <c r="I592">
+        <v>11</v>
+      </c>
+      <c r="J592">
+        <v>12</v>
+      </c>
+      <c r="K592">
+        <v>13</v>
+      </c>
+      <c r="L592">
+        <v>15</v>
+      </c>
+      <c r="M592">
+        <v>18</v>
+      </c>
+      <c r="N592">
+        <v>20</v>
+      </c>
+      <c r="O592">
+        <v>23</v>
+      </c>
+      <c r="P592">
         <v>25</v>
       </c>
     </row>
     <row r="593" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A593" s="5">
+      <c r="A593">
         <v>3663</v>
       </c>
-      <c r="B593" s="6">
-        <v>1</v>
-      </c>
-      <c r="C593" s="6">
-        <v>3</v>
-      </c>
-      <c r="D593" s="6">
-        <v>4</v>
-      </c>
-      <c r="E593" s="6">
-        <v>5</v>
-      </c>
-      <c r="F593" s="6">
-        <v>6</v>
-      </c>
-      <c r="G593" s="6">
-        <v>10</v>
-      </c>
-      <c r="H593" s="6">
-        <v>12</v>
-      </c>
-      <c r="I593" s="6">
-        <v>14</v>
-      </c>
-      <c r="J593" s="6">
-        <v>17</v>
-      </c>
-      <c r="K593" s="6">
-        <v>19</v>
-      </c>
-      <c r="L593" s="6">
-        <v>20</v>
-      </c>
-      <c r="M593" s="6">
-        <v>22</v>
-      </c>
-      <c r="N593" s="6">
-        <v>23</v>
-      </c>
-      <c r="O593" s="6">
-        <v>24</v>
-      </c>
-      <c r="P593" s="6">
+      <c r="B593">
+        <v>1</v>
+      </c>
+      <c r="C593">
+        <v>3</v>
+      </c>
+      <c r="D593">
+        <v>4</v>
+      </c>
+      <c r="E593">
+        <v>5</v>
+      </c>
+      <c r="F593">
+        <v>6</v>
+      </c>
+      <c r="G593">
+        <v>10</v>
+      </c>
+      <c r="H593">
+        <v>12</v>
+      </c>
+      <c r="I593">
+        <v>14</v>
+      </c>
+      <c r="J593">
+        <v>17</v>
+      </c>
+      <c r="K593">
+        <v>19</v>
+      </c>
+      <c r="L593">
+        <v>20</v>
+      </c>
+      <c r="M593">
+        <v>22</v>
+      </c>
+      <c r="N593">
+        <v>23</v>
+      </c>
+      <c r="O593">
+        <v>24</v>
+      </c>
+      <c r="P593">
         <v>25</v>
       </c>
     </row>
     <row r="594" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A594" s="5">
+      <c r="A594">
         <v>3664</v>
       </c>
-      <c r="B594" s="6">
-        <v>1</v>
-      </c>
-      <c r="C594" s="6">
-        <v>2</v>
-      </c>
-      <c r="D594" s="6">
-        <v>4</v>
-      </c>
-      <c r="E594" s="6">
-        <v>5</v>
-      </c>
-      <c r="F594" s="6">
-        <v>6</v>
-      </c>
-      <c r="G594" s="6">
-        <v>7</v>
-      </c>
-      <c r="H594" s="6">
-        <v>10</v>
-      </c>
-      <c r="I594" s="6">
-        <v>11</v>
-      </c>
-      <c r="J594" s="6">
-        <v>12</v>
-      </c>
-      <c r="K594" s="6">
-        <v>16</v>
-      </c>
-      <c r="L594" s="6">
-        <v>18</v>
-      </c>
-      <c r="M594" s="6">
-        <v>19</v>
-      </c>
-      <c r="N594" s="6">
-        <v>20</v>
-      </c>
-      <c r="O594" s="6">
-        <v>22</v>
-      </c>
-      <c r="P594" s="6">
+      <c r="B594">
+        <v>1</v>
+      </c>
+      <c r="C594">
+        <v>2</v>
+      </c>
+      <c r="D594">
+        <v>4</v>
+      </c>
+      <c r="E594">
+        <v>5</v>
+      </c>
+      <c r="F594">
+        <v>6</v>
+      </c>
+      <c r="G594">
+        <v>7</v>
+      </c>
+      <c r="H594">
+        <v>10</v>
+      </c>
+      <c r="I594">
+        <v>11</v>
+      </c>
+      <c r="J594">
+        <v>12</v>
+      </c>
+      <c r="K594">
+        <v>16</v>
+      </c>
+      <c r="L594">
+        <v>18</v>
+      </c>
+      <c r="M594">
+        <v>19</v>
+      </c>
+      <c r="N594">
+        <v>20</v>
+      </c>
+      <c r="O594">
+        <v>22</v>
+      </c>
+      <c r="P594">
         <v>23</v>
       </c>
     </row>
     <row r="595" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A595" s="5">
+      <c r="A595">
         <v>3665</v>
       </c>
-      <c r="B595" s="6">
-        <v>1</v>
-      </c>
-      <c r="C595" s="6">
-        <v>2</v>
-      </c>
-      <c r="D595" s="6">
-        <v>3</v>
-      </c>
-      <c r="E595" s="6">
-        <v>5</v>
-      </c>
-      <c r="F595" s="6">
-        <v>6</v>
-      </c>
-      <c r="G595" s="6">
-        <v>7</v>
-      </c>
-      <c r="H595" s="6">
-        <v>9</v>
-      </c>
-      <c r="I595" s="6">
-        <v>10</v>
-      </c>
-      <c r="J595" s="6">
-        <v>11</v>
-      </c>
-      <c r="K595" s="6">
-        <v>13</v>
-      </c>
-      <c r="L595" s="6">
-        <v>16</v>
-      </c>
-      <c r="M595" s="6">
-        <v>18</v>
-      </c>
-      <c r="N595" s="6">
-        <v>22</v>
-      </c>
-      <c r="O595" s="6">
-        <v>23</v>
-      </c>
-      <c r="P595" s="6">
+      <c r="B595">
+        <v>1</v>
+      </c>
+      <c r="C595">
+        <v>2</v>
+      </c>
+      <c r="D595">
+        <v>3</v>
+      </c>
+      <c r="E595">
+        <v>5</v>
+      </c>
+      <c r="F595">
+        <v>6</v>
+      </c>
+      <c r="G595">
+        <v>7</v>
+      </c>
+      <c r="H595">
+        <v>9</v>
+      </c>
+      <c r="I595">
+        <v>10</v>
+      </c>
+      <c r="J595">
+        <v>11</v>
+      </c>
+      <c r="K595">
+        <v>13</v>
+      </c>
+      <c r="L595">
+        <v>16</v>
+      </c>
+      <c r="M595">
+        <v>18</v>
+      </c>
+      <c r="N595">
+        <v>22</v>
+      </c>
+      <c r="O595">
+        <v>23</v>
+      </c>
+      <c r="P595">
         <v>25</v>
       </c>
     </row>
     <row r="596" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A596" s="5">
+      <c r="A596">
         <v>3666</v>
       </c>
-      <c r="B596" s="6">
-        <v>1</v>
-      </c>
-      <c r="C596" s="6">
-        <v>4</v>
-      </c>
-      <c r="D596" s="6">
-        <v>6</v>
-      </c>
-      <c r="E596" s="6">
-        <v>7</v>
-      </c>
-      <c r="F596" s="6">
-        <v>9</v>
-      </c>
-      <c r="G596" s="6">
-        <v>12</v>
-      </c>
-      <c r="H596" s="6">
-        <v>14</v>
-      </c>
-      <c r="I596" s="6">
-        <v>15</v>
-      </c>
-      <c r="J596" s="6">
-        <v>16</v>
-      </c>
-      <c r="K596" s="6">
-        <v>17</v>
-      </c>
-      <c r="L596" s="6">
-        <v>19</v>
-      </c>
-      <c r="M596" s="6">
-        <v>20</v>
-      </c>
-      <c r="N596" s="6">
-        <v>21</v>
-      </c>
-      <c r="O596" s="6">
-        <v>22</v>
-      </c>
-      <c r="P596" s="6">
+      <c r="B596">
+        <v>1</v>
+      </c>
+      <c r="C596">
+        <v>4</v>
+      </c>
+      <c r="D596">
+        <v>6</v>
+      </c>
+      <c r="E596">
+        <v>7</v>
+      </c>
+      <c r="F596">
+        <v>9</v>
+      </c>
+      <c r="G596">
+        <v>12</v>
+      </c>
+      <c r="H596">
+        <v>14</v>
+      </c>
+      <c r="I596">
+        <v>15</v>
+      </c>
+      <c r="J596">
+        <v>16</v>
+      </c>
+      <c r="K596">
+        <v>17</v>
+      </c>
+      <c r="L596">
+        <v>19</v>
+      </c>
+      <c r="M596">
+        <v>20</v>
+      </c>
+      <c r="N596">
+        <v>21</v>
+      </c>
+      <c r="O596">
+        <v>22</v>
+      </c>
+      <c r="P596">
         <v>23</v>
       </c>
     </row>
     <row r="597" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A597" s="5">
+      <c r="A597">
         <v>3667</v>
       </c>
-      <c r="B597" s="6">
-        <v>1</v>
-      </c>
-      <c r="C597" s="6">
-        <v>3</v>
-      </c>
-      <c r="D597" s="6">
-        <v>4</v>
-      </c>
-      <c r="E597" s="6">
-        <v>5</v>
-      </c>
-      <c r="F597" s="6">
-        <v>6</v>
-      </c>
-      <c r="G597" s="6">
-        <v>7</v>
-      </c>
-      <c r="H597" s="6">
-        <v>9</v>
-      </c>
-      <c r="I597" s="6">
-        <v>11</v>
-      </c>
-      <c r="J597" s="6">
-        <v>14</v>
-      </c>
-      <c r="K597" s="6">
-        <v>15</v>
-      </c>
-      <c r="L597" s="6">
-        <v>19</v>
-      </c>
-      <c r="M597" s="6">
-        <v>21</v>
-      </c>
-      <c r="N597" s="6">
-        <v>22</v>
-      </c>
-      <c r="O597" s="6">
-        <v>23</v>
-      </c>
-      <c r="P597" s="6">
+      <c r="B597">
+        <v>1</v>
+      </c>
+      <c r="C597">
+        <v>3</v>
+      </c>
+      <c r="D597">
+        <v>4</v>
+      </c>
+      <c r="E597">
+        <v>5</v>
+      </c>
+      <c r="F597">
+        <v>6</v>
+      </c>
+      <c r="G597">
+        <v>7</v>
+      </c>
+      <c r="H597">
+        <v>9</v>
+      </c>
+      <c r="I597">
+        <v>11</v>
+      </c>
+      <c r="J597">
+        <v>14</v>
+      </c>
+      <c r="K597">
+        <v>15</v>
+      </c>
+      <c r="L597">
+        <v>19</v>
+      </c>
+      <c r="M597">
+        <v>21</v>
+      </c>
+      <c r="N597">
+        <v>22</v>
+      </c>
+      <c r="O597">
+        <v>23</v>
+      </c>
+      <c r="P597">
         <v>25</v>
       </c>
     </row>
     <row r="598" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A598" s="5">
+      <c r="A598">
         <v>3668</v>
       </c>
-      <c r="B598" s="6">
-        <v>1</v>
-      </c>
-      <c r="C598" s="6">
-        <v>2</v>
-      </c>
-      <c r="D598" s="6">
-        <v>3</v>
-      </c>
-      <c r="E598" s="6">
-        <v>5</v>
-      </c>
-      <c r="F598" s="6">
-        <v>7</v>
-      </c>
-      <c r="G598" s="6">
-        <v>8</v>
-      </c>
-      <c r="H598" s="6">
-        <v>9</v>
-      </c>
-      <c r="I598" s="6">
-        <v>10</v>
-      </c>
-      <c r="J598" s="6">
-        <v>11</v>
-      </c>
-      <c r="K598" s="6">
-        <v>13</v>
-      </c>
-      <c r="L598" s="6">
-        <v>15</v>
-      </c>
-      <c r="M598" s="6">
-        <v>17</v>
-      </c>
-      <c r="N598" s="6">
-        <v>18</v>
-      </c>
-      <c r="O598" s="6">
-        <v>21</v>
-      </c>
-      <c r="P598" s="6">
+      <c r="B598">
+        <v>1</v>
+      </c>
+      <c r="C598">
+        <v>2</v>
+      </c>
+      <c r="D598">
+        <v>3</v>
+      </c>
+      <c r="E598">
+        <v>5</v>
+      </c>
+      <c r="F598">
+        <v>7</v>
+      </c>
+      <c r="G598">
+        <v>8</v>
+      </c>
+      <c r="H598">
+        <v>9</v>
+      </c>
+      <c r="I598">
+        <v>10</v>
+      </c>
+      <c r="J598">
+        <v>11</v>
+      </c>
+      <c r="K598">
+        <v>13</v>
+      </c>
+      <c r="L598">
+        <v>15</v>
+      </c>
+      <c r="M598">
+        <v>17</v>
+      </c>
+      <c r="N598">
+        <v>18</v>
+      </c>
+      <c r="O598">
+        <v>21</v>
+      </c>
+      <c r="P598">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="599" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A599">
+        <v>3669</v>
+      </c>
+      <c r="B599">
+        <v>2</v>
+      </c>
+      <c r="C599">
+        <v>3</v>
+      </c>
+      <c r="D599">
+        <v>4</v>
+      </c>
+      <c r="E599">
+        <v>5</v>
+      </c>
+      <c r="F599">
+        <v>8</v>
+      </c>
+      <c r="G599">
+        <v>9</v>
+      </c>
+      <c r="H599">
+        <v>10</v>
+      </c>
+      <c r="I599">
+        <v>11</v>
+      </c>
+      <c r="J599">
+        <v>12</v>
+      </c>
+      <c r="K599">
+        <v>15</v>
+      </c>
+      <c r="L599">
+        <v>16</v>
+      </c>
+      <c r="M599">
+        <v>17</v>
+      </c>
+      <c r="N599">
+        <v>22</v>
+      </c>
+      <c r="O599">
+        <v>23</v>
+      </c>
+      <c r="P599">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="600" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A600">
+        <v>3670</v>
+      </c>
+      <c r="B600">
+        <v>1</v>
+      </c>
+      <c r="C600">
+        <v>2</v>
+      </c>
+      <c r="D600">
+        <v>3</v>
+      </c>
+      <c r="E600">
+        <v>5</v>
+      </c>
+      <c r="F600">
+        <v>6</v>
+      </c>
+      <c r="G600">
+        <v>10</v>
+      </c>
+      <c r="H600">
+        <v>11</v>
+      </c>
+      <c r="I600">
+        <v>14</v>
+      </c>
+      <c r="J600">
+        <v>15</v>
+      </c>
+      <c r="K600">
+        <v>17</v>
+      </c>
+      <c r="L600">
+        <v>18</v>
+      </c>
+      <c r="M600">
+        <v>19</v>
+      </c>
+      <c r="N600">
+        <v>21</v>
+      </c>
+      <c r="O600">
+        <v>23</v>
+      </c>
+      <c r="P600">
         <v>24</v>
       </c>
     </row>
@@ -30393,15 +30491,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30569,6 +30658,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -30580,14 +30678,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30607,6 +30697,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7464987B-B19E-4B52-8FFC-5A7A27FD9842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AEE931-069D-452C-8FC4-F300C340B235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57630" yWindow="6450" windowWidth="23355" windowHeight="8970" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P600"/>
+  <dimension ref="A1:P601"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -30485,12 +30485,71 @@
         <v>24</v>
       </c>
     </row>
+    <row r="601" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A601">
+        <v>3671</v>
+      </c>
+      <c r="B601">
+        <v>1</v>
+      </c>
+      <c r="C601">
+        <v>3</v>
+      </c>
+      <c r="D601">
+        <v>4</v>
+      </c>
+      <c r="E601">
+        <v>5</v>
+      </c>
+      <c r="F601">
+        <v>6</v>
+      </c>
+      <c r="G601">
+        <v>7</v>
+      </c>
+      <c r="H601">
+        <v>9</v>
+      </c>
+      <c r="I601">
+        <v>10</v>
+      </c>
+      <c r="J601">
+        <v>12</v>
+      </c>
+      <c r="K601">
+        <v>13</v>
+      </c>
+      <c r="L601">
+        <v>15</v>
+      </c>
+      <c r="M601">
+        <v>16</v>
+      </c>
+      <c r="N601">
+        <v>17</v>
+      </c>
+      <c r="O601">
+        <v>18</v>
+      </c>
+      <c r="P601">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30658,15 +30717,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -30678,6 +30728,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30697,14 +30755,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AEE931-069D-452C-8FC4-F300C340B235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8086D3D-92C3-4C3A-A6FD-921F5490B713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57630" yWindow="6450" windowWidth="23355" windowHeight="8970" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="8190" yWindow="1493" windowWidth="19590" windowHeight="12509" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P601"/>
+  <dimension ref="A1:P609"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -30535,21 +30535,412 @@
         <v>21</v>
       </c>
     </row>
+    <row r="602" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A602">
+        <v>3672</v>
+      </c>
+      <c r="B602">
+        <v>1</v>
+      </c>
+      <c r="C602">
+        <v>3</v>
+      </c>
+      <c r="D602">
+        <v>5</v>
+      </c>
+      <c r="E602">
+        <v>7</v>
+      </c>
+      <c r="F602">
+        <v>9</v>
+      </c>
+      <c r="G602">
+        <v>10</v>
+      </c>
+      <c r="H602">
+        <v>11</v>
+      </c>
+      <c r="I602">
+        <v>12</v>
+      </c>
+      <c r="J602">
+        <v>13</v>
+      </c>
+      <c r="K602">
+        <v>14</v>
+      </c>
+      <c r="L602">
+        <v>16</v>
+      </c>
+      <c r="M602">
+        <v>20</v>
+      </c>
+      <c r="N602">
+        <v>23</v>
+      </c>
+      <c r="O602">
+        <v>24</v>
+      </c>
+      <c r="P602">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="603" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A603">
+        <v>3673</v>
+      </c>
+      <c r="B603">
+        <v>1</v>
+      </c>
+      <c r="C603">
+        <v>3</v>
+      </c>
+      <c r="D603">
+        <v>4</v>
+      </c>
+      <c r="E603">
+        <v>8</v>
+      </c>
+      <c r="F603">
+        <v>10</v>
+      </c>
+      <c r="G603">
+        <v>11</v>
+      </c>
+      <c r="H603">
+        <v>12</v>
+      </c>
+      <c r="I603">
+        <v>15</v>
+      </c>
+      <c r="J603">
+        <v>16</v>
+      </c>
+      <c r="K603">
+        <v>18</v>
+      </c>
+      <c r="L603">
+        <v>19</v>
+      </c>
+      <c r="M603">
+        <v>20</v>
+      </c>
+      <c r="N603">
+        <v>21</v>
+      </c>
+      <c r="O603">
+        <v>22</v>
+      </c>
+      <c r="P603">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="604" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A604">
+        <v>3674</v>
+      </c>
+      <c r="B604">
+        <v>2</v>
+      </c>
+      <c r="C604">
+        <v>6</v>
+      </c>
+      <c r="D604">
+        <v>7</v>
+      </c>
+      <c r="E604">
+        <v>8</v>
+      </c>
+      <c r="F604">
+        <v>9</v>
+      </c>
+      <c r="G604">
+        <v>10</v>
+      </c>
+      <c r="H604">
+        <v>15</v>
+      </c>
+      <c r="I604">
+        <v>17</v>
+      </c>
+      <c r="J604">
+        <v>19</v>
+      </c>
+      <c r="K604">
+        <v>20</v>
+      </c>
+      <c r="L604">
+        <v>21</v>
+      </c>
+      <c r="M604">
+        <v>22</v>
+      </c>
+      <c r="N604">
+        <v>23</v>
+      </c>
+      <c r="O604">
+        <v>24</v>
+      </c>
+      <c r="P604">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="605" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A605">
+        <v>3675</v>
+      </c>
+      <c r="B605">
+        <v>2</v>
+      </c>
+      <c r="C605">
+        <v>3</v>
+      </c>
+      <c r="D605">
+        <v>4</v>
+      </c>
+      <c r="E605">
+        <v>5</v>
+      </c>
+      <c r="F605">
+        <v>7</v>
+      </c>
+      <c r="G605">
+        <v>8</v>
+      </c>
+      <c r="H605">
+        <v>10</v>
+      </c>
+      <c r="I605">
+        <v>12</v>
+      </c>
+      <c r="J605">
+        <v>13</v>
+      </c>
+      <c r="K605">
+        <v>15</v>
+      </c>
+      <c r="L605">
+        <v>17</v>
+      </c>
+      <c r="M605">
+        <v>18</v>
+      </c>
+      <c r="N605">
+        <v>19</v>
+      </c>
+      <c r="O605">
+        <v>23</v>
+      </c>
+      <c r="P605">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="606" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A606">
+        <v>3676</v>
+      </c>
+      <c r="B606">
+        <v>4</v>
+      </c>
+      <c r="C606">
+        <v>5</v>
+      </c>
+      <c r="D606">
+        <v>6</v>
+      </c>
+      <c r="E606">
+        <v>8</v>
+      </c>
+      <c r="F606">
+        <v>10</v>
+      </c>
+      <c r="G606">
+        <v>13</v>
+      </c>
+      <c r="H606">
+        <v>15</v>
+      </c>
+      <c r="I606">
+        <v>16</v>
+      </c>
+      <c r="J606">
+        <v>18</v>
+      </c>
+      <c r="K606">
+        <v>19</v>
+      </c>
+      <c r="L606">
+        <v>21</v>
+      </c>
+      <c r="M606">
+        <v>22</v>
+      </c>
+      <c r="N606">
+        <v>23</v>
+      </c>
+      <c r="O606">
+        <v>24</v>
+      </c>
+      <c r="P606">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="607" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A607">
+        <v>3677</v>
+      </c>
+      <c r="B607">
+        <v>1</v>
+      </c>
+      <c r="C607">
+        <v>2</v>
+      </c>
+      <c r="D607">
+        <v>3</v>
+      </c>
+      <c r="E607">
+        <v>8</v>
+      </c>
+      <c r="F607">
+        <v>9</v>
+      </c>
+      <c r="G607">
+        <v>10</v>
+      </c>
+      <c r="H607">
+        <v>12</v>
+      </c>
+      <c r="I607">
+        <v>13</v>
+      </c>
+      <c r="J607">
+        <v>14</v>
+      </c>
+      <c r="K607">
+        <v>15</v>
+      </c>
+      <c r="L607">
+        <v>16</v>
+      </c>
+      <c r="M607">
+        <v>18</v>
+      </c>
+      <c r="N607">
+        <v>22</v>
+      </c>
+      <c r="O607">
+        <v>23</v>
+      </c>
+      <c r="P607">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="608" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A608">
+        <v>3678</v>
+      </c>
+      <c r="B608">
+        <v>1</v>
+      </c>
+      <c r="C608">
+        <v>2</v>
+      </c>
+      <c r="D608">
+        <v>3</v>
+      </c>
+      <c r="E608">
+        <v>4</v>
+      </c>
+      <c r="F608">
+        <v>5</v>
+      </c>
+      <c r="G608">
+        <v>6</v>
+      </c>
+      <c r="H608">
+        <v>8</v>
+      </c>
+      <c r="I608">
+        <v>10</v>
+      </c>
+      <c r="J608">
+        <v>11</v>
+      </c>
+      <c r="K608">
+        <v>14</v>
+      </c>
+      <c r="L608">
+        <v>18</v>
+      </c>
+      <c r="M608">
+        <v>20</v>
+      </c>
+      <c r="N608">
+        <v>23</v>
+      </c>
+      <c r="O608">
+        <v>24</v>
+      </c>
+      <c r="P608">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="609" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A609">
+        <v>3679</v>
+      </c>
+      <c r="B609">
+        <v>1</v>
+      </c>
+      <c r="C609">
+        <v>2</v>
+      </c>
+      <c r="D609">
+        <v>3</v>
+      </c>
+      <c r="E609">
+        <v>7</v>
+      </c>
+      <c r="F609">
+        <v>8</v>
+      </c>
+      <c r="G609">
+        <v>10</v>
+      </c>
+      <c r="H609">
+        <v>11</v>
+      </c>
+      <c r="I609">
+        <v>13</v>
+      </c>
+      <c r="J609">
+        <v>14</v>
+      </c>
+      <c r="K609">
+        <v>17</v>
+      </c>
+      <c r="L609">
+        <v>18</v>
+      </c>
+      <c r="M609">
+        <v>21</v>
+      </c>
+      <c r="N609">
+        <v>22</v>
+      </c>
+      <c r="O609">
+        <v>23</v>
+      </c>
+      <c r="P609">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -30717,6 +31108,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -30728,14 +31128,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30755,6 +31147,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8086D3D-92C3-4C3A-A6FD-921F5490B713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C5D69A-20AE-437B-87DF-72A535F80DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8190" yWindow="1493" windowWidth="19590" windowHeight="12509" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="59010" yWindow="120" windowWidth="15285" windowHeight="13365" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P609"/>
+  <dimension ref="A1:P646"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -30935,12 +30935,1871 @@
         <v>24</v>
       </c>
     </row>
+    <row r="610" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A610">
+        <v>3680</v>
+      </c>
+      <c r="B610">
+        <v>1</v>
+      </c>
+      <c r="C610">
+        <v>2</v>
+      </c>
+      <c r="D610">
+        <v>3</v>
+      </c>
+      <c r="E610">
+        <v>4</v>
+      </c>
+      <c r="F610">
+        <v>5</v>
+      </c>
+      <c r="G610">
+        <v>7</v>
+      </c>
+      <c r="H610">
+        <v>8</v>
+      </c>
+      <c r="I610">
+        <v>9</v>
+      </c>
+      <c r="J610">
+        <v>11</v>
+      </c>
+      <c r="K610">
+        <v>15</v>
+      </c>
+      <c r="L610">
+        <v>16</v>
+      </c>
+      <c r="M610">
+        <v>19</v>
+      </c>
+      <c r="N610">
+        <v>22</v>
+      </c>
+      <c r="O610">
+        <v>24</v>
+      </c>
+      <c r="P610">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="611" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A611">
+        <v>3681</v>
+      </c>
+      <c r="B611">
+        <v>1</v>
+      </c>
+      <c r="C611">
+        <v>2</v>
+      </c>
+      <c r="D611">
+        <v>4</v>
+      </c>
+      <c r="E611">
+        <v>5</v>
+      </c>
+      <c r="F611">
+        <v>7</v>
+      </c>
+      <c r="G611">
+        <v>9</v>
+      </c>
+      <c r="H611">
+        <v>11</v>
+      </c>
+      <c r="I611">
+        <v>12</v>
+      </c>
+      <c r="J611">
+        <v>14</v>
+      </c>
+      <c r="K611">
+        <v>15</v>
+      </c>
+      <c r="L611">
+        <v>16</v>
+      </c>
+      <c r="M611">
+        <v>20</v>
+      </c>
+      <c r="N611">
+        <v>21</v>
+      </c>
+      <c r="O611">
+        <v>22</v>
+      </c>
+      <c r="P611">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="612" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A612">
+        <v>3682</v>
+      </c>
+      <c r="B612">
+        <v>1</v>
+      </c>
+      <c r="C612">
+        <v>2</v>
+      </c>
+      <c r="D612">
+        <v>4</v>
+      </c>
+      <c r="E612">
+        <v>5</v>
+      </c>
+      <c r="F612">
+        <v>7</v>
+      </c>
+      <c r="G612">
+        <v>9</v>
+      </c>
+      <c r="H612">
+        <v>10</v>
+      </c>
+      <c r="I612">
+        <v>11</v>
+      </c>
+      <c r="J612">
+        <v>12</v>
+      </c>
+      <c r="K612">
+        <v>13</v>
+      </c>
+      <c r="L612">
+        <v>17</v>
+      </c>
+      <c r="M612">
+        <v>18</v>
+      </c>
+      <c r="N612">
+        <v>21</v>
+      </c>
+      <c r="O612">
+        <v>22</v>
+      </c>
+      <c r="P612">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="613" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A613">
+        <v>3683</v>
+      </c>
+      <c r="B613">
+        <v>2</v>
+      </c>
+      <c r="C613">
+        <v>3</v>
+      </c>
+      <c r="D613">
+        <v>5</v>
+      </c>
+      <c r="E613">
+        <v>7</v>
+      </c>
+      <c r="F613">
+        <v>8</v>
+      </c>
+      <c r="G613">
+        <v>9</v>
+      </c>
+      <c r="H613">
+        <v>10</v>
+      </c>
+      <c r="I613">
+        <v>11</v>
+      </c>
+      <c r="J613">
+        <v>12</v>
+      </c>
+      <c r="K613">
+        <v>14</v>
+      </c>
+      <c r="L613">
+        <v>16</v>
+      </c>
+      <c r="M613">
+        <v>19</v>
+      </c>
+      <c r="N613">
+        <v>20</v>
+      </c>
+      <c r="O613">
+        <v>24</v>
+      </c>
+      <c r="P613">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="614" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A614">
+        <v>3684</v>
+      </c>
+      <c r="B614">
+        <v>1</v>
+      </c>
+      <c r="C614">
+        <v>3</v>
+      </c>
+      <c r="D614">
+        <v>5</v>
+      </c>
+      <c r="E614">
+        <v>6</v>
+      </c>
+      <c r="F614">
+        <v>9</v>
+      </c>
+      <c r="G614">
+        <v>10</v>
+      </c>
+      <c r="H614">
+        <v>11</v>
+      </c>
+      <c r="I614">
+        <v>12</v>
+      </c>
+      <c r="J614">
+        <v>13</v>
+      </c>
+      <c r="K614">
+        <v>17</v>
+      </c>
+      <c r="L614">
+        <v>18</v>
+      </c>
+      <c r="M614">
+        <v>19</v>
+      </c>
+      <c r="N614">
+        <v>20</v>
+      </c>
+      <c r="O614">
+        <v>21</v>
+      </c>
+      <c r="P614">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="615" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A615">
+        <v>3685</v>
+      </c>
+      <c r="B615">
+        <v>1</v>
+      </c>
+      <c r="C615">
+        <v>2</v>
+      </c>
+      <c r="D615">
+        <v>4</v>
+      </c>
+      <c r="E615">
+        <v>8</v>
+      </c>
+      <c r="F615">
+        <v>10</v>
+      </c>
+      <c r="G615">
+        <v>11</v>
+      </c>
+      <c r="H615">
+        <v>14</v>
+      </c>
+      <c r="I615">
+        <v>15</v>
+      </c>
+      <c r="J615">
+        <v>17</v>
+      </c>
+      <c r="K615">
+        <v>19</v>
+      </c>
+      <c r="L615">
+        <v>20</v>
+      </c>
+      <c r="M615">
+        <v>21</v>
+      </c>
+      <c r="N615">
+        <v>23</v>
+      </c>
+      <c r="O615">
+        <v>24</v>
+      </c>
+      <c r="P615">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="616" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A616">
+        <v>3686</v>
+      </c>
+      <c r="B616">
+        <v>1</v>
+      </c>
+      <c r="C616">
+        <v>2</v>
+      </c>
+      <c r="D616">
+        <v>4</v>
+      </c>
+      <c r="E616">
+        <v>5</v>
+      </c>
+      <c r="F616">
+        <v>6</v>
+      </c>
+      <c r="G616">
+        <v>8</v>
+      </c>
+      <c r="H616">
+        <v>9</v>
+      </c>
+      <c r="I616">
+        <v>10</v>
+      </c>
+      <c r="J616">
+        <v>13</v>
+      </c>
+      <c r="K616">
+        <v>15</v>
+      </c>
+      <c r="L616">
+        <v>18</v>
+      </c>
+      <c r="M616">
+        <v>19</v>
+      </c>
+      <c r="N616">
+        <v>23</v>
+      </c>
+      <c r="O616">
+        <v>24</v>
+      </c>
+      <c r="P616">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="617" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A617">
+        <v>3687</v>
+      </c>
+      <c r="B617">
+        <v>3</v>
+      </c>
+      <c r="C617">
+        <v>4</v>
+      </c>
+      <c r="D617">
+        <v>5</v>
+      </c>
+      <c r="E617">
+        <v>6</v>
+      </c>
+      <c r="F617">
+        <v>12</v>
+      </c>
+      <c r="G617">
+        <v>13</v>
+      </c>
+      <c r="H617">
+        <v>14</v>
+      </c>
+      <c r="I617">
+        <v>16</v>
+      </c>
+      <c r="J617">
+        <v>17</v>
+      </c>
+      <c r="K617">
+        <v>18</v>
+      </c>
+      <c r="L617">
+        <v>20</v>
+      </c>
+      <c r="M617">
+        <v>21</v>
+      </c>
+      <c r="N617">
+        <v>23</v>
+      </c>
+      <c r="O617">
+        <v>24</v>
+      </c>
+      <c r="P617">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="618" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A618">
+        <v>3688</v>
+      </c>
+      <c r="B618">
+        <v>1</v>
+      </c>
+      <c r="C618">
+        <v>2</v>
+      </c>
+      <c r="D618">
+        <v>3</v>
+      </c>
+      <c r="E618">
+        <v>4</v>
+      </c>
+      <c r="F618">
+        <v>5</v>
+      </c>
+      <c r="G618">
+        <v>6</v>
+      </c>
+      <c r="H618">
+        <v>7</v>
+      </c>
+      <c r="I618">
+        <v>11</v>
+      </c>
+      <c r="J618">
+        <v>12</v>
+      </c>
+      <c r="K618">
+        <v>16</v>
+      </c>
+      <c r="L618">
+        <v>17</v>
+      </c>
+      <c r="M618">
+        <v>19</v>
+      </c>
+      <c r="N618">
+        <v>21</v>
+      </c>
+      <c r="O618">
+        <v>24</v>
+      </c>
+      <c r="P618">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="619" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A619">
+        <v>3689</v>
+      </c>
+      <c r="B619">
+        <v>3</v>
+      </c>
+      <c r="C619">
+        <v>5</v>
+      </c>
+      <c r="D619">
+        <v>7</v>
+      </c>
+      <c r="E619">
+        <v>8</v>
+      </c>
+      <c r="F619">
+        <v>10</v>
+      </c>
+      <c r="G619">
+        <v>11</v>
+      </c>
+      <c r="H619">
+        <v>12</v>
+      </c>
+      <c r="I619">
+        <v>13</v>
+      </c>
+      <c r="J619">
+        <v>14</v>
+      </c>
+      <c r="K619">
+        <v>15</v>
+      </c>
+      <c r="L619">
+        <v>16</v>
+      </c>
+      <c r="M619">
+        <v>18</v>
+      </c>
+      <c r="N619">
+        <v>19</v>
+      </c>
+      <c r="O619">
+        <v>20</v>
+      </c>
+      <c r="P619">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="620" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A620">
+        <v>3690</v>
+      </c>
+      <c r="B620">
+        <v>2</v>
+      </c>
+      <c r="C620">
+        <v>5</v>
+      </c>
+      <c r="D620">
+        <v>6</v>
+      </c>
+      <c r="E620">
+        <v>7</v>
+      </c>
+      <c r="F620">
+        <v>8</v>
+      </c>
+      <c r="G620">
+        <v>9</v>
+      </c>
+      <c r="H620">
+        <v>12</v>
+      </c>
+      <c r="I620">
+        <v>15</v>
+      </c>
+      <c r="J620">
+        <v>18</v>
+      </c>
+      <c r="K620">
+        <v>19</v>
+      </c>
+      <c r="L620">
+        <v>20</v>
+      </c>
+      <c r="M620">
+        <v>21</v>
+      </c>
+      <c r="N620">
+        <v>22</v>
+      </c>
+      <c r="O620">
+        <v>24</v>
+      </c>
+      <c r="P620">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="621" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A621">
+        <v>3691</v>
+      </c>
+      <c r="B621">
+        <v>2</v>
+      </c>
+      <c r="C621">
+        <v>3</v>
+      </c>
+      <c r="D621">
+        <v>5</v>
+      </c>
+      <c r="E621">
+        <v>8</v>
+      </c>
+      <c r="F621">
+        <v>9</v>
+      </c>
+      <c r="G621">
+        <v>10</v>
+      </c>
+      <c r="H621">
+        <v>13</v>
+      </c>
+      <c r="I621">
+        <v>14</v>
+      </c>
+      <c r="J621">
+        <v>15</v>
+      </c>
+      <c r="K621">
+        <v>18</v>
+      </c>
+      <c r="L621">
+        <v>19</v>
+      </c>
+      <c r="M621">
+        <v>21</v>
+      </c>
+      <c r="N621">
+        <v>23</v>
+      </c>
+      <c r="O621">
+        <v>24</v>
+      </c>
+      <c r="P621">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="622" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A622">
+        <v>3692</v>
+      </c>
+      <c r="B622">
+        <v>2</v>
+      </c>
+      <c r="C622">
+        <v>3</v>
+      </c>
+      <c r="D622">
+        <v>5</v>
+      </c>
+      <c r="E622">
+        <v>6</v>
+      </c>
+      <c r="F622">
+        <v>7</v>
+      </c>
+      <c r="G622">
+        <v>9</v>
+      </c>
+      <c r="H622">
+        <v>10</v>
+      </c>
+      <c r="I622">
+        <v>13</v>
+      </c>
+      <c r="J622">
+        <v>14</v>
+      </c>
+      <c r="K622">
+        <v>15</v>
+      </c>
+      <c r="L622">
+        <v>19</v>
+      </c>
+      <c r="M622">
+        <v>20</v>
+      </c>
+      <c r="N622">
+        <v>23</v>
+      </c>
+      <c r="O622">
+        <v>24</v>
+      </c>
+      <c r="P622">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="623" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A623">
+        <v>3693</v>
+      </c>
+      <c r="B623">
+        <v>1</v>
+      </c>
+      <c r="C623">
+        <v>4</v>
+      </c>
+      <c r="D623">
+        <v>6</v>
+      </c>
+      <c r="E623">
+        <v>7</v>
+      </c>
+      <c r="F623">
+        <v>9</v>
+      </c>
+      <c r="G623">
+        <v>10</v>
+      </c>
+      <c r="H623">
+        <v>11</v>
+      </c>
+      <c r="I623">
+        <v>13</v>
+      </c>
+      <c r="J623">
+        <v>14</v>
+      </c>
+      <c r="K623">
+        <v>16</v>
+      </c>
+      <c r="L623">
+        <v>17</v>
+      </c>
+      <c r="M623">
+        <v>18</v>
+      </c>
+      <c r="N623">
+        <v>20</v>
+      </c>
+      <c r="O623">
+        <v>21</v>
+      </c>
+      <c r="P623">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="624" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A624">
+        <v>3694</v>
+      </c>
+      <c r="B624">
+        <v>2</v>
+      </c>
+      <c r="C624">
+        <v>4</v>
+      </c>
+      <c r="D624">
+        <v>5</v>
+      </c>
+      <c r="E624">
+        <v>7</v>
+      </c>
+      <c r="F624">
+        <v>8</v>
+      </c>
+      <c r="G624">
+        <v>9</v>
+      </c>
+      <c r="H624">
+        <v>13</v>
+      </c>
+      <c r="I624">
+        <v>14</v>
+      </c>
+      <c r="J624">
+        <v>17</v>
+      </c>
+      <c r="K624">
+        <v>18</v>
+      </c>
+      <c r="L624">
+        <v>19</v>
+      </c>
+      <c r="M624">
+        <v>20</v>
+      </c>
+      <c r="N624">
+        <v>22</v>
+      </c>
+      <c r="O624">
+        <v>23</v>
+      </c>
+      <c r="P624">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="625" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A625">
+        <v>3695</v>
+      </c>
+      <c r="B625">
+        <v>1</v>
+      </c>
+      <c r="C625">
+        <v>2</v>
+      </c>
+      <c r="D625">
+        <v>3</v>
+      </c>
+      <c r="E625">
+        <v>4</v>
+      </c>
+      <c r="F625">
+        <v>6</v>
+      </c>
+      <c r="G625">
+        <v>8</v>
+      </c>
+      <c r="H625">
+        <v>9</v>
+      </c>
+      <c r="I625">
+        <v>13</v>
+      </c>
+      <c r="J625">
+        <v>15</v>
+      </c>
+      <c r="K625">
+        <v>17</v>
+      </c>
+      <c r="L625">
+        <v>18</v>
+      </c>
+      <c r="M625">
+        <v>21</v>
+      </c>
+      <c r="N625">
+        <v>22</v>
+      </c>
+      <c r="O625">
+        <v>23</v>
+      </c>
+      <c r="P625">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="626" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A626">
+        <v>3696</v>
+      </c>
+      <c r="B626">
+        <v>2</v>
+      </c>
+      <c r="C626">
+        <v>3</v>
+      </c>
+      <c r="D626">
+        <v>5</v>
+      </c>
+      <c r="E626">
+        <v>6</v>
+      </c>
+      <c r="F626">
+        <v>7</v>
+      </c>
+      <c r="G626">
+        <v>9</v>
+      </c>
+      <c r="H626">
+        <v>11</v>
+      </c>
+      <c r="I626">
+        <v>13</v>
+      </c>
+      <c r="J626">
+        <v>15</v>
+      </c>
+      <c r="K626">
+        <v>16</v>
+      </c>
+      <c r="L626">
+        <v>17</v>
+      </c>
+      <c r="M626">
+        <v>19</v>
+      </c>
+      <c r="N626">
+        <v>21</v>
+      </c>
+      <c r="O626">
+        <v>23</v>
+      </c>
+      <c r="P626">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="627" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A627">
+        <v>3697</v>
+      </c>
+      <c r="B627">
+        <v>1</v>
+      </c>
+      <c r="C627">
+        <v>5</v>
+      </c>
+      <c r="D627">
+        <v>6</v>
+      </c>
+      <c r="E627">
+        <v>7</v>
+      </c>
+      <c r="F627">
+        <v>9</v>
+      </c>
+      <c r="G627">
+        <v>10</v>
+      </c>
+      <c r="H627">
+        <v>13</v>
+      </c>
+      <c r="I627">
+        <v>15</v>
+      </c>
+      <c r="J627">
+        <v>17</v>
+      </c>
+      <c r="K627">
+        <v>18</v>
+      </c>
+      <c r="L627">
+        <v>19</v>
+      </c>
+      <c r="M627">
+        <v>20</v>
+      </c>
+      <c r="N627">
+        <v>21</v>
+      </c>
+      <c r="O627">
+        <v>24</v>
+      </c>
+      <c r="P627">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="628" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A628">
+        <v>3698</v>
+      </c>
+      <c r="B628">
+        <v>1</v>
+      </c>
+      <c r="C628">
+        <v>3</v>
+      </c>
+      <c r="D628">
+        <v>5</v>
+      </c>
+      <c r="E628">
+        <v>6</v>
+      </c>
+      <c r="F628">
+        <v>7</v>
+      </c>
+      <c r="G628">
+        <v>8</v>
+      </c>
+      <c r="H628">
+        <v>9</v>
+      </c>
+      <c r="I628">
+        <v>10</v>
+      </c>
+      <c r="J628">
+        <v>12</v>
+      </c>
+      <c r="K628">
+        <v>13</v>
+      </c>
+      <c r="L628">
+        <v>16</v>
+      </c>
+      <c r="M628">
+        <v>18</v>
+      </c>
+      <c r="N628">
+        <v>20</v>
+      </c>
+      <c r="O628">
+        <v>21</v>
+      </c>
+      <c r="P628">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="629" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A629">
+        <v>3699</v>
+      </c>
+      <c r="B629">
+        <v>1</v>
+      </c>
+      <c r="C629">
+        <v>2</v>
+      </c>
+      <c r="D629">
+        <v>3</v>
+      </c>
+      <c r="E629">
+        <v>5</v>
+      </c>
+      <c r="F629">
+        <v>6</v>
+      </c>
+      <c r="G629">
+        <v>8</v>
+      </c>
+      <c r="H629">
+        <v>9</v>
+      </c>
+      <c r="I629">
+        <v>11</v>
+      </c>
+      <c r="J629">
+        <v>14</v>
+      </c>
+      <c r="K629">
+        <v>18</v>
+      </c>
+      <c r="L629">
+        <v>20</v>
+      </c>
+      <c r="M629">
+        <v>21</v>
+      </c>
+      <c r="N629">
+        <v>22</v>
+      </c>
+      <c r="O629">
+        <v>24</v>
+      </c>
+      <c r="P629">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="630" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A630">
+        <v>3700</v>
+      </c>
+      <c r="B630">
+        <v>1</v>
+      </c>
+      <c r="C630">
+        <v>3</v>
+      </c>
+      <c r="D630">
+        <v>7</v>
+      </c>
+      <c r="E630">
+        <v>8</v>
+      </c>
+      <c r="F630">
+        <v>9</v>
+      </c>
+      <c r="G630">
+        <v>10</v>
+      </c>
+      <c r="H630">
+        <v>12</v>
+      </c>
+      <c r="I630">
+        <v>13</v>
+      </c>
+      <c r="J630">
+        <v>14</v>
+      </c>
+      <c r="K630">
+        <v>17</v>
+      </c>
+      <c r="L630">
+        <v>18</v>
+      </c>
+      <c r="M630">
+        <v>19</v>
+      </c>
+      <c r="N630">
+        <v>20</v>
+      </c>
+      <c r="O630">
+        <v>23</v>
+      </c>
+      <c r="P630">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="631" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A631">
+        <v>3701</v>
+      </c>
+      <c r="B631">
+        <v>1</v>
+      </c>
+      <c r="C631">
+        <v>2</v>
+      </c>
+      <c r="D631">
+        <v>4</v>
+      </c>
+      <c r="E631">
+        <v>7</v>
+      </c>
+      <c r="F631">
+        <v>8</v>
+      </c>
+      <c r="G631">
+        <v>9</v>
+      </c>
+      <c r="H631">
+        <v>10</v>
+      </c>
+      <c r="I631">
+        <v>12</v>
+      </c>
+      <c r="J631">
+        <v>13</v>
+      </c>
+      <c r="K631">
+        <v>14</v>
+      </c>
+      <c r="L631">
+        <v>17</v>
+      </c>
+      <c r="M631">
+        <v>22</v>
+      </c>
+      <c r="N631">
+        <v>23</v>
+      </c>
+      <c r="O631">
+        <v>24</v>
+      </c>
+      <c r="P631">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="632" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A632">
+        <v>3702</v>
+      </c>
+      <c r="B632">
+        <v>2</v>
+      </c>
+      <c r="C632">
+        <v>3</v>
+      </c>
+      <c r="D632">
+        <v>5</v>
+      </c>
+      <c r="E632">
+        <v>9</v>
+      </c>
+      <c r="F632">
+        <v>13</v>
+      </c>
+      <c r="G632">
+        <v>14</v>
+      </c>
+      <c r="H632">
+        <v>15</v>
+      </c>
+      <c r="I632">
+        <v>16</v>
+      </c>
+      <c r="J632">
+        <v>17</v>
+      </c>
+      <c r="K632">
+        <v>18</v>
+      </c>
+      <c r="L632">
+        <v>20</v>
+      </c>
+      <c r="M632">
+        <v>21</v>
+      </c>
+      <c r="N632">
+        <v>22</v>
+      </c>
+      <c r="O632">
+        <v>23</v>
+      </c>
+      <c r="P632">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="633" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A633">
+        <v>3703</v>
+      </c>
+      <c r="B633">
+        <v>1</v>
+      </c>
+      <c r="C633">
+        <v>3</v>
+      </c>
+      <c r="D633">
+        <v>5</v>
+      </c>
+      <c r="E633">
+        <v>7</v>
+      </c>
+      <c r="F633">
+        <v>8</v>
+      </c>
+      <c r="G633">
+        <v>9</v>
+      </c>
+      <c r="H633">
+        <v>10</v>
+      </c>
+      <c r="I633">
+        <v>14</v>
+      </c>
+      <c r="J633">
+        <v>15</v>
+      </c>
+      <c r="K633">
+        <v>17</v>
+      </c>
+      <c r="L633">
+        <v>21</v>
+      </c>
+      <c r="M633">
+        <v>22</v>
+      </c>
+      <c r="N633">
+        <v>23</v>
+      </c>
+      <c r="O633">
+        <v>24</v>
+      </c>
+      <c r="P633">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="634" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A634">
+        <v>3704</v>
+      </c>
+      <c r="B634">
+        <v>1</v>
+      </c>
+      <c r="C634">
+        <v>3</v>
+      </c>
+      <c r="D634">
+        <v>4</v>
+      </c>
+      <c r="E634">
+        <v>9</v>
+      </c>
+      <c r="F634">
+        <v>10</v>
+      </c>
+      <c r="G634">
+        <v>11</v>
+      </c>
+      <c r="H634">
+        <v>12</v>
+      </c>
+      <c r="I634">
+        <v>13</v>
+      </c>
+      <c r="J634">
+        <v>14</v>
+      </c>
+      <c r="K634">
+        <v>15</v>
+      </c>
+      <c r="L634">
+        <v>19</v>
+      </c>
+      <c r="M634">
+        <v>20</v>
+      </c>
+      <c r="N634">
+        <v>22</v>
+      </c>
+      <c r="O634">
+        <v>23</v>
+      </c>
+      <c r="P634">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="635" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A635">
+        <v>3705</v>
+      </c>
+      <c r="B635">
+        <v>1</v>
+      </c>
+      <c r="C635">
+        <v>3</v>
+      </c>
+      <c r="D635">
+        <v>4</v>
+      </c>
+      <c r="E635">
+        <v>6</v>
+      </c>
+      <c r="F635">
+        <v>8</v>
+      </c>
+      <c r="G635">
+        <v>10</v>
+      </c>
+      <c r="H635">
+        <v>14</v>
+      </c>
+      <c r="I635">
+        <v>15</v>
+      </c>
+      <c r="J635">
+        <v>16</v>
+      </c>
+      <c r="K635">
+        <v>18</v>
+      </c>
+      <c r="L635">
+        <v>20</v>
+      </c>
+      <c r="M635">
+        <v>21</v>
+      </c>
+      <c r="N635">
+        <v>22</v>
+      </c>
+      <c r="O635">
+        <v>24</v>
+      </c>
+      <c r="P635">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="636" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A636">
+        <v>3706</v>
+      </c>
+      <c r="B636">
+        <v>1</v>
+      </c>
+      <c r="C636">
+        <v>4</v>
+      </c>
+      <c r="D636">
+        <v>6</v>
+      </c>
+      <c r="E636">
+        <v>8</v>
+      </c>
+      <c r="F636">
+        <v>9</v>
+      </c>
+      <c r="G636">
+        <v>10</v>
+      </c>
+      <c r="H636">
+        <v>12</v>
+      </c>
+      <c r="I636">
+        <v>14</v>
+      </c>
+      <c r="J636">
+        <v>15</v>
+      </c>
+      <c r="K636">
+        <v>16</v>
+      </c>
+      <c r="L636">
+        <v>18</v>
+      </c>
+      <c r="M636">
+        <v>21</v>
+      </c>
+      <c r="N636">
+        <v>22</v>
+      </c>
+      <c r="O636">
+        <v>24</v>
+      </c>
+      <c r="P636">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="637" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A637">
+        <v>3707</v>
+      </c>
+      <c r="B637">
+        <v>1</v>
+      </c>
+      <c r="C637">
+        <v>2</v>
+      </c>
+      <c r="D637">
+        <v>3</v>
+      </c>
+      <c r="E637">
+        <v>7</v>
+      </c>
+      <c r="F637">
+        <v>8</v>
+      </c>
+      <c r="G637">
+        <v>9</v>
+      </c>
+      <c r="H637">
+        <v>10</v>
+      </c>
+      <c r="I637">
+        <v>13</v>
+      </c>
+      <c r="J637">
+        <v>14</v>
+      </c>
+      <c r="K637">
+        <v>18</v>
+      </c>
+      <c r="L637">
+        <v>20</v>
+      </c>
+      <c r="M637">
+        <v>21</v>
+      </c>
+      <c r="N637">
+        <v>22</v>
+      </c>
+      <c r="O637">
+        <v>23</v>
+      </c>
+      <c r="P637">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="638" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A638">
+        <v>3708</v>
+      </c>
+      <c r="B638">
+        <v>1</v>
+      </c>
+      <c r="C638">
+        <v>2</v>
+      </c>
+      <c r="D638">
+        <v>4</v>
+      </c>
+      <c r="E638">
+        <v>5</v>
+      </c>
+      <c r="F638">
+        <v>6</v>
+      </c>
+      <c r="G638">
+        <v>8</v>
+      </c>
+      <c r="H638">
+        <v>9</v>
+      </c>
+      <c r="I638">
+        <v>12</v>
+      </c>
+      <c r="J638">
+        <v>16</v>
+      </c>
+      <c r="K638">
+        <v>17</v>
+      </c>
+      <c r="L638">
+        <v>18</v>
+      </c>
+      <c r="M638">
+        <v>19</v>
+      </c>
+      <c r="N638">
+        <v>21</v>
+      </c>
+      <c r="O638">
+        <v>23</v>
+      </c>
+      <c r="P638">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="639" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A639">
+        <v>3709</v>
+      </c>
+      <c r="B639">
+        <v>1</v>
+      </c>
+      <c r="C639">
+        <v>4</v>
+      </c>
+      <c r="D639">
+        <v>6</v>
+      </c>
+      <c r="E639">
+        <v>7</v>
+      </c>
+      <c r="F639">
+        <v>9</v>
+      </c>
+      <c r="G639">
+        <v>10</v>
+      </c>
+      <c r="H639">
+        <v>11</v>
+      </c>
+      <c r="I639">
+        <v>14</v>
+      </c>
+      <c r="J639">
+        <v>15</v>
+      </c>
+      <c r="K639">
+        <v>18</v>
+      </c>
+      <c r="L639">
+        <v>19</v>
+      </c>
+      <c r="M639">
+        <v>20</v>
+      </c>
+      <c r="N639">
+        <v>23</v>
+      </c>
+      <c r="O639">
+        <v>24</v>
+      </c>
+      <c r="P639">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="640" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A640">
+        <v>3710</v>
+      </c>
+      <c r="B640">
+        <v>1</v>
+      </c>
+      <c r="C640">
+        <v>2</v>
+      </c>
+      <c r="D640">
+        <v>3</v>
+      </c>
+      <c r="E640">
+        <v>4</v>
+      </c>
+      <c r="F640">
+        <v>5</v>
+      </c>
+      <c r="G640">
+        <v>6</v>
+      </c>
+      <c r="H640">
+        <v>9</v>
+      </c>
+      <c r="I640">
+        <v>12</v>
+      </c>
+      <c r="J640">
+        <v>13</v>
+      </c>
+      <c r="K640">
+        <v>14</v>
+      </c>
+      <c r="L640">
+        <v>15</v>
+      </c>
+      <c r="M640">
+        <v>16</v>
+      </c>
+      <c r="N640">
+        <v>17</v>
+      </c>
+      <c r="O640">
+        <v>18</v>
+      </c>
+      <c r="P640">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="641" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A641">
+        <v>3711</v>
+      </c>
+      <c r="B641">
+        <v>1</v>
+      </c>
+      <c r="C641">
+        <v>5</v>
+      </c>
+      <c r="D641">
+        <v>6</v>
+      </c>
+      <c r="E641">
+        <v>8</v>
+      </c>
+      <c r="F641">
+        <v>9</v>
+      </c>
+      <c r="G641">
+        <v>10</v>
+      </c>
+      <c r="H641">
+        <v>12</v>
+      </c>
+      <c r="I641">
+        <v>13</v>
+      </c>
+      <c r="J641">
+        <v>15</v>
+      </c>
+      <c r="K641">
+        <v>16</v>
+      </c>
+      <c r="L641">
+        <v>17</v>
+      </c>
+      <c r="M641">
+        <v>20</v>
+      </c>
+      <c r="N641">
+        <v>22</v>
+      </c>
+      <c r="O641">
+        <v>24</v>
+      </c>
+      <c r="P641">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="642" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A642">
+        <v>3712</v>
+      </c>
+      <c r="B642">
+        <v>1</v>
+      </c>
+      <c r="C642">
+        <v>3</v>
+      </c>
+      <c r="D642">
+        <v>4</v>
+      </c>
+      <c r="E642">
+        <v>6</v>
+      </c>
+      <c r="F642">
+        <v>13</v>
+      </c>
+      <c r="G642">
+        <v>14</v>
+      </c>
+      <c r="H642">
+        <v>15</v>
+      </c>
+      <c r="I642">
+        <v>16</v>
+      </c>
+      <c r="J642">
+        <v>18</v>
+      </c>
+      <c r="K642">
+        <v>19</v>
+      </c>
+      <c r="L642">
+        <v>20</v>
+      </c>
+      <c r="M642">
+        <v>21</v>
+      </c>
+      <c r="N642">
+        <v>22</v>
+      </c>
+      <c r="O642">
+        <v>23</v>
+      </c>
+      <c r="P642">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="643" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A643">
+        <v>3713</v>
+      </c>
+      <c r="B643">
+        <v>2</v>
+      </c>
+      <c r="C643">
+        <v>4</v>
+      </c>
+      <c r="D643">
+        <v>5</v>
+      </c>
+      <c r="E643">
+        <v>6</v>
+      </c>
+      <c r="F643">
+        <v>7</v>
+      </c>
+      <c r="G643">
+        <v>8</v>
+      </c>
+      <c r="H643">
+        <v>9</v>
+      </c>
+      <c r="I643">
+        <v>11</v>
+      </c>
+      <c r="J643">
+        <v>12</v>
+      </c>
+      <c r="K643">
+        <v>13</v>
+      </c>
+      <c r="L643">
+        <v>14</v>
+      </c>
+      <c r="M643">
+        <v>15</v>
+      </c>
+      <c r="N643">
+        <v>19</v>
+      </c>
+      <c r="O643">
+        <v>20</v>
+      </c>
+      <c r="P643">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="644" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A644">
+        <v>3714</v>
+      </c>
+      <c r="B644">
+        <v>3</v>
+      </c>
+      <c r="C644">
+        <v>4</v>
+      </c>
+      <c r="D644">
+        <v>5</v>
+      </c>
+      <c r="E644">
+        <v>6</v>
+      </c>
+      <c r="F644">
+        <v>9</v>
+      </c>
+      <c r="G644">
+        <v>10</v>
+      </c>
+      <c r="H644">
+        <v>11</v>
+      </c>
+      <c r="I644">
+        <v>12</v>
+      </c>
+      <c r="J644">
+        <v>13</v>
+      </c>
+      <c r="K644">
+        <v>14</v>
+      </c>
+      <c r="L644">
+        <v>15</v>
+      </c>
+      <c r="M644">
+        <v>16</v>
+      </c>
+      <c r="N644">
+        <v>18</v>
+      </c>
+      <c r="O644">
+        <v>19</v>
+      </c>
+      <c r="P644">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="645" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A645">
+        <v>3715</v>
+      </c>
+      <c r="B645">
+        <v>3</v>
+      </c>
+      <c r="C645">
+        <v>5</v>
+      </c>
+      <c r="D645">
+        <v>6</v>
+      </c>
+      <c r="E645">
+        <v>9</v>
+      </c>
+      <c r="F645">
+        <v>11</v>
+      </c>
+      <c r="G645">
+        <v>12</v>
+      </c>
+      <c r="H645">
+        <v>14</v>
+      </c>
+      <c r="I645">
+        <v>16</v>
+      </c>
+      <c r="J645">
+        <v>18</v>
+      </c>
+      <c r="K645">
+        <v>20</v>
+      </c>
+      <c r="L645">
+        <v>21</v>
+      </c>
+      <c r="M645">
+        <v>22</v>
+      </c>
+      <c r="N645">
+        <v>23</v>
+      </c>
+      <c r="O645">
+        <v>24</v>
+      </c>
+      <c r="P645">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="646" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A646">
+        <v>3716</v>
+      </c>
+      <c r="B646">
+        <v>1</v>
+      </c>
+      <c r="C646">
+        <v>2</v>
+      </c>
+      <c r="D646">
+        <v>4</v>
+      </c>
+      <c r="E646">
+        <v>5</v>
+      </c>
+      <c r="F646">
+        <v>7</v>
+      </c>
+      <c r="G646">
+        <v>11</v>
+      </c>
+      <c r="H646">
+        <v>12</v>
+      </c>
+      <c r="I646">
+        <v>15</v>
+      </c>
+      <c r="J646">
+        <v>17</v>
+      </c>
+      <c r="K646">
+        <v>18</v>
+      </c>
+      <c r="L646">
+        <v>21</v>
+      </c>
+      <c r="M646">
+        <v>22</v>
+      </c>
+      <c r="N646">
+        <v>23</v>
+      </c>
+      <c r="O646">
+        <v>24</v>
+      </c>
+      <c r="P646">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -31108,15 +32967,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -31128,6 +32978,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31147,14 +33005,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C5D69A-20AE-437B-87DF-72A535F80DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827D77CF-A44A-41B3-B842-50E21354FD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59010" yWindow="120" windowWidth="15285" windowHeight="13365" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58335" yWindow="735" windowWidth="16230" windowHeight="15165" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P646"/>
+  <dimension ref="A1:P650"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -32785,18 +32785,219 @@
         <v>25</v>
       </c>
     </row>
+    <row r="647" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A647">
+        <v>3717</v>
+      </c>
+      <c r="B647">
+        <v>1</v>
+      </c>
+      <c r="C647">
+        <v>2</v>
+      </c>
+      <c r="D647">
+        <v>4</v>
+      </c>
+      <c r="E647">
+        <v>5</v>
+      </c>
+      <c r="F647">
+        <v>6</v>
+      </c>
+      <c r="G647">
+        <v>7</v>
+      </c>
+      <c r="H647">
+        <v>9</v>
+      </c>
+      <c r="I647">
+        <v>10</v>
+      </c>
+      <c r="J647">
+        <v>11</v>
+      </c>
+      <c r="K647">
+        <v>14</v>
+      </c>
+      <c r="L647">
+        <v>15</v>
+      </c>
+      <c r="M647">
+        <v>17</v>
+      </c>
+      <c r="N647">
+        <v>18</v>
+      </c>
+      <c r="O647">
+        <v>20</v>
+      </c>
+      <c r="P647">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="648" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A648">
+        <v>3718</v>
+      </c>
+      <c r="B648">
+        <v>1</v>
+      </c>
+      <c r="C648">
+        <v>5</v>
+      </c>
+      <c r="D648">
+        <v>7</v>
+      </c>
+      <c r="E648">
+        <v>9</v>
+      </c>
+      <c r="F648">
+        <v>11</v>
+      </c>
+      <c r="G648">
+        <v>12</v>
+      </c>
+      <c r="H648">
+        <v>14</v>
+      </c>
+      <c r="I648">
+        <v>16</v>
+      </c>
+      <c r="J648">
+        <v>17</v>
+      </c>
+      <c r="K648">
+        <v>18</v>
+      </c>
+      <c r="L648">
+        <v>19</v>
+      </c>
+      <c r="M648">
+        <v>20</v>
+      </c>
+      <c r="N648">
+        <v>21</v>
+      </c>
+      <c r="O648">
+        <v>22</v>
+      </c>
+      <c r="P648">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="649" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A649">
+        <v>3719</v>
+      </c>
+      <c r="B649">
+        <v>2</v>
+      </c>
+      <c r="C649">
+        <v>3</v>
+      </c>
+      <c r="D649">
+        <v>4</v>
+      </c>
+      <c r="E649">
+        <v>8</v>
+      </c>
+      <c r="F649">
+        <v>10</v>
+      </c>
+      <c r="G649">
+        <v>11</v>
+      </c>
+      <c r="H649">
+        <v>12</v>
+      </c>
+      <c r="I649">
+        <v>14</v>
+      </c>
+      <c r="J649">
+        <v>15</v>
+      </c>
+      <c r="K649">
+        <v>18</v>
+      </c>
+      <c r="L649">
+        <v>19</v>
+      </c>
+      <c r="M649">
+        <v>21</v>
+      </c>
+      <c r="N649">
+        <v>22</v>
+      </c>
+      <c r="O649">
+        <v>23</v>
+      </c>
+      <c r="P649">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="650" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A650">
+        <v>3720</v>
+      </c>
+      <c r="B650">
+        <v>1</v>
+      </c>
+      <c r="C650">
+        <v>5</v>
+      </c>
+      <c r="D650">
+        <v>7</v>
+      </c>
+      <c r="E650">
+        <v>8</v>
+      </c>
+      <c r="F650">
+        <v>9</v>
+      </c>
+      <c r="G650">
+        <v>10</v>
+      </c>
+      <c r="H650">
+        <v>11</v>
+      </c>
+      <c r="I650">
+        <v>13</v>
+      </c>
+      <c r="J650">
+        <v>15</v>
+      </c>
+      <c r="K650">
+        <v>16</v>
+      </c>
+      <c r="L650">
+        <v>17</v>
+      </c>
+      <c r="M650">
+        <v>18</v>
+      </c>
+      <c r="N650">
+        <v>20</v>
+      </c>
+      <c r="O650">
+        <v>22</v>
+      </c>
+      <c r="P650">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32968,19 +33169,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -33006,12 +33209,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827D77CF-A44A-41B3-B842-50E21354FD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DFD9C6-FA04-4BD7-9470-029CF90C30EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58335" yWindow="735" windowWidth="16230" windowHeight="15165" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57540" yWindow="120" windowWidth="19515" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,6 +156,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P650"/>
+  <dimension ref="A1:P652"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -32985,22 +32987,112 @@
         <v>24</v>
       </c>
     </row>
+    <row r="651" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A651" s="5">
+        <v>3721</v>
+      </c>
+      <c r="B651" s="6">
+        <v>1</v>
+      </c>
+      <c r="C651" s="6">
+        <v>3</v>
+      </c>
+      <c r="D651" s="6">
+        <v>4</v>
+      </c>
+      <c r="E651" s="6">
+        <v>5</v>
+      </c>
+      <c r="F651" s="6">
+        <v>7</v>
+      </c>
+      <c r="G651" s="6">
+        <v>8</v>
+      </c>
+      <c r="H651" s="6">
+        <v>10</v>
+      </c>
+      <c r="I651" s="6">
+        <v>11</v>
+      </c>
+      <c r="J651" s="6">
+        <v>12</v>
+      </c>
+      <c r="K651" s="6">
+        <v>14</v>
+      </c>
+      <c r="L651" s="6">
+        <v>15</v>
+      </c>
+      <c r="M651" s="6">
+        <v>20</v>
+      </c>
+      <c r="N651" s="6">
+        <v>21</v>
+      </c>
+      <c r="O651" s="6">
+        <v>23</v>
+      </c>
+      <c r="P651" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="652" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A652" s="5">
+        <v>3722</v>
+      </c>
+      <c r="B652" s="6">
+        <v>2</v>
+      </c>
+      <c r="C652" s="6">
+        <v>3</v>
+      </c>
+      <c r="D652" s="6">
+        <v>5</v>
+      </c>
+      <c r="E652" s="6">
+        <v>6</v>
+      </c>
+      <c r="F652" s="6">
+        <v>9</v>
+      </c>
+      <c r="G652" s="6">
+        <v>10</v>
+      </c>
+      <c r="H652" s="6">
+        <v>11</v>
+      </c>
+      <c r="I652" s="6">
+        <v>12</v>
+      </c>
+      <c r="J652" s="6">
+        <v>13</v>
+      </c>
+      <c r="K652" s="6">
+        <v>14</v>
+      </c>
+      <c r="L652" s="6">
+        <v>15</v>
+      </c>
+      <c r="M652" s="6">
+        <v>17</v>
+      </c>
+      <c r="N652" s="6">
+        <v>19</v>
+      </c>
+      <c r="O652" s="6">
+        <v>20</v>
+      </c>
+      <c r="P652" s="6">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -33168,6 +33260,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -33178,17 +33280,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33208,6 +33299,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DFD9C6-FA04-4BD7-9470-029CF90C30EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771FF0FE-D1B5-41AD-A143-175009050442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57540" yWindow="120" windowWidth="19515" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="67755" yWindow="1935" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P652"/>
+  <dimension ref="A1:P659"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -32988,103 +32988,453 @@
       </c>
     </row>
     <row r="651" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A651" s="5">
+      <c r="A651">
         <v>3721</v>
       </c>
-      <c r="B651" s="6">
-        <v>1</v>
-      </c>
-      <c r="C651" s="6">
-        <v>3</v>
-      </c>
-      <c r="D651" s="6">
-        <v>4</v>
-      </c>
-      <c r="E651" s="6">
-        <v>5</v>
-      </c>
-      <c r="F651" s="6">
-        <v>7</v>
-      </c>
-      <c r="G651" s="6">
-        <v>8</v>
-      </c>
-      <c r="H651" s="6">
-        <v>10</v>
-      </c>
-      <c r="I651" s="6">
-        <v>11</v>
-      </c>
-      <c r="J651" s="6">
-        <v>12</v>
-      </c>
-      <c r="K651" s="6">
-        <v>14</v>
-      </c>
-      <c r="L651" s="6">
-        <v>15</v>
-      </c>
-      <c r="M651" s="6">
-        <v>20</v>
-      </c>
-      <c r="N651" s="6">
-        <v>21</v>
-      </c>
-      <c r="O651" s="6">
-        <v>23</v>
-      </c>
-      <c r="P651" s="6">
+      <c r="B651">
+        <v>1</v>
+      </c>
+      <c r="C651">
+        <v>3</v>
+      </c>
+      <c r="D651">
+        <v>4</v>
+      </c>
+      <c r="E651">
+        <v>5</v>
+      </c>
+      <c r="F651">
+        <v>7</v>
+      </c>
+      <c r="G651">
+        <v>8</v>
+      </c>
+      <c r="H651">
+        <v>10</v>
+      </c>
+      <c r="I651">
+        <v>11</v>
+      </c>
+      <c r="J651">
+        <v>12</v>
+      </c>
+      <c r="K651">
+        <v>14</v>
+      </c>
+      <c r="L651">
+        <v>15</v>
+      </c>
+      <c r="M651">
+        <v>20</v>
+      </c>
+      <c r="N651">
+        <v>21</v>
+      </c>
+      <c r="O651">
+        <v>23</v>
+      </c>
+      <c r="P651">
         <v>24</v>
       </c>
     </row>
     <row r="652" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A652" s="5">
+      <c r="A652">
         <v>3722</v>
       </c>
-      <c r="B652" s="6">
-        <v>2</v>
-      </c>
-      <c r="C652" s="6">
-        <v>3</v>
-      </c>
-      <c r="D652" s="6">
-        <v>5</v>
-      </c>
-      <c r="E652" s="6">
-        <v>6</v>
-      </c>
-      <c r="F652" s="6">
-        <v>9</v>
-      </c>
-      <c r="G652" s="6">
-        <v>10</v>
-      </c>
-      <c r="H652" s="6">
-        <v>11</v>
-      </c>
-      <c r="I652" s="6">
-        <v>12</v>
-      </c>
-      <c r="J652" s="6">
-        <v>13</v>
-      </c>
-      <c r="K652" s="6">
-        <v>14</v>
-      </c>
-      <c r="L652" s="6">
-        <v>15</v>
-      </c>
-      <c r="M652" s="6">
-        <v>17</v>
-      </c>
-      <c r="N652" s="6">
-        <v>19</v>
-      </c>
-      <c r="O652" s="6">
-        <v>20</v>
-      </c>
-      <c r="P652" s="6">
-        <v>23</v>
+      <c r="B652">
+        <v>2</v>
+      </c>
+      <c r="C652">
+        <v>3</v>
+      </c>
+      <c r="D652">
+        <v>5</v>
+      </c>
+      <c r="E652">
+        <v>6</v>
+      </c>
+      <c r="F652">
+        <v>9</v>
+      </c>
+      <c r="G652">
+        <v>10</v>
+      </c>
+      <c r="H652">
+        <v>11</v>
+      </c>
+      <c r="I652">
+        <v>12</v>
+      </c>
+      <c r="J652">
+        <v>13</v>
+      </c>
+      <c r="K652">
+        <v>14</v>
+      </c>
+      <c r="L652">
+        <v>15</v>
+      </c>
+      <c r="M652">
+        <v>17</v>
+      </c>
+      <c r="N652">
+        <v>19</v>
+      </c>
+      <c r="O652">
+        <v>20</v>
+      </c>
+      <c r="P652">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="653" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A653" s="5">
+        <v>3723</v>
+      </c>
+      <c r="B653" s="6">
+        <v>2</v>
+      </c>
+      <c r="C653" s="6">
+        <v>4</v>
+      </c>
+      <c r="D653" s="6">
+        <v>5</v>
+      </c>
+      <c r="E653" s="6">
+        <v>6</v>
+      </c>
+      <c r="F653" s="6">
+        <v>7</v>
+      </c>
+      <c r="G653" s="6">
+        <v>10</v>
+      </c>
+      <c r="H653" s="6">
+        <v>12</v>
+      </c>
+      <c r="I653" s="6">
+        <v>15</v>
+      </c>
+      <c r="J653" s="6">
+        <v>17</v>
+      </c>
+      <c r="K653" s="6">
+        <v>18</v>
+      </c>
+      <c r="L653" s="6">
+        <v>19</v>
+      </c>
+      <c r="M653" s="6">
+        <v>20</v>
+      </c>
+      <c r="N653" s="6">
+        <v>22</v>
+      </c>
+      <c r="O653" s="6">
+        <v>23</v>
+      </c>
+      <c r="P653" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="654" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A654" s="5">
+        <v>3724</v>
+      </c>
+      <c r="B654" s="6">
+        <v>1</v>
+      </c>
+      <c r="C654" s="6">
+        <v>2</v>
+      </c>
+      <c r="D654" s="6">
+        <v>3</v>
+      </c>
+      <c r="E654" s="6">
+        <v>5</v>
+      </c>
+      <c r="F654" s="6">
+        <v>6</v>
+      </c>
+      <c r="G654" s="6">
+        <v>7</v>
+      </c>
+      <c r="H654" s="6">
+        <v>12</v>
+      </c>
+      <c r="I654" s="6">
+        <v>15</v>
+      </c>
+      <c r="J654" s="6">
+        <v>16</v>
+      </c>
+      <c r="K654" s="6">
+        <v>17</v>
+      </c>
+      <c r="L654" s="6">
+        <v>19</v>
+      </c>
+      <c r="M654" s="6">
+        <v>21</v>
+      </c>
+      <c r="N654" s="6">
+        <v>22</v>
+      </c>
+      <c r="O654" s="6">
+        <v>24</v>
+      </c>
+      <c r="P654" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="655" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A655" s="5">
+        <v>3725</v>
+      </c>
+      <c r="B655" s="6">
+        <v>1</v>
+      </c>
+      <c r="C655" s="6">
+        <v>2</v>
+      </c>
+      <c r="D655" s="6">
+        <v>4</v>
+      </c>
+      <c r="E655" s="6">
+        <v>5</v>
+      </c>
+      <c r="F655" s="6">
+        <v>6</v>
+      </c>
+      <c r="G655" s="6">
+        <v>8</v>
+      </c>
+      <c r="H655" s="6">
+        <v>11</v>
+      </c>
+      <c r="I655" s="6">
+        <v>13</v>
+      </c>
+      <c r="J655" s="6">
+        <v>14</v>
+      </c>
+      <c r="K655" s="6">
+        <v>16</v>
+      </c>
+      <c r="L655" s="6">
+        <v>17</v>
+      </c>
+      <c r="M655" s="6">
+        <v>19</v>
+      </c>
+      <c r="N655" s="6">
+        <v>21</v>
+      </c>
+      <c r="O655" s="6">
+        <v>24</v>
+      </c>
+      <c r="P655" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="656" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A656" s="5">
+        <v>3726</v>
+      </c>
+      <c r="B656" s="6">
+        <v>2</v>
+      </c>
+      <c r="C656" s="6">
+        <v>5</v>
+      </c>
+      <c r="D656" s="6">
+        <v>6</v>
+      </c>
+      <c r="E656" s="6">
+        <v>7</v>
+      </c>
+      <c r="F656" s="6">
+        <v>10</v>
+      </c>
+      <c r="G656" s="6">
+        <v>13</v>
+      </c>
+      <c r="H656" s="6">
+        <v>14</v>
+      </c>
+      <c r="I656" s="6">
+        <v>17</v>
+      </c>
+      <c r="J656" s="6">
+        <v>18</v>
+      </c>
+      <c r="K656" s="6">
+        <v>19</v>
+      </c>
+      <c r="L656" s="6">
+        <v>20</v>
+      </c>
+      <c r="M656" s="6">
+        <v>21</v>
+      </c>
+      <c r="N656" s="6">
+        <v>22</v>
+      </c>
+      <c r="O656" s="6">
+        <v>24</v>
+      </c>
+      <c r="P656" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="657" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A657" s="5">
+        <v>3727</v>
+      </c>
+      <c r="B657" s="6">
+        <v>1</v>
+      </c>
+      <c r="C657" s="6">
+        <v>2</v>
+      </c>
+      <c r="D657" s="6">
+        <v>3</v>
+      </c>
+      <c r="E657" s="6">
+        <v>4</v>
+      </c>
+      <c r="F657" s="6">
+        <v>5</v>
+      </c>
+      <c r="G657" s="6">
+        <v>9</v>
+      </c>
+      <c r="H657" s="6">
+        <v>10</v>
+      </c>
+      <c r="I657" s="6">
+        <v>11</v>
+      </c>
+      <c r="J657" s="6">
+        <v>13</v>
+      </c>
+      <c r="K657" s="6">
+        <v>14</v>
+      </c>
+      <c r="L657" s="6">
+        <v>16</v>
+      </c>
+      <c r="M657" s="6">
+        <v>18</v>
+      </c>
+      <c r="N657" s="6">
+        <v>19</v>
+      </c>
+      <c r="O657" s="6">
+        <v>22</v>
+      </c>
+      <c r="P657" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="658" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A658" s="5">
+        <v>3728</v>
+      </c>
+      <c r="B658" s="6">
+        <v>1</v>
+      </c>
+      <c r="C658" s="6">
+        <v>2</v>
+      </c>
+      <c r="D658" s="6">
+        <v>3</v>
+      </c>
+      <c r="E658" s="6">
+        <v>6</v>
+      </c>
+      <c r="F658" s="6">
+        <v>7</v>
+      </c>
+      <c r="G658" s="6">
+        <v>8</v>
+      </c>
+      <c r="H658" s="6">
+        <v>10</v>
+      </c>
+      <c r="I658" s="6">
+        <v>11</v>
+      </c>
+      <c r="J658" s="6">
+        <v>16</v>
+      </c>
+      <c r="K658" s="6">
+        <v>17</v>
+      </c>
+      <c r="L658" s="6">
+        <v>19</v>
+      </c>
+      <c r="M658" s="6">
+        <v>21</v>
+      </c>
+      <c r="N658" s="6">
+        <v>22</v>
+      </c>
+      <c r="O658" s="6">
+        <v>23</v>
+      </c>
+      <c r="P658" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="659" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A659" s="5">
+        <v>3729</v>
+      </c>
+      <c r="B659" s="6">
+        <v>1</v>
+      </c>
+      <c r="C659" s="6">
+        <v>2</v>
+      </c>
+      <c r="D659" s="6">
+        <v>3</v>
+      </c>
+      <c r="E659" s="6">
+        <v>5</v>
+      </c>
+      <c r="F659" s="6">
+        <v>6</v>
+      </c>
+      <c r="G659" s="6">
+        <v>11</v>
+      </c>
+      <c r="H659" s="6">
+        <v>12</v>
+      </c>
+      <c r="I659" s="6">
+        <v>13</v>
+      </c>
+      <c r="J659" s="6">
+        <v>14</v>
+      </c>
+      <c r="K659" s="6">
+        <v>15</v>
+      </c>
+      <c r="L659" s="6">
+        <v>16</v>
+      </c>
+      <c r="M659" s="6">
+        <v>18</v>
+      </c>
+      <c r="N659" s="6">
+        <v>20</v>
+      </c>
+      <c r="O659" s="6">
+        <v>21</v>
+      </c>
+      <c r="P659" s="6">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -33093,6 +33443,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -33260,16 +33620,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -33280,6 +33630,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33299,17 +33660,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771FF0FE-D1B5-41AD-A143-175009050442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB2F879-6E6F-433D-9684-3FA33F8C2B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67755" yWindow="1935" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="61245" yWindow="870" windowWidth="21360" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P659"/>
+  <dimension ref="A1:P662"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -33088,353 +33088,503 @@
       </c>
     </row>
     <row r="653" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A653" s="5">
+      <c r="A653">
         <v>3723</v>
       </c>
-      <c r="B653" s="6">
-        <v>2</v>
-      </c>
-      <c r="C653" s="6">
-        <v>4</v>
-      </c>
-      <c r="D653" s="6">
-        <v>5</v>
-      </c>
-      <c r="E653" s="6">
-        <v>6</v>
-      </c>
-      <c r="F653" s="6">
-        <v>7</v>
-      </c>
-      <c r="G653" s="6">
-        <v>10</v>
-      </c>
-      <c r="H653" s="6">
-        <v>12</v>
-      </c>
-      <c r="I653" s="6">
-        <v>15</v>
-      </c>
-      <c r="J653" s="6">
-        <v>17</v>
-      </c>
-      <c r="K653" s="6">
-        <v>18</v>
-      </c>
-      <c r="L653" s="6">
-        <v>19</v>
-      </c>
-      <c r="M653" s="6">
-        <v>20</v>
-      </c>
-      <c r="N653" s="6">
-        <v>22</v>
-      </c>
-      <c r="O653" s="6">
-        <v>23</v>
-      </c>
-      <c r="P653" s="6">
+      <c r="B653">
+        <v>2</v>
+      </c>
+      <c r="C653">
+        <v>4</v>
+      </c>
+      <c r="D653">
+        <v>5</v>
+      </c>
+      <c r="E653">
+        <v>6</v>
+      </c>
+      <c r="F653">
+        <v>7</v>
+      </c>
+      <c r="G653">
+        <v>10</v>
+      </c>
+      <c r="H653">
+        <v>12</v>
+      </c>
+      <c r="I653">
+        <v>15</v>
+      </c>
+      <c r="J653">
+        <v>17</v>
+      </c>
+      <c r="K653">
+        <v>18</v>
+      </c>
+      <c r="L653">
+        <v>19</v>
+      </c>
+      <c r="M653">
+        <v>20</v>
+      </c>
+      <c r="N653">
+        <v>22</v>
+      </c>
+      <c r="O653">
+        <v>23</v>
+      </c>
+      <c r="P653">
         <v>25</v>
       </c>
     </row>
     <row r="654" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A654" s="5">
+      <c r="A654">
         <v>3724</v>
       </c>
-      <c r="B654" s="6">
-        <v>1</v>
-      </c>
-      <c r="C654" s="6">
-        <v>2</v>
-      </c>
-      <c r="D654" s="6">
-        <v>3</v>
-      </c>
-      <c r="E654" s="6">
-        <v>5</v>
-      </c>
-      <c r="F654" s="6">
-        <v>6</v>
-      </c>
-      <c r="G654" s="6">
-        <v>7</v>
-      </c>
-      <c r="H654" s="6">
-        <v>12</v>
-      </c>
-      <c r="I654" s="6">
-        <v>15</v>
-      </c>
-      <c r="J654" s="6">
-        <v>16</v>
-      </c>
-      <c r="K654" s="6">
-        <v>17</v>
-      </c>
-      <c r="L654" s="6">
-        <v>19</v>
-      </c>
-      <c r="M654" s="6">
-        <v>21</v>
-      </c>
-      <c r="N654" s="6">
-        <v>22</v>
-      </c>
-      <c r="O654" s="6">
-        <v>24</v>
-      </c>
-      <c r="P654" s="6">
+      <c r="B654">
+        <v>1</v>
+      </c>
+      <c r="C654">
+        <v>2</v>
+      </c>
+      <c r="D654">
+        <v>3</v>
+      </c>
+      <c r="E654">
+        <v>5</v>
+      </c>
+      <c r="F654">
+        <v>6</v>
+      </c>
+      <c r="G654">
+        <v>7</v>
+      </c>
+      <c r="H654">
+        <v>12</v>
+      </c>
+      <c r="I654">
+        <v>15</v>
+      </c>
+      <c r="J654">
+        <v>16</v>
+      </c>
+      <c r="K654">
+        <v>17</v>
+      </c>
+      <c r="L654">
+        <v>19</v>
+      </c>
+      <c r="M654">
+        <v>21</v>
+      </c>
+      <c r="N654">
+        <v>22</v>
+      </c>
+      <c r="O654">
+        <v>24</v>
+      </c>
+      <c r="P654">
         <v>25</v>
       </c>
     </row>
     <row r="655" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A655" s="5">
+      <c r="A655">
         <v>3725</v>
       </c>
-      <c r="B655" s="6">
-        <v>1</v>
-      </c>
-      <c r="C655" s="6">
-        <v>2</v>
-      </c>
-      <c r="D655" s="6">
-        <v>4</v>
-      </c>
-      <c r="E655" s="6">
-        <v>5</v>
-      </c>
-      <c r="F655" s="6">
-        <v>6</v>
-      </c>
-      <c r="G655" s="6">
-        <v>8</v>
-      </c>
-      <c r="H655" s="6">
-        <v>11</v>
-      </c>
-      <c r="I655" s="6">
-        <v>13</v>
-      </c>
-      <c r="J655" s="6">
-        <v>14</v>
-      </c>
-      <c r="K655" s="6">
-        <v>16</v>
-      </c>
-      <c r="L655" s="6">
-        <v>17</v>
-      </c>
-      <c r="M655" s="6">
-        <v>19</v>
-      </c>
-      <c r="N655" s="6">
-        <v>21</v>
-      </c>
-      <c r="O655" s="6">
-        <v>24</v>
-      </c>
-      <c r="P655" s="6">
+      <c r="B655">
+        <v>1</v>
+      </c>
+      <c r="C655">
+        <v>2</v>
+      </c>
+      <c r="D655">
+        <v>4</v>
+      </c>
+      <c r="E655">
+        <v>5</v>
+      </c>
+      <c r="F655">
+        <v>6</v>
+      </c>
+      <c r="G655">
+        <v>8</v>
+      </c>
+      <c r="H655">
+        <v>11</v>
+      </c>
+      <c r="I655">
+        <v>13</v>
+      </c>
+      <c r="J655">
+        <v>14</v>
+      </c>
+      <c r="K655">
+        <v>16</v>
+      </c>
+      <c r="L655">
+        <v>17</v>
+      </c>
+      <c r="M655">
+        <v>19</v>
+      </c>
+      <c r="N655">
+        <v>21</v>
+      </c>
+      <c r="O655">
+        <v>24</v>
+      </c>
+      <c r="P655">
         <v>25</v>
       </c>
     </row>
     <row r="656" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A656" s="5">
+      <c r="A656">
         <v>3726</v>
       </c>
-      <c r="B656" s="6">
-        <v>2</v>
-      </c>
-      <c r="C656" s="6">
-        <v>5</v>
-      </c>
-      <c r="D656" s="6">
-        <v>6</v>
-      </c>
-      <c r="E656" s="6">
-        <v>7</v>
-      </c>
-      <c r="F656" s="6">
-        <v>10</v>
-      </c>
-      <c r="G656" s="6">
-        <v>13</v>
-      </c>
-      <c r="H656" s="6">
-        <v>14</v>
-      </c>
-      <c r="I656" s="6">
-        <v>17</v>
-      </c>
-      <c r="J656" s="6">
-        <v>18</v>
-      </c>
-      <c r="K656" s="6">
-        <v>19</v>
-      </c>
-      <c r="L656" s="6">
-        <v>20</v>
-      </c>
-      <c r="M656" s="6">
-        <v>21</v>
-      </c>
-      <c r="N656" s="6">
-        <v>22</v>
-      </c>
-      <c r="O656" s="6">
-        <v>24</v>
-      </c>
-      <c r="P656" s="6">
+      <c r="B656">
+        <v>2</v>
+      </c>
+      <c r="C656">
+        <v>5</v>
+      </c>
+      <c r="D656">
+        <v>6</v>
+      </c>
+      <c r="E656">
+        <v>7</v>
+      </c>
+      <c r="F656">
+        <v>10</v>
+      </c>
+      <c r="G656">
+        <v>13</v>
+      </c>
+      <c r="H656">
+        <v>14</v>
+      </c>
+      <c r="I656">
+        <v>17</v>
+      </c>
+      <c r="J656">
+        <v>18</v>
+      </c>
+      <c r="K656">
+        <v>19</v>
+      </c>
+      <c r="L656">
+        <v>20</v>
+      </c>
+      <c r="M656">
+        <v>21</v>
+      </c>
+      <c r="N656">
+        <v>22</v>
+      </c>
+      <c r="O656">
+        <v>24</v>
+      </c>
+      <c r="P656">
         <v>25</v>
       </c>
     </row>
     <row r="657" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A657" s="5">
+      <c r="A657">
         <v>3727</v>
       </c>
-      <c r="B657" s="6">
-        <v>1</v>
-      </c>
-      <c r="C657" s="6">
-        <v>2</v>
-      </c>
-      <c r="D657" s="6">
-        <v>3</v>
-      </c>
-      <c r="E657" s="6">
-        <v>4</v>
-      </c>
-      <c r="F657" s="6">
-        <v>5</v>
-      </c>
-      <c r="G657" s="6">
-        <v>9</v>
-      </c>
-      <c r="H657" s="6">
-        <v>10</v>
-      </c>
-      <c r="I657" s="6">
-        <v>11</v>
-      </c>
-      <c r="J657" s="6">
-        <v>13</v>
-      </c>
-      <c r="K657" s="6">
-        <v>14</v>
-      </c>
-      <c r="L657" s="6">
-        <v>16</v>
-      </c>
-      <c r="M657" s="6">
-        <v>18</v>
-      </c>
-      <c r="N657" s="6">
-        <v>19</v>
-      </c>
-      <c r="O657" s="6">
-        <v>22</v>
-      </c>
-      <c r="P657" s="6">
+      <c r="B657">
+        <v>1</v>
+      </c>
+      <c r="C657">
+        <v>2</v>
+      </c>
+      <c r="D657">
+        <v>3</v>
+      </c>
+      <c r="E657">
+        <v>4</v>
+      </c>
+      <c r="F657">
+        <v>5</v>
+      </c>
+      <c r="G657">
+        <v>9</v>
+      </c>
+      <c r="H657">
+        <v>10</v>
+      </c>
+      <c r="I657">
+        <v>11</v>
+      </c>
+      <c r="J657">
+        <v>13</v>
+      </c>
+      <c r="K657">
+        <v>14</v>
+      </c>
+      <c r="L657">
+        <v>16</v>
+      </c>
+      <c r="M657">
+        <v>18</v>
+      </c>
+      <c r="N657">
+        <v>19</v>
+      </c>
+      <c r="O657">
+        <v>22</v>
+      </c>
+      <c r="P657">
         <v>23</v>
       </c>
     </row>
     <row r="658" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A658" s="5">
+      <c r="A658">
         <v>3728</v>
       </c>
-      <c r="B658" s="6">
-        <v>1</v>
-      </c>
-      <c r="C658" s="6">
-        <v>2</v>
-      </c>
-      <c r="D658" s="6">
-        <v>3</v>
-      </c>
-      <c r="E658" s="6">
-        <v>6</v>
-      </c>
-      <c r="F658" s="6">
-        <v>7</v>
-      </c>
-      <c r="G658" s="6">
-        <v>8</v>
-      </c>
-      <c r="H658" s="6">
-        <v>10</v>
-      </c>
-      <c r="I658" s="6">
-        <v>11</v>
-      </c>
-      <c r="J658" s="6">
-        <v>16</v>
-      </c>
-      <c r="K658" s="6">
-        <v>17</v>
-      </c>
-      <c r="L658" s="6">
-        <v>19</v>
-      </c>
-      <c r="M658" s="6">
-        <v>21</v>
-      </c>
-      <c r="N658" s="6">
-        <v>22</v>
-      </c>
-      <c r="O658" s="6">
-        <v>23</v>
-      </c>
-      <c r="P658" s="6">
+      <c r="B658">
+        <v>1</v>
+      </c>
+      <c r="C658">
+        <v>2</v>
+      </c>
+      <c r="D658">
+        <v>3</v>
+      </c>
+      <c r="E658">
+        <v>6</v>
+      </c>
+      <c r="F658">
+        <v>7</v>
+      </c>
+      <c r="G658">
+        <v>8</v>
+      </c>
+      <c r="H658">
+        <v>10</v>
+      </c>
+      <c r="I658">
+        <v>11</v>
+      </c>
+      <c r="J658">
+        <v>16</v>
+      </c>
+      <c r="K658">
+        <v>17</v>
+      </c>
+      <c r="L658">
+        <v>19</v>
+      </c>
+      <c r="M658">
+        <v>21</v>
+      </c>
+      <c r="N658">
+        <v>22</v>
+      </c>
+      <c r="O658">
+        <v>23</v>
+      </c>
+      <c r="P658">
         <v>25</v>
       </c>
     </row>
     <row r="659" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A659" s="5">
+      <c r="A659">
         <v>3729</v>
       </c>
-      <c r="B659" s="6">
-        <v>1</v>
-      </c>
-      <c r="C659" s="6">
-        <v>2</v>
-      </c>
-      <c r="D659" s="6">
-        <v>3</v>
-      </c>
-      <c r="E659" s="6">
-        <v>5</v>
-      </c>
-      <c r="F659" s="6">
-        <v>6</v>
-      </c>
-      <c r="G659" s="6">
-        <v>11</v>
-      </c>
-      <c r="H659" s="6">
-        <v>12</v>
-      </c>
-      <c r="I659" s="6">
-        <v>13</v>
-      </c>
-      <c r="J659" s="6">
-        <v>14</v>
-      </c>
-      <c r="K659" s="6">
-        <v>15</v>
-      </c>
-      <c r="L659" s="6">
-        <v>16</v>
-      </c>
-      <c r="M659" s="6">
-        <v>18</v>
-      </c>
-      <c r="N659" s="6">
-        <v>20</v>
-      </c>
-      <c r="O659" s="6">
-        <v>21</v>
-      </c>
-      <c r="P659" s="6">
-        <v>22</v>
+      <c r="B659">
+        <v>1</v>
+      </c>
+      <c r="C659">
+        <v>2</v>
+      </c>
+      <c r="D659">
+        <v>3</v>
+      </c>
+      <c r="E659">
+        <v>5</v>
+      </c>
+      <c r="F659">
+        <v>6</v>
+      </c>
+      <c r="G659">
+        <v>11</v>
+      </c>
+      <c r="H659">
+        <v>12</v>
+      </c>
+      <c r="I659">
+        <v>13</v>
+      </c>
+      <c r="J659">
+        <v>14</v>
+      </c>
+      <c r="K659">
+        <v>15</v>
+      </c>
+      <c r="L659">
+        <v>16</v>
+      </c>
+      <c r="M659">
+        <v>18</v>
+      </c>
+      <c r="N659">
+        <v>20</v>
+      </c>
+      <c r="O659">
+        <v>21</v>
+      </c>
+      <c r="P659">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="660" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A660" s="5">
+        <v>3730</v>
+      </c>
+      <c r="B660" s="6">
+        <v>2</v>
+      </c>
+      <c r="C660" s="6">
+        <v>3</v>
+      </c>
+      <c r="D660" s="6">
+        <v>5</v>
+      </c>
+      <c r="E660" s="6">
+        <v>6</v>
+      </c>
+      <c r="F660" s="6">
+        <v>8</v>
+      </c>
+      <c r="G660" s="6">
+        <v>11</v>
+      </c>
+      <c r="H660" s="6">
+        <v>12</v>
+      </c>
+      <c r="I660" s="6">
+        <v>13</v>
+      </c>
+      <c r="J660" s="6">
+        <v>14</v>
+      </c>
+      <c r="K660" s="6">
+        <v>15</v>
+      </c>
+      <c r="L660" s="6">
+        <v>16</v>
+      </c>
+      <c r="M660" s="6">
+        <v>19</v>
+      </c>
+      <c r="N660" s="6">
+        <v>20</v>
+      </c>
+      <c r="O660" s="6">
+        <v>21</v>
+      </c>
+      <c r="P660" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="661" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A661" s="5">
+        <v>3731</v>
+      </c>
+      <c r="B661" s="6">
+        <v>1</v>
+      </c>
+      <c r="C661" s="6">
+        <v>2</v>
+      </c>
+      <c r="D661" s="6">
+        <v>4</v>
+      </c>
+      <c r="E661" s="6">
+        <v>5</v>
+      </c>
+      <c r="F661" s="6">
+        <v>6</v>
+      </c>
+      <c r="G661" s="6">
+        <v>7</v>
+      </c>
+      <c r="H661" s="6">
+        <v>10</v>
+      </c>
+      <c r="I661" s="6">
+        <v>11</v>
+      </c>
+      <c r="J661" s="6">
+        <v>12</v>
+      </c>
+      <c r="K661" s="6">
+        <v>13</v>
+      </c>
+      <c r="L661" s="6">
+        <v>16</v>
+      </c>
+      <c r="M661" s="6">
+        <v>17</v>
+      </c>
+      <c r="N661" s="6">
+        <v>22</v>
+      </c>
+      <c r="O661" s="6">
+        <v>23</v>
+      </c>
+      <c r="P661" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="662" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A662" s="5">
+        <v>3732</v>
+      </c>
+      <c r="B662" s="6">
+        <v>2</v>
+      </c>
+      <c r="C662" s="6">
+        <v>3</v>
+      </c>
+      <c r="D662" s="6">
+        <v>7</v>
+      </c>
+      <c r="E662" s="6">
+        <v>8</v>
+      </c>
+      <c r="F662" s="6">
+        <v>11</v>
+      </c>
+      <c r="G662" s="6">
+        <v>13</v>
+      </c>
+      <c r="H662" s="6">
+        <v>16</v>
+      </c>
+      <c r="I662" s="6">
+        <v>17</v>
+      </c>
+      <c r="J662" s="6">
+        <v>18</v>
+      </c>
+      <c r="K662" s="6">
+        <v>19</v>
+      </c>
+      <c r="L662" s="6">
+        <v>20</v>
+      </c>
+      <c r="M662" s="6">
+        <v>22</v>
+      </c>
+      <c r="N662" s="6">
+        <v>23</v>
+      </c>
+      <c r="O662" s="6">
+        <v>24</v>
+      </c>
+      <c r="P662" s="6">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -33443,16 +33593,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -33620,6 +33760,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -33630,17 +33780,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33660,6 +33799,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB2F879-6E6F-433D-9684-3FA33F8C2B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C2741F-47FF-45D5-BD74-02B30854E050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61245" yWindow="870" windowWidth="21360" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58335" yWindow="735" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P662"/>
+  <dimension ref="A1:P666"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -33438,153 +33438,353 @@
       </c>
     </row>
     <row r="660" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A660" s="5">
+      <c r="A660">
         <v>3730</v>
       </c>
-      <c r="B660" s="6">
-        <v>2</v>
-      </c>
-      <c r="C660" s="6">
-        <v>3</v>
-      </c>
-      <c r="D660" s="6">
-        <v>5</v>
-      </c>
-      <c r="E660" s="6">
-        <v>6</v>
-      </c>
-      <c r="F660" s="6">
-        <v>8</v>
-      </c>
-      <c r="G660" s="6">
-        <v>11</v>
-      </c>
-      <c r="H660" s="6">
-        <v>12</v>
-      </c>
-      <c r="I660" s="6">
-        <v>13</v>
-      </c>
-      <c r="J660" s="6">
-        <v>14</v>
-      </c>
-      <c r="K660" s="6">
-        <v>15</v>
-      </c>
-      <c r="L660" s="6">
-        <v>16</v>
-      </c>
-      <c r="M660" s="6">
-        <v>19</v>
-      </c>
-      <c r="N660" s="6">
-        <v>20</v>
-      </c>
-      <c r="O660" s="6">
-        <v>21</v>
-      </c>
-      <c r="P660" s="6">
+      <c r="B660">
+        <v>2</v>
+      </c>
+      <c r="C660">
+        <v>3</v>
+      </c>
+      <c r="D660">
+        <v>5</v>
+      </c>
+      <c r="E660">
+        <v>6</v>
+      </c>
+      <c r="F660">
+        <v>8</v>
+      </c>
+      <c r="G660">
+        <v>11</v>
+      </c>
+      <c r="H660">
+        <v>12</v>
+      </c>
+      <c r="I660">
+        <v>13</v>
+      </c>
+      <c r="J660">
+        <v>14</v>
+      </c>
+      <c r="K660">
+        <v>15</v>
+      </c>
+      <c r="L660">
+        <v>16</v>
+      </c>
+      <c r="M660">
+        <v>19</v>
+      </c>
+      <c r="N660">
+        <v>20</v>
+      </c>
+      <c r="O660">
+        <v>21</v>
+      </c>
+      <c r="P660">
         <v>24</v>
       </c>
     </row>
     <row r="661" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A661" s="5">
+      <c r="A661">
         <v>3731</v>
       </c>
-      <c r="B661" s="6">
-        <v>1</v>
-      </c>
-      <c r="C661" s="6">
-        <v>2</v>
-      </c>
-      <c r="D661" s="6">
-        <v>4</v>
-      </c>
-      <c r="E661" s="6">
-        <v>5</v>
-      </c>
-      <c r="F661" s="6">
-        <v>6</v>
-      </c>
-      <c r="G661" s="6">
-        <v>7</v>
-      </c>
-      <c r="H661" s="6">
-        <v>10</v>
-      </c>
-      <c r="I661" s="6">
-        <v>11</v>
-      </c>
-      <c r="J661" s="6">
-        <v>12</v>
-      </c>
-      <c r="K661" s="6">
-        <v>13</v>
-      </c>
-      <c r="L661" s="6">
-        <v>16</v>
-      </c>
-      <c r="M661" s="6">
-        <v>17</v>
-      </c>
-      <c r="N661" s="6">
-        <v>22</v>
-      </c>
-      <c r="O661" s="6">
-        <v>23</v>
-      </c>
-      <c r="P661" s="6">
+      <c r="B661">
+        <v>1</v>
+      </c>
+      <c r="C661">
+        <v>2</v>
+      </c>
+      <c r="D661">
+        <v>4</v>
+      </c>
+      <c r="E661">
+        <v>5</v>
+      </c>
+      <c r="F661">
+        <v>6</v>
+      </c>
+      <c r="G661">
+        <v>7</v>
+      </c>
+      <c r="H661">
+        <v>10</v>
+      </c>
+      <c r="I661">
+        <v>11</v>
+      </c>
+      <c r="J661">
+        <v>12</v>
+      </c>
+      <c r="K661">
+        <v>13</v>
+      </c>
+      <c r="L661">
+        <v>16</v>
+      </c>
+      <c r="M661">
+        <v>17</v>
+      </c>
+      <c r="N661">
+        <v>22</v>
+      </c>
+      <c r="O661">
+        <v>23</v>
+      </c>
+      <c r="P661">
         <v>25</v>
       </c>
     </row>
     <row r="662" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A662" s="5">
+      <c r="A662">
         <v>3732</v>
       </c>
-      <c r="B662" s="6">
-        <v>2</v>
-      </c>
-      <c r="C662" s="6">
-        <v>3</v>
-      </c>
-      <c r="D662" s="6">
-        <v>7</v>
-      </c>
-      <c r="E662" s="6">
-        <v>8</v>
-      </c>
-      <c r="F662" s="6">
-        <v>11</v>
-      </c>
-      <c r="G662" s="6">
-        <v>13</v>
-      </c>
-      <c r="H662" s="6">
-        <v>16</v>
-      </c>
-      <c r="I662" s="6">
-        <v>17</v>
-      </c>
-      <c r="J662" s="6">
-        <v>18</v>
-      </c>
-      <c r="K662" s="6">
-        <v>19</v>
-      </c>
-      <c r="L662" s="6">
-        <v>20</v>
-      </c>
-      <c r="M662" s="6">
-        <v>22</v>
-      </c>
-      <c r="N662" s="6">
-        <v>23</v>
-      </c>
-      <c r="O662" s="6">
-        <v>24</v>
-      </c>
-      <c r="P662" s="6">
-        <v>25</v>
+      <c r="B662">
+        <v>2</v>
+      </c>
+      <c r="C662">
+        <v>3</v>
+      </c>
+      <c r="D662">
+        <v>7</v>
+      </c>
+      <c r="E662">
+        <v>8</v>
+      </c>
+      <c r="F662">
+        <v>11</v>
+      </c>
+      <c r="G662">
+        <v>13</v>
+      </c>
+      <c r="H662">
+        <v>16</v>
+      </c>
+      <c r="I662">
+        <v>17</v>
+      </c>
+      <c r="J662">
+        <v>18</v>
+      </c>
+      <c r="K662">
+        <v>19</v>
+      </c>
+      <c r="L662">
+        <v>20</v>
+      </c>
+      <c r="M662">
+        <v>22</v>
+      </c>
+      <c r="N662">
+        <v>23</v>
+      </c>
+      <c r="O662">
+        <v>24</v>
+      </c>
+      <c r="P662">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="663" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A663" s="5">
+        <v>3733</v>
+      </c>
+      <c r="B663" s="6">
+        <v>1</v>
+      </c>
+      <c r="C663" s="6">
+        <v>2</v>
+      </c>
+      <c r="D663" s="6">
+        <v>3</v>
+      </c>
+      <c r="E663" s="6">
+        <v>5</v>
+      </c>
+      <c r="F663" s="6">
+        <v>7</v>
+      </c>
+      <c r="G663" s="6">
+        <v>10</v>
+      </c>
+      <c r="H663" s="6">
+        <v>11</v>
+      </c>
+      <c r="I663" s="6">
+        <v>12</v>
+      </c>
+      <c r="J663" s="6">
+        <v>13</v>
+      </c>
+      <c r="K663" s="6">
+        <v>14</v>
+      </c>
+      <c r="L663" s="6">
+        <v>16</v>
+      </c>
+      <c r="M663" s="6">
+        <v>17</v>
+      </c>
+      <c r="N663" s="6">
+        <v>19</v>
+      </c>
+      <c r="O663" s="6">
+        <v>22</v>
+      </c>
+      <c r="P663" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="664" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A664" s="5">
+        <v>3734</v>
+      </c>
+      <c r="B664" s="6">
+        <v>2</v>
+      </c>
+      <c r="C664" s="6">
+        <v>3</v>
+      </c>
+      <c r="D664" s="6">
+        <v>5</v>
+      </c>
+      <c r="E664" s="6">
+        <v>8</v>
+      </c>
+      <c r="F664" s="6">
+        <v>10</v>
+      </c>
+      <c r="G664" s="6">
+        <v>12</v>
+      </c>
+      <c r="H664" s="6">
+        <v>13</v>
+      </c>
+      <c r="I664" s="6">
+        <v>14</v>
+      </c>
+      <c r="J664" s="6">
+        <v>15</v>
+      </c>
+      <c r="K664" s="6">
+        <v>16</v>
+      </c>
+      <c r="L664" s="6">
+        <v>17</v>
+      </c>
+      <c r="M664" s="6">
+        <v>19</v>
+      </c>
+      <c r="N664" s="6">
+        <v>22</v>
+      </c>
+      <c r="O664" s="6">
+        <v>23</v>
+      </c>
+      <c r="P664" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="665" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A665" s="5">
+        <v>3735</v>
+      </c>
+      <c r="B665" s="6">
+        <v>3</v>
+      </c>
+      <c r="C665" s="6">
+        <v>5</v>
+      </c>
+      <c r="D665" s="6">
+        <v>7</v>
+      </c>
+      <c r="E665" s="6">
+        <v>12</v>
+      </c>
+      <c r="F665" s="6">
+        <v>14</v>
+      </c>
+      <c r="G665" s="6">
+        <v>15</v>
+      </c>
+      <c r="H665" s="6">
+        <v>16</v>
+      </c>
+      <c r="I665" s="6">
+        <v>17</v>
+      </c>
+      <c r="J665" s="6">
+        <v>18</v>
+      </c>
+      <c r="K665" s="6">
+        <v>20</v>
+      </c>
+      <c r="L665" s="6">
+        <v>21</v>
+      </c>
+      <c r="M665" s="6">
+        <v>22</v>
+      </c>
+      <c r="N665" s="6">
+        <v>23</v>
+      </c>
+      <c r="O665" s="6">
+        <v>24</v>
+      </c>
+      <c r="P665" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="666" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A666" s="5">
+        <v>3736</v>
+      </c>
+      <c r="B666" s="6">
+        <v>3</v>
+      </c>
+      <c r="C666" s="6">
+        <v>4</v>
+      </c>
+      <c r="D666" s="6">
+        <v>6</v>
+      </c>
+      <c r="E666" s="6">
+        <v>7</v>
+      </c>
+      <c r="F666" s="6">
+        <v>8</v>
+      </c>
+      <c r="G666" s="6">
+        <v>9</v>
+      </c>
+      <c r="H666" s="6">
+        <v>11</v>
+      </c>
+      <c r="I666" s="6">
+        <v>12</v>
+      </c>
+      <c r="J666" s="6">
+        <v>14</v>
+      </c>
+      <c r="K666" s="6">
+        <v>17</v>
+      </c>
+      <c r="L666" s="6">
+        <v>18</v>
+      </c>
+      <c r="M666" s="6">
+        <v>19</v>
+      </c>
+      <c r="N666" s="6">
+        <v>21</v>
+      </c>
+      <c r="O666" s="6">
+        <v>22</v>
+      </c>
+      <c r="P666" s="6">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -33593,6 +33793,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -33760,16 +33970,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -33780,6 +33980,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33799,17 +34010,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C2741F-47FF-45D5-BD74-02B30854E050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871C2593-12F7-4AEC-A723-7D7C9243430C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58335" yWindow="735" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="22395" windowHeight="10358" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P666"/>
+  <dimension ref="A1:P677"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -33588,203 +33588,753 @@
       </c>
     </row>
     <row r="663" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A663" s="5">
+      <c r="A663">
         <v>3733</v>
       </c>
-      <c r="B663" s="6">
-        <v>1</v>
-      </c>
-      <c r="C663" s="6">
-        <v>2</v>
-      </c>
-      <c r="D663" s="6">
-        <v>3</v>
-      </c>
-      <c r="E663" s="6">
-        <v>5</v>
-      </c>
-      <c r="F663" s="6">
-        <v>7</v>
-      </c>
-      <c r="G663" s="6">
-        <v>10</v>
-      </c>
-      <c r="H663" s="6">
-        <v>11</v>
-      </c>
-      <c r="I663" s="6">
-        <v>12</v>
-      </c>
-      <c r="J663" s="6">
-        <v>13</v>
-      </c>
-      <c r="K663" s="6">
-        <v>14</v>
-      </c>
-      <c r="L663" s="6">
-        <v>16</v>
-      </c>
-      <c r="M663" s="6">
-        <v>17</v>
-      </c>
-      <c r="N663" s="6">
-        <v>19</v>
-      </c>
-      <c r="O663" s="6">
-        <v>22</v>
-      </c>
-      <c r="P663" s="6">
+      <c r="B663">
+        <v>1</v>
+      </c>
+      <c r="C663">
+        <v>2</v>
+      </c>
+      <c r="D663">
+        <v>3</v>
+      </c>
+      <c r="E663">
+        <v>5</v>
+      </c>
+      <c r="F663">
+        <v>7</v>
+      </c>
+      <c r="G663">
+        <v>10</v>
+      </c>
+      <c r="H663">
+        <v>11</v>
+      </c>
+      <c r="I663">
+        <v>12</v>
+      </c>
+      <c r="J663">
+        <v>13</v>
+      </c>
+      <c r="K663">
+        <v>14</v>
+      </c>
+      <c r="L663">
+        <v>16</v>
+      </c>
+      <c r="M663">
+        <v>17</v>
+      </c>
+      <c r="N663">
+        <v>19</v>
+      </c>
+      <c r="O663">
+        <v>22</v>
+      </c>
+      <c r="P663">
         <v>25</v>
       </c>
     </row>
     <row r="664" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A664" s="5">
+      <c r="A664">
         <v>3734</v>
       </c>
-      <c r="B664" s="6">
-        <v>2</v>
-      </c>
-      <c r="C664" s="6">
-        <v>3</v>
-      </c>
-      <c r="D664" s="6">
-        <v>5</v>
-      </c>
-      <c r="E664" s="6">
-        <v>8</v>
-      </c>
-      <c r="F664" s="6">
-        <v>10</v>
-      </c>
-      <c r="G664" s="6">
-        <v>12</v>
-      </c>
-      <c r="H664" s="6">
-        <v>13</v>
-      </c>
-      <c r="I664" s="6">
-        <v>14</v>
-      </c>
-      <c r="J664" s="6">
-        <v>15</v>
-      </c>
-      <c r="K664" s="6">
-        <v>16</v>
-      </c>
-      <c r="L664" s="6">
-        <v>17</v>
-      </c>
-      <c r="M664" s="6">
-        <v>19</v>
-      </c>
-      <c r="N664" s="6">
-        <v>22</v>
-      </c>
-      <c r="O664" s="6">
-        <v>23</v>
-      </c>
-      <c r="P664" s="6">
+      <c r="B664">
+        <v>2</v>
+      </c>
+      <c r="C664">
+        <v>3</v>
+      </c>
+      <c r="D664">
+        <v>5</v>
+      </c>
+      <c r="E664">
+        <v>8</v>
+      </c>
+      <c r="F664">
+        <v>10</v>
+      </c>
+      <c r="G664">
+        <v>12</v>
+      </c>
+      <c r="H664">
+        <v>13</v>
+      </c>
+      <c r="I664">
+        <v>14</v>
+      </c>
+      <c r="J664">
+        <v>15</v>
+      </c>
+      <c r="K664">
+        <v>16</v>
+      </c>
+      <c r="L664">
+        <v>17</v>
+      </c>
+      <c r="M664">
+        <v>19</v>
+      </c>
+      <c r="N664">
+        <v>22</v>
+      </c>
+      <c r="O664">
+        <v>23</v>
+      </c>
+      <c r="P664">
         <v>25</v>
       </c>
     </row>
     <row r="665" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A665" s="5">
+      <c r="A665">
         <v>3735</v>
       </c>
-      <c r="B665" s="6">
-        <v>3</v>
-      </c>
-      <c r="C665" s="6">
-        <v>5</v>
-      </c>
-      <c r="D665" s="6">
-        <v>7</v>
-      </c>
-      <c r="E665" s="6">
-        <v>12</v>
-      </c>
-      <c r="F665" s="6">
-        <v>14</v>
-      </c>
-      <c r="G665" s="6">
-        <v>15</v>
-      </c>
-      <c r="H665" s="6">
-        <v>16</v>
-      </c>
-      <c r="I665" s="6">
-        <v>17</v>
-      </c>
-      <c r="J665" s="6">
-        <v>18</v>
-      </c>
-      <c r="K665" s="6">
-        <v>20</v>
-      </c>
-      <c r="L665" s="6">
-        <v>21</v>
-      </c>
-      <c r="M665" s="6">
-        <v>22</v>
-      </c>
-      <c r="N665" s="6">
-        <v>23</v>
-      </c>
-      <c r="O665" s="6">
-        <v>24</v>
-      </c>
-      <c r="P665" s="6">
+      <c r="B665">
+        <v>3</v>
+      </c>
+      <c r="C665">
+        <v>5</v>
+      </c>
+      <c r="D665">
+        <v>7</v>
+      </c>
+      <c r="E665">
+        <v>12</v>
+      </c>
+      <c r="F665">
+        <v>14</v>
+      </c>
+      <c r="G665">
+        <v>15</v>
+      </c>
+      <c r="H665">
+        <v>16</v>
+      </c>
+      <c r="I665">
+        <v>17</v>
+      </c>
+      <c r="J665">
+        <v>18</v>
+      </c>
+      <c r="K665">
+        <v>20</v>
+      </c>
+      <c r="L665">
+        <v>21</v>
+      </c>
+      <c r="M665">
+        <v>22</v>
+      </c>
+      <c r="N665">
+        <v>23</v>
+      </c>
+      <c r="O665">
+        <v>24</v>
+      </c>
+      <c r="P665">
         <v>25</v>
       </c>
     </row>
     <row r="666" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A666" s="5">
+      <c r="A666">
         <v>3736</v>
       </c>
-      <c r="B666" s="6">
-        <v>3</v>
-      </c>
-      <c r="C666" s="6">
-        <v>4</v>
-      </c>
-      <c r="D666" s="6">
-        <v>6</v>
-      </c>
-      <c r="E666" s="6">
-        <v>7</v>
-      </c>
-      <c r="F666" s="6">
-        <v>8</v>
-      </c>
-      <c r="G666" s="6">
-        <v>9</v>
-      </c>
-      <c r="H666" s="6">
-        <v>11</v>
-      </c>
-      <c r="I666" s="6">
-        <v>12</v>
-      </c>
-      <c r="J666" s="6">
-        <v>14</v>
-      </c>
-      <c r="K666" s="6">
-        <v>17</v>
-      </c>
-      <c r="L666" s="6">
-        <v>18</v>
-      </c>
-      <c r="M666" s="6">
-        <v>19</v>
-      </c>
-      <c r="N666" s="6">
-        <v>21</v>
-      </c>
-      <c r="O666" s="6">
-        <v>22</v>
-      </c>
-      <c r="P666" s="6">
-        <v>23</v>
+      <c r="B666">
+        <v>3</v>
+      </c>
+      <c r="C666">
+        <v>4</v>
+      </c>
+      <c r="D666">
+        <v>6</v>
+      </c>
+      <c r="E666">
+        <v>7</v>
+      </c>
+      <c r="F666">
+        <v>8</v>
+      </c>
+      <c r="G666">
+        <v>9</v>
+      </c>
+      <c r="H666">
+        <v>11</v>
+      </c>
+      <c r="I666">
+        <v>12</v>
+      </c>
+      <c r="J666">
+        <v>14</v>
+      </c>
+      <c r="K666">
+        <v>17</v>
+      </c>
+      <c r="L666">
+        <v>18</v>
+      </c>
+      <c r="M666">
+        <v>19</v>
+      </c>
+      <c r="N666">
+        <v>21</v>
+      </c>
+      <c r="O666">
+        <v>22</v>
+      </c>
+      <c r="P666">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="667" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A667" s="5">
+        <v>3737</v>
+      </c>
+      <c r="B667" s="6">
+        <v>2</v>
+      </c>
+      <c r="C667" s="6">
+        <v>3</v>
+      </c>
+      <c r="D667" s="6">
+        <v>5</v>
+      </c>
+      <c r="E667" s="6">
+        <v>6</v>
+      </c>
+      <c r="F667" s="6">
+        <v>8</v>
+      </c>
+      <c r="G667" s="6">
+        <v>9</v>
+      </c>
+      <c r="H667" s="6">
+        <v>11</v>
+      </c>
+      <c r="I667" s="6">
+        <v>12</v>
+      </c>
+      <c r="J667" s="6">
+        <v>13</v>
+      </c>
+      <c r="K667" s="6">
+        <v>14</v>
+      </c>
+      <c r="L667" s="6">
+        <v>15</v>
+      </c>
+      <c r="M667" s="6">
+        <v>17</v>
+      </c>
+      <c r="N667" s="6">
+        <v>22</v>
+      </c>
+      <c r="O667" s="6">
+        <v>23</v>
+      </c>
+      <c r="P667" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="668" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A668" s="5">
+        <v>3738</v>
+      </c>
+      <c r="B668" s="6">
+        <v>2</v>
+      </c>
+      <c r="C668" s="6">
+        <v>3</v>
+      </c>
+      <c r="D668" s="6">
+        <v>4</v>
+      </c>
+      <c r="E668" s="6">
+        <v>5</v>
+      </c>
+      <c r="F668" s="6">
+        <v>7</v>
+      </c>
+      <c r="G668" s="6">
+        <v>8</v>
+      </c>
+      <c r="H668" s="6">
+        <v>10</v>
+      </c>
+      <c r="I668" s="6">
+        <v>11</v>
+      </c>
+      <c r="J668" s="6">
+        <v>13</v>
+      </c>
+      <c r="K668" s="6">
+        <v>14</v>
+      </c>
+      <c r="L668" s="6">
+        <v>17</v>
+      </c>
+      <c r="M668" s="6">
+        <v>18</v>
+      </c>
+      <c r="N668" s="6">
+        <v>20</v>
+      </c>
+      <c r="O668" s="6">
+        <v>23</v>
+      </c>
+      <c r="P668" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="669" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A669" s="5">
+        <v>3739</v>
+      </c>
+      <c r="B669" s="6">
+        <v>1</v>
+      </c>
+      <c r="C669" s="6">
+        <v>4</v>
+      </c>
+      <c r="D669" s="6">
+        <v>5</v>
+      </c>
+      <c r="E669" s="6">
+        <v>6</v>
+      </c>
+      <c r="F669" s="6">
+        <v>9</v>
+      </c>
+      <c r="G669" s="6">
+        <v>11</v>
+      </c>
+      <c r="H669" s="6">
+        <v>13</v>
+      </c>
+      <c r="I669" s="6">
+        <v>15</v>
+      </c>
+      <c r="J669" s="6">
+        <v>16</v>
+      </c>
+      <c r="K669" s="6">
+        <v>18</v>
+      </c>
+      <c r="L669" s="6">
+        <v>19</v>
+      </c>
+      <c r="M669" s="6">
+        <v>20</v>
+      </c>
+      <c r="N669" s="6">
+        <v>23</v>
+      </c>
+      <c r="O669" s="6">
+        <v>24</v>
+      </c>
+      <c r="P669" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="670" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A670" s="5">
+        <v>3740</v>
+      </c>
+      <c r="B670" s="6">
+        <v>1</v>
+      </c>
+      <c r="C670" s="6">
+        <v>2</v>
+      </c>
+      <c r="D670" s="6">
+        <v>5</v>
+      </c>
+      <c r="E670" s="6">
+        <v>6</v>
+      </c>
+      <c r="F670" s="6">
+        <v>8</v>
+      </c>
+      <c r="G670" s="6">
+        <v>9</v>
+      </c>
+      <c r="H670" s="6">
+        <v>11</v>
+      </c>
+      <c r="I670" s="6">
+        <v>12</v>
+      </c>
+      <c r="J670" s="6">
+        <v>13</v>
+      </c>
+      <c r="K670" s="6">
+        <v>15</v>
+      </c>
+      <c r="L670" s="6">
+        <v>16</v>
+      </c>
+      <c r="M670" s="6">
+        <v>17</v>
+      </c>
+      <c r="N670" s="6">
+        <v>20</v>
+      </c>
+      <c r="O670" s="6">
+        <v>21</v>
+      </c>
+      <c r="P670" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="671" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A671" s="5">
+        <v>3741</v>
+      </c>
+      <c r="B671" s="6">
+        <v>2</v>
+      </c>
+      <c r="C671" s="6">
+        <v>3</v>
+      </c>
+      <c r="D671" s="6">
+        <v>4</v>
+      </c>
+      <c r="E671" s="6">
+        <v>5</v>
+      </c>
+      <c r="F671" s="6">
+        <v>9</v>
+      </c>
+      <c r="G671" s="6">
+        <v>11</v>
+      </c>
+      <c r="H671" s="6">
+        <v>12</v>
+      </c>
+      <c r="I671" s="6">
+        <v>14</v>
+      </c>
+      <c r="J671" s="6">
+        <v>15</v>
+      </c>
+      <c r="K671" s="6">
+        <v>16</v>
+      </c>
+      <c r="L671" s="6">
+        <v>18</v>
+      </c>
+      <c r="M671" s="6">
+        <v>20</v>
+      </c>
+      <c r="N671" s="6">
+        <v>21</v>
+      </c>
+      <c r="O671" s="6">
+        <v>22</v>
+      </c>
+      <c r="P671" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="672" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A672" s="5">
+        <v>3742</v>
+      </c>
+      <c r="B672" s="6">
+        <v>1</v>
+      </c>
+      <c r="C672" s="6">
+        <v>4</v>
+      </c>
+      <c r="D672" s="6">
+        <v>5</v>
+      </c>
+      <c r="E672" s="6">
+        <v>6</v>
+      </c>
+      <c r="F672" s="6">
+        <v>9</v>
+      </c>
+      <c r="G672" s="6">
+        <v>10</v>
+      </c>
+      <c r="H672" s="6">
+        <v>12</v>
+      </c>
+      <c r="I672" s="6">
+        <v>13</v>
+      </c>
+      <c r="J672" s="6">
+        <v>14</v>
+      </c>
+      <c r="K672" s="6">
+        <v>15</v>
+      </c>
+      <c r="L672" s="6">
+        <v>16</v>
+      </c>
+      <c r="M672" s="6">
+        <v>19</v>
+      </c>
+      <c r="N672" s="6">
+        <v>20</v>
+      </c>
+      <c r="O672" s="6">
+        <v>21</v>
+      </c>
+      <c r="P672" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="673" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A673" s="5">
+        <v>3743</v>
+      </c>
+      <c r="B673" s="6">
+        <v>2</v>
+      </c>
+      <c r="C673" s="6">
+        <v>3</v>
+      </c>
+      <c r="D673" s="6">
+        <v>4</v>
+      </c>
+      <c r="E673" s="6">
+        <v>5</v>
+      </c>
+      <c r="F673" s="6">
+        <v>9</v>
+      </c>
+      <c r="G673" s="6">
+        <v>10</v>
+      </c>
+      <c r="H673" s="6">
+        <v>11</v>
+      </c>
+      <c r="I673" s="6">
+        <v>13</v>
+      </c>
+      <c r="J673" s="6">
+        <v>15</v>
+      </c>
+      <c r="K673" s="6">
+        <v>18</v>
+      </c>
+      <c r="L673" s="6">
+        <v>19</v>
+      </c>
+      <c r="M673" s="6">
+        <v>20</v>
+      </c>
+      <c r="N673" s="6">
+        <v>21</v>
+      </c>
+      <c r="O673" s="6">
+        <v>23</v>
+      </c>
+      <c r="P673" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="674" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A674" s="5">
+        <v>3744</v>
+      </c>
+      <c r="B674" s="6">
+        <v>1</v>
+      </c>
+      <c r="C674" s="6">
+        <v>2</v>
+      </c>
+      <c r="D674" s="6">
+        <v>3</v>
+      </c>
+      <c r="E674" s="6">
+        <v>5</v>
+      </c>
+      <c r="F674" s="6">
+        <v>7</v>
+      </c>
+      <c r="G674" s="6">
+        <v>10</v>
+      </c>
+      <c r="H674" s="6">
+        <v>14</v>
+      </c>
+      <c r="I674" s="6">
+        <v>16</v>
+      </c>
+      <c r="J674" s="6">
+        <v>17</v>
+      </c>
+      <c r="K674" s="6">
+        <v>18</v>
+      </c>
+      <c r="L674" s="6">
+        <v>20</v>
+      </c>
+      <c r="M674" s="6">
+        <v>21</v>
+      </c>
+      <c r="N674" s="6">
+        <v>22</v>
+      </c>
+      <c r="O674" s="6">
+        <v>23</v>
+      </c>
+      <c r="P674" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="675" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A675" s="5">
+        <v>3745</v>
+      </c>
+      <c r="B675" s="6">
+        <v>1</v>
+      </c>
+      <c r="C675" s="6">
+        <v>2</v>
+      </c>
+      <c r="D675" s="6">
+        <v>4</v>
+      </c>
+      <c r="E675" s="6">
+        <v>5</v>
+      </c>
+      <c r="F675" s="6">
+        <v>6</v>
+      </c>
+      <c r="G675" s="6">
+        <v>7</v>
+      </c>
+      <c r="H675" s="6">
+        <v>8</v>
+      </c>
+      <c r="I675" s="6">
+        <v>9</v>
+      </c>
+      <c r="J675" s="6">
+        <v>10</v>
+      </c>
+      <c r="K675" s="6">
+        <v>12</v>
+      </c>
+      <c r="L675" s="6">
+        <v>13</v>
+      </c>
+      <c r="M675" s="6">
+        <v>19</v>
+      </c>
+      <c r="N675" s="6">
+        <v>21</v>
+      </c>
+      <c r="O675" s="6">
+        <v>22</v>
+      </c>
+      <c r="P675" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="676" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A676" s="5">
+        <v>3746</v>
+      </c>
+      <c r="B676" s="6">
+        <v>1</v>
+      </c>
+      <c r="C676" s="6">
+        <v>3</v>
+      </c>
+      <c r="D676" s="6">
+        <v>4</v>
+      </c>
+      <c r="E676" s="6">
+        <v>6</v>
+      </c>
+      <c r="F676" s="6">
+        <v>7</v>
+      </c>
+      <c r="G676" s="6">
+        <v>8</v>
+      </c>
+      <c r="H676" s="6">
+        <v>9</v>
+      </c>
+      <c r="I676" s="6">
+        <v>10</v>
+      </c>
+      <c r="J676" s="6">
+        <v>14</v>
+      </c>
+      <c r="K676" s="6">
+        <v>15</v>
+      </c>
+      <c r="L676" s="6">
+        <v>17</v>
+      </c>
+      <c r="M676" s="6">
+        <v>18</v>
+      </c>
+      <c r="N676" s="6">
+        <v>21</v>
+      </c>
+      <c r="O676" s="6">
+        <v>22</v>
+      </c>
+      <c r="P676" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="677" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A677" s="5">
+        <v>3747</v>
+      </c>
+      <c r="B677" s="6">
+        <v>1</v>
+      </c>
+      <c r="C677" s="6">
+        <v>2</v>
+      </c>
+      <c r="D677" s="6">
+        <v>4</v>
+      </c>
+      <c r="E677" s="6">
+        <v>5</v>
+      </c>
+      <c r="F677" s="6">
+        <v>6</v>
+      </c>
+      <c r="G677" s="6">
+        <v>8</v>
+      </c>
+      <c r="H677" s="6">
+        <v>9</v>
+      </c>
+      <c r="I677" s="6">
+        <v>11</v>
+      </c>
+      <c r="J677" s="6">
+        <v>12</v>
+      </c>
+      <c r="K677" s="6">
+        <v>13</v>
+      </c>
+      <c r="L677" s="6">
+        <v>18</v>
+      </c>
+      <c r="M677" s="6">
+        <v>19</v>
+      </c>
+      <c r="N677" s="6">
+        <v>21</v>
+      </c>
+      <c r="O677" s="6">
+        <v>24</v>
+      </c>
+      <c r="P677" s="6">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -33793,16 +34343,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -33970,6 +34510,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -33980,17 +34530,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34010,6 +34549,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871C2593-12F7-4AEC-A723-7D7C9243430C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA2BAA2-1D81-4466-9D23-8476C14C2FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="22395" windowHeight="10358" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,8 +156,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P677"/>
+  <dimension ref="A1:P678"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -33788,552 +33786,602 @@
       </c>
     </row>
     <row r="667" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A667" s="5">
+      <c r="A667">
         <v>3737</v>
       </c>
-      <c r="B667" s="6">
-        <v>2</v>
-      </c>
-      <c r="C667" s="6">
-        <v>3</v>
-      </c>
-      <c r="D667" s="6">
-        <v>5</v>
-      </c>
-      <c r="E667" s="6">
-        <v>6</v>
-      </c>
-      <c r="F667" s="6">
-        <v>8</v>
-      </c>
-      <c r="G667" s="6">
-        <v>9</v>
-      </c>
-      <c r="H667" s="6">
-        <v>11</v>
-      </c>
-      <c r="I667" s="6">
-        <v>12</v>
-      </c>
-      <c r="J667" s="6">
-        <v>13</v>
-      </c>
-      <c r="K667" s="6">
-        <v>14</v>
-      </c>
-      <c r="L667" s="6">
-        <v>15</v>
-      </c>
-      <c r="M667" s="6">
-        <v>17</v>
-      </c>
-      <c r="N667" s="6">
-        <v>22</v>
-      </c>
-      <c r="O667" s="6">
-        <v>23</v>
-      </c>
-      <c r="P667" s="6">
+      <c r="B667">
+        <v>2</v>
+      </c>
+      <c r="C667">
+        <v>3</v>
+      </c>
+      <c r="D667">
+        <v>5</v>
+      </c>
+      <c r="E667">
+        <v>6</v>
+      </c>
+      <c r="F667">
+        <v>8</v>
+      </c>
+      <c r="G667">
+        <v>9</v>
+      </c>
+      <c r="H667">
+        <v>11</v>
+      </c>
+      <c r="I667">
+        <v>12</v>
+      </c>
+      <c r="J667">
+        <v>13</v>
+      </c>
+      <c r="K667">
+        <v>14</v>
+      </c>
+      <c r="L667">
+        <v>15</v>
+      </c>
+      <c r="M667">
+        <v>17</v>
+      </c>
+      <c r="N667">
+        <v>22</v>
+      </c>
+      <c r="O667">
+        <v>23</v>
+      </c>
+      <c r="P667">
         <v>25</v>
       </c>
     </row>
     <row r="668" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A668" s="5">
+      <c r="A668">
         <v>3738</v>
       </c>
-      <c r="B668" s="6">
-        <v>2</v>
-      </c>
-      <c r="C668" s="6">
-        <v>3</v>
-      </c>
-      <c r="D668" s="6">
-        <v>4</v>
-      </c>
-      <c r="E668" s="6">
-        <v>5</v>
-      </c>
-      <c r="F668" s="6">
-        <v>7</v>
-      </c>
-      <c r="G668" s="6">
-        <v>8</v>
-      </c>
-      <c r="H668" s="6">
-        <v>10</v>
-      </c>
-      <c r="I668" s="6">
-        <v>11</v>
-      </c>
-      <c r="J668" s="6">
-        <v>13</v>
-      </c>
-      <c r="K668" s="6">
-        <v>14</v>
-      </c>
-      <c r="L668" s="6">
-        <v>17</v>
-      </c>
-      <c r="M668" s="6">
-        <v>18</v>
-      </c>
-      <c r="N668" s="6">
-        <v>20</v>
-      </c>
-      <c r="O668" s="6">
-        <v>23</v>
-      </c>
-      <c r="P668" s="6">
+      <c r="B668">
+        <v>2</v>
+      </c>
+      <c r="C668">
+        <v>3</v>
+      </c>
+      <c r="D668">
+        <v>4</v>
+      </c>
+      <c r="E668">
+        <v>5</v>
+      </c>
+      <c r="F668">
+        <v>7</v>
+      </c>
+      <c r="G668">
+        <v>8</v>
+      </c>
+      <c r="H668">
+        <v>10</v>
+      </c>
+      <c r="I668">
+        <v>11</v>
+      </c>
+      <c r="J668">
+        <v>13</v>
+      </c>
+      <c r="K668">
+        <v>14</v>
+      </c>
+      <c r="L668">
+        <v>17</v>
+      </c>
+      <c r="M668">
+        <v>18</v>
+      </c>
+      <c r="N668">
+        <v>20</v>
+      </c>
+      <c r="O668">
+        <v>23</v>
+      </c>
+      <c r="P668">
         <v>24</v>
       </c>
     </row>
     <row r="669" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A669" s="5">
+      <c r="A669">
         <v>3739</v>
       </c>
-      <c r="B669" s="6">
-        <v>1</v>
-      </c>
-      <c r="C669" s="6">
-        <v>4</v>
-      </c>
-      <c r="D669" s="6">
-        <v>5</v>
-      </c>
-      <c r="E669" s="6">
-        <v>6</v>
-      </c>
-      <c r="F669" s="6">
-        <v>9</v>
-      </c>
-      <c r="G669" s="6">
-        <v>11</v>
-      </c>
-      <c r="H669" s="6">
-        <v>13</v>
-      </c>
-      <c r="I669" s="6">
-        <v>15</v>
-      </c>
-      <c r="J669" s="6">
-        <v>16</v>
-      </c>
-      <c r="K669" s="6">
-        <v>18</v>
-      </c>
-      <c r="L669" s="6">
-        <v>19</v>
-      </c>
-      <c r="M669" s="6">
-        <v>20</v>
-      </c>
-      <c r="N669" s="6">
-        <v>23</v>
-      </c>
-      <c r="O669" s="6">
-        <v>24</v>
-      </c>
-      <c r="P669" s="6">
+      <c r="B669">
+        <v>1</v>
+      </c>
+      <c r="C669">
+        <v>4</v>
+      </c>
+      <c r="D669">
+        <v>5</v>
+      </c>
+      <c r="E669">
+        <v>6</v>
+      </c>
+      <c r="F669">
+        <v>9</v>
+      </c>
+      <c r="G669">
+        <v>11</v>
+      </c>
+      <c r="H669">
+        <v>13</v>
+      </c>
+      <c r="I669">
+        <v>15</v>
+      </c>
+      <c r="J669">
+        <v>16</v>
+      </c>
+      <c r="K669">
+        <v>18</v>
+      </c>
+      <c r="L669">
+        <v>19</v>
+      </c>
+      <c r="M669">
+        <v>20</v>
+      </c>
+      <c r="N669">
+        <v>23</v>
+      </c>
+      <c r="O669">
+        <v>24</v>
+      </c>
+      <c r="P669">
         <v>25</v>
       </c>
     </row>
     <row r="670" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A670" s="5">
+      <c r="A670">
         <v>3740</v>
       </c>
-      <c r="B670" s="6">
-        <v>1</v>
-      </c>
-      <c r="C670" s="6">
-        <v>2</v>
-      </c>
-      <c r="D670" s="6">
-        <v>5</v>
-      </c>
-      <c r="E670" s="6">
-        <v>6</v>
-      </c>
-      <c r="F670" s="6">
-        <v>8</v>
-      </c>
-      <c r="G670" s="6">
-        <v>9</v>
-      </c>
-      <c r="H670" s="6">
-        <v>11</v>
-      </c>
-      <c r="I670" s="6">
-        <v>12</v>
-      </c>
-      <c r="J670" s="6">
-        <v>13</v>
-      </c>
-      <c r="K670" s="6">
-        <v>15</v>
-      </c>
-      <c r="L670" s="6">
-        <v>16</v>
-      </c>
-      <c r="M670" s="6">
-        <v>17</v>
-      </c>
-      <c r="N670" s="6">
-        <v>20</v>
-      </c>
-      <c r="O670" s="6">
-        <v>21</v>
-      </c>
-      <c r="P670" s="6">
+      <c r="B670">
+        <v>1</v>
+      </c>
+      <c r="C670">
+        <v>2</v>
+      </c>
+      <c r="D670">
+        <v>5</v>
+      </c>
+      <c r="E670">
+        <v>6</v>
+      </c>
+      <c r="F670">
+        <v>8</v>
+      </c>
+      <c r="G670">
+        <v>9</v>
+      </c>
+      <c r="H670">
+        <v>11</v>
+      </c>
+      <c r="I670">
+        <v>12</v>
+      </c>
+      <c r="J670">
+        <v>13</v>
+      </c>
+      <c r="K670">
+        <v>15</v>
+      </c>
+      <c r="L670">
+        <v>16</v>
+      </c>
+      <c r="M670">
+        <v>17</v>
+      </c>
+      <c r="N670">
+        <v>20</v>
+      </c>
+      <c r="O670">
+        <v>21</v>
+      </c>
+      <c r="P670">
         <v>22</v>
       </c>
     </row>
     <row r="671" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A671" s="5">
+      <c r="A671">
         <v>3741</v>
       </c>
-      <c r="B671" s="6">
-        <v>2</v>
-      </c>
-      <c r="C671" s="6">
-        <v>3</v>
-      </c>
-      <c r="D671" s="6">
-        <v>4</v>
-      </c>
-      <c r="E671" s="6">
-        <v>5</v>
-      </c>
-      <c r="F671" s="6">
-        <v>9</v>
-      </c>
-      <c r="G671" s="6">
-        <v>11</v>
-      </c>
-      <c r="H671" s="6">
-        <v>12</v>
-      </c>
-      <c r="I671" s="6">
-        <v>14</v>
-      </c>
-      <c r="J671" s="6">
-        <v>15</v>
-      </c>
-      <c r="K671" s="6">
-        <v>16</v>
-      </c>
-      <c r="L671" s="6">
-        <v>18</v>
-      </c>
-      <c r="M671" s="6">
-        <v>20</v>
-      </c>
-      <c r="N671" s="6">
-        <v>21</v>
-      </c>
-      <c r="O671" s="6">
-        <v>22</v>
-      </c>
-      <c r="P671" s="6">
+      <c r="B671">
+        <v>2</v>
+      </c>
+      <c r="C671">
+        <v>3</v>
+      </c>
+      <c r="D671">
+        <v>4</v>
+      </c>
+      <c r="E671">
+        <v>5</v>
+      </c>
+      <c r="F671">
+        <v>9</v>
+      </c>
+      <c r="G671">
+        <v>11</v>
+      </c>
+      <c r="H671">
+        <v>12</v>
+      </c>
+      <c r="I671">
+        <v>14</v>
+      </c>
+      <c r="J671">
+        <v>15</v>
+      </c>
+      <c r="K671">
+        <v>16</v>
+      </c>
+      <c r="L671">
+        <v>18</v>
+      </c>
+      <c r="M671">
+        <v>20</v>
+      </c>
+      <c r="N671">
+        <v>21</v>
+      </c>
+      <c r="O671">
+        <v>22</v>
+      </c>
+      <c r="P671">
         <v>23</v>
       </c>
     </row>
     <row r="672" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A672" s="5">
+      <c r="A672">
         <v>3742</v>
       </c>
-      <c r="B672" s="6">
-        <v>1</v>
-      </c>
-      <c r="C672" s="6">
-        <v>4</v>
-      </c>
-      <c r="D672" s="6">
-        <v>5</v>
-      </c>
-      <c r="E672" s="6">
-        <v>6</v>
-      </c>
-      <c r="F672" s="6">
-        <v>9</v>
-      </c>
-      <c r="G672" s="6">
-        <v>10</v>
-      </c>
-      <c r="H672" s="6">
-        <v>12</v>
-      </c>
-      <c r="I672" s="6">
-        <v>13</v>
-      </c>
-      <c r="J672" s="6">
-        <v>14</v>
-      </c>
-      <c r="K672" s="6">
-        <v>15</v>
-      </c>
-      <c r="L672" s="6">
-        <v>16</v>
-      </c>
-      <c r="M672" s="6">
-        <v>19</v>
-      </c>
-      <c r="N672" s="6">
-        <v>20</v>
-      </c>
-      <c r="O672" s="6">
-        <v>21</v>
-      </c>
-      <c r="P672" s="6">
+      <c r="B672">
+        <v>1</v>
+      </c>
+      <c r="C672">
+        <v>4</v>
+      </c>
+      <c r="D672">
+        <v>5</v>
+      </c>
+      <c r="E672">
+        <v>6</v>
+      </c>
+      <c r="F672">
+        <v>9</v>
+      </c>
+      <c r="G672">
+        <v>10</v>
+      </c>
+      <c r="H672">
+        <v>12</v>
+      </c>
+      <c r="I672">
+        <v>13</v>
+      </c>
+      <c r="J672">
+        <v>14</v>
+      </c>
+      <c r="K672">
+        <v>15</v>
+      </c>
+      <c r="L672">
+        <v>16</v>
+      </c>
+      <c r="M672">
+        <v>19</v>
+      </c>
+      <c r="N672">
+        <v>20</v>
+      </c>
+      <c r="O672">
+        <v>21</v>
+      </c>
+      <c r="P672">
         <v>23</v>
       </c>
     </row>
     <row r="673" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A673" s="5">
+      <c r="A673">
         <v>3743</v>
       </c>
-      <c r="B673" s="6">
-        <v>2</v>
-      </c>
-      <c r="C673" s="6">
-        <v>3</v>
-      </c>
-      <c r="D673" s="6">
-        <v>4</v>
-      </c>
-      <c r="E673" s="6">
-        <v>5</v>
-      </c>
-      <c r="F673" s="6">
-        <v>9</v>
-      </c>
-      <c r="G673" s="6">
-        <v>10</v>
-      </c>
-      <c r="H673" s="6">
-        <v>11</v>
-      </c>
-      <c r="I673" s="6">
-        <v>13</v>
-      </c>
-      <c r="J673" s="6">
-        <v>15</v>
-      </c>
-      <c r="K673" s="6">
-        <v>18</v>
-      </c>
-      <c r="L673" s="6">
-        <v>19</v>
-      </c>
-      <c r="M673" s="6">
-        <v>20</v>
-      </c>
-      <c r="N673" s="6">
-        <v>21</v>
-      </c>
-      <c r="O673" s="6">
-        <v>23</v>
-      </c>
-      <c r="P673" s="6">
+      <c r="B673">
+        <v>2</v>
+      </c>
+      <c r="C673">
+        <v>3</v>
+      </c>
+      <c r="D673">
+        <v>4</v>
+      </c>
+      <c r="E673">
+        <v>5</v>
+      </c>
+      <c r="F673">
+        <v>9</v>
+      </c>
+      <c r="G673">
+        <v>10</v>
+      </c>
+      <c r="H673">
+        <v>11</v>
+      </c>
+      <c r="I673">
+        <v>13</v>
+      </c>
+      <c r="J673">
+        <v>15</v>
+      </c>
+      <c r="K673">
+        <v>18</v>
+      </c>
+      <c r="L673">
+        <v>19</v>
+      </c>
+      <c r="M673">
+        <v>20</v>
+      </c>
+      <c r="N673">
+        <v>21</v>
+      </c>
+      <c r="O673">
+        <v>23</v>
+      </c>
+      <c r="P673">
         <v>25</v>
       </c>
     </row>
     <row r="674" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A674" s="5">
+      <c r="A674">
         <v>3744</v>
       </c>
-      <c r="B674" s="6">
-        <v>1</v>
-      </c>
-      <c r="C674" s="6">
-        <v>2</v>
-      </c>
-      <c r="D674" s="6">
-        <v>3</v>
-      </c>
-      <c r="E674" s="6">
-        <v>5</v>
-      </c>
-      <c r="F674" s="6">
-        <v>7</v>
-      </c>
-      <c r="G674" s="6">
-        <v>10</v>
-      </c>
-      <c r="H674" s="6">
-        <v>14</v>
-      </c>
-      <c r="I674" s="6">
-        <v>16</v>
-      </c>
-      <c r="J674" s="6">
-        <v>17</v>
-      </c>
-      <c r="K674" s="6">
-        <v>18</v>
-      </c>
-      <c r="L674" s="6">
-        <v>20</v>
-      </c>
-      <c r="M674" s="6">
-        <v>21</v>
-      </c>
-      <c r="N674" s="6">
-        <v>22</v>
-      </c>
-      <c r="O674" s="6">
-        <v>23</v>
-      </c>
-      <c r="P674" s="6">
+      <c r="B674">
+        <v>1</v>
+      </c>
+      <c r="C674">
+        <v>2</v>
+      </c>
+      <c r="D674">
+        <v>3</v>
+      </c>
+      <c r="E674">
+        <v>5</v>
+      </c>
+      <c r="F674">
+        <v>7</v>
+      </c>
+      <c r="G674">
+        <v>10</v>
+      </c>
+      <c r="H674">
+        <v>14</v>
+      </c>
+      <c r="I674">
+        <v>16</v>
+      </c>
+      <c r="J674">
+        <v>17</v>
+      </c>
+      <c r="K674">
+        <v>18</v>
+      </c>
+      <c r="L674">
+        <v>20</v>
+      </c>
+      <c r="M674">
+        <v>21</v>
+      </c>
+      <c r="N674">
+        <v>22</v>
+      </c>
+      <c r="O674">
+        <v>23</v>
+      </c>
+      <c r="P674">
         <v>24</v>
       </c>
     </row>
     <row r="675" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A675" s="5">
+      <c r="A675">
         <v>3745</v>
       </c>
-      <c r="B675" s="6">
-        <v>1</v>
-      </c>
-      <c r="C675" s="6">
-        <v>2</v>
-      </c>
-      <c r="D675" s="6">
-        <v>4</v>
-      </c>
-      <c r="E675" s="6">
-        <v>5</v>
-      </c>
-      <c r="F675" s="6">
-        <v>6</v>
-      </c>
-      <c r="G675" s="6">
-        <v>7</v>
-      </c>
-      <c r="H675" s="6">
-        <v>8</v>
-      </c>
-      <c r="I675" s="6">
-        <v>9</v>
-      </c>
-      <c r="J675" s="6">
-        <v>10</v>
-      </c>
-      <c r="K675" s="6">
-        <v>12</v>
-      </c>
-      <c r="L675" s="6">
-        <v>13</v>
-      </c>
-      <c r="M675" s="6">
-        <v>19</v>
-      </c>
-      <c r="N675" s="6">
-        <v>21</v>
-      </c>
-      <c r="O675" s="6">
-        <v>22</v>
-      </c>
-      <c r="P675" s="6">
+      <c r="B675">
+        <v>1</v>
+      </c>
+      <c r="C675">
+        <v>2</v>
+      </c>
+      <c r="D675">
+        <v>4</v>
+      </c>
+      <c r="E675">
+        <v>5</v>
+      </c>
+      <c r="F675">
+        <v>6</v>
+      </c>
+      <c r="G675">
+        <v>7</v>
+      </c>
+      <c r="H675">
+        <v>8</v>
+      </c>
+      <c r="I675">
+        <v>9</v>
+      </c>
+      <c r="J675">
+        <v>10</v>
+      </c>
+      <c r="K675">
+        <v>12</v>
+      </c>
+      <c r="L675">
+        <v>13</v>
+      </c>
+      <c r="M675">
+        <v>19</v>
+      </c>
+      <c r="N675">
+        <v>21</v>
+      </c>
+      <c r="O675">
+        <v>22</v>
+      </c>
+      <c r="P675">
         <v>24</v>
       </c>
     </row>
     <row r="676" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A676" s="5">
+      <c r="A676">
         <v>3746</v>
       </c>
-      <c r="B676" s="6">
-        <v>1</v>
-      </c>
-      <c r="C676" s="6">
-        <v>3</v>
-      </c>
-      <c r="D676" s="6">
-        <v>4</v>
-      </c>
-      <c r="E676" s="6">
-        <v>6</v>
-      </c>
-      <c r="F676" s="6">
-        <v>7</v>
-      </c>
-      <c r="G676" s="6">
-        <v>8</v>
-      </c>
-      <c r="H676" s="6">
-        <v>9</v>
-      </c>
-      <c r="I676" s="6">
-        <v>10</v>
-      </c>
-      <c r="J676" s="6">
-        <v>14</v>
-      </c>
-      <c r="K676" s="6">
-        <v>15</v>
-      </c>
-      <c r="L676" s="6">
-        <v>17</v>
-      </c>
-      <c r="M676" s="6">
-        <v>18</v>
-      </c>
-      <c r="N676" s="6">
-        <v>21</v>
-      </c>
-      <c r="O676" s="6">
-        <v>22</v>
-      </c>
-      <c r="P676" s="6">
+      <c r="B676">
+        <v>1</v>
+      </c>
+      <c r="C676">
+        <v>3</v>
+      </c>
+      <c r="D676">
+        <v>4</v>
+      </c>
+      <c r="E676">
+        <v>6</v>
+      </c>
+      <c r="F676">
+        <v>7</v>
+      </c>
+      <c r="G676">
+        <v>8</v>
+      </c>
+      <c r="H676">
+        <v>9</v>
+      </c>
+      <c r="I676">
+        <v>10</v>
+      </c>
+      <c r="J676">
+        <v>14</v>
+      </c>
+      <c r="K676">
+        <v>15</v>
+      </c>
+      <c r="L676">
+        <v>17</v>
+      </c>
+      <c r="M676">
+        <v>18</v>
+      </c>
+      <c r="N676">
+        <v>21</v>
+      </c>
+      <c r="O676">
+        <v>22</v>
+      </c>
+      <c r="P676">
         <v>24</v>
       </c>
     </row>
     <row r="677" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A677" s="5">
+      <c r="A677">
         <v>3747</v>
       </c>
-      <c r="B677" s="6">
-        <v>1</v>
-      </c>
-      <c r="C677" s="6">
-        <v>2</v>
-      </c>
-      <c r="D677" s="6">
-        <v>4</v>
-      </c>
-      <c r="E677" s="6">
-        <v>5</v>
-      </c>
-      <c r="F677" s="6">
-        <v>6</v>
-      </c>
-      <c r="G677" s="6">
-        <v>8</v>
-      </c>
-      <c r="H677" s="6">
-        <v>9</v>
-      </c>
-      <c r="I677" s="6">
-        <v>11</v>
-      </c>
-      <c r="J677" s="6">
-        <v>12</v>
-      </c>
-      <c r="K677" s="6">
-        <v>13</v>
-      </c>
-      <c r="L677" s="6">
-        <v>18</v>
-      </c>
-      <c r="M677" s="6">
-        <v>19</v>
-      </c>
-      <c r="N677" s="6">
-        <v>21</v>
-      </c>
-      <c r="O677" s="6">
-        <v>24</v>
-      </c>
-      <c r="P677" s="6">
+      <c r="B677">
+        <v>1</v>
+      </c>
+      <c r="C677">
+        <v>2</v>
+      </c>
+      <c r="D677">
+        <v>4</v>
+      </c>
+      <c r="E677">
+        <v>5</v>
+      </c>
+      <c r="F677">
+        <v>6</v>
+      </c>
+      <c r="G677">
+        <v>8</v>
+      </c>
+      <c r="H677">
+        <v>9</v>
+      </c>
+      <c r="I677">
+        <v>11</v>
+      </c>
+      <c r="J677">
+        <v>12</v>
+      </c>
+      <c r="K677">
+        <v>13</v>
+      </c>
+      <c r="L677">
+        <v>18</v>
+      </c>
+      <c r="M677">
+        <v>19</v>
+      </c>
+      <c r="N677">
+        <v>21</v>
+      </c>
+      <c r="O677">
+        <v>24</v>
+      </c>
+      <c r="P677">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="678" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A678">
+        <v>3748</v>
+      </c>
+      <c r="B678">
+        <v>1</v>
+      </c>
+      <c r="C678">
+        <v>4</v>
+      </c>
+      <c r="D678">
+        <v>5</v>
+      </c>
+      <c r="E678">
+        <v>6</v>
+      </c>
+      <c r="F678">
+        <v>8</v>
+      </c>
+      <c r="G678">
+        <v>9</v>
+      </c>
+      <c r="H678">
+        <v>11</v>
+      </c>
+      <c r="I678">
+        <v>13</v>
+      </c>
+      <c r="J678">
+        <v>14</v>
+      </c>
+      <c r="K678">
+        <v>15</v>
+      </c>
+      <c r="L678">
+        <v>17</v>
+      </c>
+      <c r="M678">
+        <v>19</v>
+      </c>
+      <c r="N678">
+        <v>20</v>
+      </c>
+      <c r="O678">
+        <v>22</v>
+      </c>
+      <c r="P678">
         <v>25</v>
       </c>
     </row>
@@ -34343,6 +34391,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -34510,16 +34568,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -34530,6 +34578,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34549,17 +34608,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA2BAA2-1D81-4466-9D23-8476C14C2FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D3D44A-6BA7-42B4-AD5B-0267ACF79EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58365" yWindow="1125" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P678"/>
+  <dimension ref="A1:P679"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -34385,22 +34385,62 @@
         <v>25</v>
       </c>
     </row>
+    <row r="679" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A679">
+        <v>3749</v>
+      </c>
+      <c r="B679">
+        <v>1</v>
+      </c>
+      <c r="C679">
+        <v>2</v>
+      </c>
+      <c r="D679">
+        <v>3</v>
+      </c>
+      <c r="E679">
+        <v>7</v>
+      </c>
+      <c r="F679">
+        <v>8</v>
+      </c>
+      <c r="G679">
+        <v>9</v>
+      </c>
+      <c r="H679">
+        <v>11</v>
+      </c>
+      <c r="I679">
+        <v>12</v>
+      </c>
+      <c r="J679">
+        <v>14</v>
+      </c>
+      <c r="K679">
+        <v>17</v>
+      </c>
+      <c r="L679">
+        <v>19</v>
+      </c>
+      <c r="M679">
+        <v>21</v>
+      </c>
+      <c r="N679">
+        <v>23</v>
+      </c>
+      <c r="O679">
+        <v>24</v>
+      </c>
+      <c r="P679">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -34568,6 +34608,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -34578,17 +34628,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34608,6 +34647,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D3D44A-6BA7-42B4-AD5B-0267ACF79EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5518E14C-37E9-422C-BFBF-267AACB39E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58365" yWindow="1125" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58140" yWindow="780" windowWidth="13560" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P679"/>
+  <dimension ref="A1:P681"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -34435,12 +34435,122 @@
         <v>25</v>
       </c>
     </row>
+    <row r="680" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A680">
+        <v>3750</v>
+      </c>
+      <c r="B680">
+        <v>1</v>
+      </c>
+      <c r="C680">
+        <v>2</v>
+      </c>
+      <c r="D680">
+        <v>5</v>
+      </c>
+      <c r="E680">
+        <v>6</v>
+      </c>
+      <c r="F680">
+        <v>7</v>
+      </c>
+      <c r="G680">
+        <v>11</v>
+      </c>
+      <c r="H680">
+        <v>12</v>
+      </c>
+      <c r="I680">
+        <v>13</v>
+      </c>
+      <c r="J680">
+        <v>15</v>
+      </c>
+      <c r="K680">
+        <v>18</v>
+      </c>
+      <c r="L680">
+        <v>19</v>
+      </c>
+      <c r="M680">
+        <v>20</v>
+      </c>
+      <c r="N680">
+        <v>22</v>
+      </c>
+      <c r="O680">
+        <v>24</v>
+      </c>
+      <c r="P680">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="681" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A681">
+        <v>3751</v>
+      </c>
+      <c r="B681">
+        <v>1</v>
+      </c>
+      <c r="C681">
+        <v>2</v>
+      </c>
+      <c r="D681">
+        <v>4</v>
+      </c>
+      <c r="E681">
+        <v>7</v>
+      </c>
+      <c r="F681">
+        <v>8</v>
+      </c>
+      <c r="G681">
+        <v>9</v>
+      </c>
+      <c r="H681">
+        <v>11</v>
+      </c>
+      <c r="I681">
+        <v>12</v>
+      </c>
+      <c r="J681">
+        <v>16</v>
+      </c>
+      <c r="K681">
+        <v>17</v>
+      </c>
+      <c r="L681">
+        <v>18</v>
+      </c>
+      <c r="M681">
+        <v>19</v>
+      </c>
+      <c r="N681">
+        <v>21</v>
+      </c>
+      <c r="O681">
+        <v>23</v>
+      </c>
+      <c r="P681">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -34608,16 +34718,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -34628,6 +34728,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34647,17 +34758,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5518E14C-37E9-422C-BFBF-267AACB39E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647DC86E-6910-416F-AAC6-B85E97A544A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58140" yWindow="780" windowWidth="13560" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P681"/>
+  <dimension ref="A1:P683"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -34535,22 +34535,112 @@
         <v>24</v>
       </c>
     </row>
+    <row r="682" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A682">
+        <v>3752</v>
+      </c>
+      <c r="B682">
+        <v>2</v>
+      </c>
+      <c r="C682">
+        <v>3</v>
+      </c>
+      <c r="D682">
+        <v>6</v>
+      </c>
+      <c r="E682">
+        <v>7</v>
+      </c>
+      <c r="F682">
+        <v>9</v>
+      </c>
+      <c r="G682">
+        <v>10</v>
+      </c>
+      <c r="H682">
+        <v>11</v>
+      </c>
+      <c r="I682">
+        <v>12</v>
+      </c>
+      <c r="J682">
+        <v>13</v>
+      </c>
+      <c r="K682">
+        <v>14</v>
+      </c>
+      <c r="L682">
+        <v>15</v>
+      </c>
+      <c r="M682">
+        <v>16</v>
+      </c>
+      <c r="N682">
+        <v>17</v>
+      </c>
+      <c r="O682">
+        <v>21</v>
+      </c>
+      <c r="P682">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="683" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A683">
+        <v>3751</v>
+      </c>
+      <c r="B683">
+        <v>1</v>
+      </c>
+      <c r="C683">
+        <v>2</v>
+      </c>
+      <c r="D683">
+        <v>4</v>
+      </c>
+      <c r="E683">
+        <v>6</v>
+      </c>
+      <c r="F683">
+        <v>8</v>
+      </c>
+      <c r="G683">
+        <v>9</v>
+      </c>
+      <c r="H683">
+        <v>14</v>
+      </c>
+      <c r="I683">
+        <v>15</v>
+      </c>
+      <c r="J683">
+        <v>16</v>
+      </c>
+      <c r="K683">
+        <v>17</v>
+      </c>
+      <c r="L683">
+        <v>19</v>
+      </c>
+      <c r="M683">
+        <v>21</v>
+      </c>
+      <c r="N683">
+        <v>22</v>
+      </c>
+      <c r="O683">
+        <v>24</v>
+      </c>
+      <c r="P683">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -34718,6 +34808,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -34728,17 +34828,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34758,6 +34847,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647DC86E-6910-416F-AAC6-B85E97A544A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F6F33E-54FE-4BCC-8264-A02439218C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="0" yWindow="1132" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Concurso</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Bola15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P683"/>
+  <dimension ref="A1:P687"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -34587,7 +34590,7 @@
     </row>
     <row r="683" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A683">
-        <v>3751</v>
+        <v>3753</v>
       </c>
       <c r="B683">
         <v>1</v>
@@ -34633,6 +34636,116 @@
       </c>
       <c r="P683">
         <v>25</v>
+      </c>
+    </row>
+    <row r="684" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A684">
+        <v>3754</v>
+      </c>
+      <c r="B684">
+        <v>1</v>
+      </c>
+      <c r="C684">
+        <v>3</v>
+      </c>
+      <c r="D684">
+        <v>4</v>
+      </c>
+      <c r="E684">
+        <v>5</v>
+      </c>
+      <c r="F684">
+        <v>7</v>
+      </c>
+      <c r="G684">
+        <v>8</v>
+      </c>
+      <c r="H684">
+        <v>11</v>
+      </c>
+      <c r="I684">
+        <v>12</v>
+      </c>
+      <c r="J684">
+        <v>13</v>
+      </c>
+      <c r="K684">
+        <v>14</v>
+      </c>
+      <c r="L684">
+        <v>16</v>
+      </c>
+      <c r="M684">
+        <v>20</v>
+      </c>
+      <c r="N684">
+        <v>21</v>
+      </c>
+      <c r="O684">
+        <v>23</v>
+      </c>
+      <c r="P684">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="685" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A685">
+        <v>3755</v>
+      </c>
+      <c r="B685">
+        <v>3</v>
+      </c>
+      <c r="C685">
+        <v>4</v>
+      </c>
+      <c r="D685">
+        <v>5</v>
+      </c>
+      <c r="E685">
+        <v>7</v>
+      </c>
+      <c r="F685">
+        <v>8</v>
+      </c>
+      <c r="G685">
+        <v>9</v>
+      </c>
+      <c r="H685">
+        <v>11</v>
+      </c>
+      <c r="I685">
+        <v>12</v>
+      </c>
+      <c r="J685">
+        <v>16</v>
+      </c>
+      <c r="K685">
+        <v>18</v>
+      </c>
+      <c r="L685">
+        <v>20</v>
+      </c>
+      <c r="M685">
+        <v>22</v>
+      </c>
+      <c r="N685">
+        <v>23</v>
+      </c>
+      <c r="O685">
+        <v>24</v>
+      </c>
+      <c r="P685">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="686" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A686" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="687" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A687" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -34641,6 +34754,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -34808,16 +34931,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -34828,6 +34941,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34847,17 +34971,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F6F33E-54FE-4BCC-8264-A02439218C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7DE3C5-E921-425B-A8CD-9FF0B7888FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1132" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="1950" yWindow="1357" windowWidth="23610" windowHeight="9421" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Concurso</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>Bola15</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -479,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P687"/>
+  <dimension ref="A1:P693"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -34739,13 +34736,403 @@
       </c>
     </row>
     <row r="686" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A686" t="s">
-        <v>16</v>
+      <c r="A686">
+        <v>3756</v>
+      </c>
+      <c r="B686">
+        <v>2</v>
+      </c>
+      <c r="C686">
+        <v>3</v>
+      </c>
+      <c r="D686">
+        <v>5</v>
+      </c>
+      <c r="E686">
+        <v>6</v>
+      </c>
+      <c r="F686">
+        <v>9</v>
+      </c>
+      <c r="G686">
+        <v>10</v>
+      </c>
+      <c r="H686">
+        <v>11</v>
+      </c>
+      <c r="I686">
+        <v>13</v>
+      </c>
+      <c r="J686">
+        <v>14</v>
+      </c>
+      <c r="K686">
+        <v>15</v>
+      </c>
+      <c r="L686">
+        <v>16</v>
+      </c>
+      <c r="M686">
+        <v>19</v>
+      </c>
+      <c r="N686">
+        <v>20</v>
+      </c>
+      <c r="O686">
+        <v>21</v>
+      </c>
+      <c r="P686">
+        <v>22</v>
       </c>
     </row>
     <row r="687" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A687" t="s">
-        <v>16</v>
+      <c r="A687">
+        <v>3757</v>
+      </c>
+      <c r="B687">
+        <v>1</v>
+      </c>
+      <c r="C687">
+        <v>2</v>
+      </c>
+      <c r="D687">
+        <v>3</v>
+      </c>
+      <c r="E687">
+        <v>4</v>
+      </c>
+      <c r="F687">
+        <v>6</v>
+      </c>
+      <c r="G687">
+        <v>8</v>
+      </c>
+      <c r="H687">
+        <v>11</v>
+      </c>
+      <c r="I687">
+        <v>12</v>
+      </c>
+      <c r="J687">
+        <v>15</v>
+      </c>
+      <c r="K687">
+        <v>17</v>
+      </c>
+      <c r="L687">
+        <v>20</v>
+      </c>
+      <c r="M687">
+        <v>21</v>
+      </c>
+      <c r="N687">
+        <v>22</v>
+      </c>
+      <c r="O687">
+        <v>23</v>
+      </c>
+      <c r="P687">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="688" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A688">
+        <v>3758</v>
+      </c>
+      <c r="B688">
+        <v>1</v>
+      </c>
+      <c r="C688">
+        <v>3</v>
+      </c>
+      <c r="D688">
+        <v>4</v>
+      </c>
+      <c r="E688">
+        <v>5</v>
+      </c>
+      <c r="F688">
+        <v>8</v>
+      </c>
+      <c r="G688">
+        <v>9</v>
+      </c>
+      <c r="H688">
+        <v>11</v>
+      </c>
+      <c r="I688">
+        <v>12</v>
+      </c>
+      <c r="J688">
+        <v>13</v>
+      </c>
+      <c r="K688">
+        <v>14</v>
+      </c>
+      <c r="L688">
+        <v>17</v>
+      </c>
+      <c r="M688">
+        <v>18</v>
+      </c>
+      <c r="N688">
+        <v>20</v>
+      </c>
+      <c r="O688">
+        <v>24</v>
+      </c>
+      <c r="P688">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="689" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A689">
+        <v>3759</v>
+      </c>
+      <c r="B689">
+        <v>1</v>
+      </c>
+      <c r="C689">
+        <v>2</v>
+      </c>
+      <c r="D689">
+        <v>4</v>
+      </c>
+      <c r="E689">
+        <v>5</v>
+      </c>
+      <c r="F689">
+        <v>6</v>
+      </c>
+      <c r="G689">
+        <v>7</v>
+      </c>
+      <c r="H689">
+        <v>9</v>
+      </c>
+      <c r="I689">
+        <v>10</v>
+      </c>
+      <c r="J689">
+        <v>11</v>
+      </c>
+      <c r="K689">
+        <v>12</v>
+      </c>
+      <c r="L689">
+        <v>13</v>
+      </c>
+      <c r="M689">
+        <v>14</v>
+      </c>
+      <c r="N689">
+        <v>17</v>
+      </c>
+      <c r="O689">
+        <v>24</v>
+      </c>
+      <c r="P689">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="690" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A690">
+        <v>3760</v>
+      </c>
+      <c r="B690">
+        <v>2</v>
+      </c>
+      <c r="C690">
+        <v>4</v>
+      </c>
+      <c r="D690">
+        <v>5</v>
+      </c>
+      <c r="E690">
+        <v>8</v>
+      </c>
+      <c r="F690">
+        <v>9</v>
+      </c>
+      <c r="G690">
+        <v>10</v>
+      </c>
+      <c r="H690">
+        <v>11</v>
+      </c>
+      <c r="I690">
+        <v>13</v>
+      </c>
+      <c r="J690">
+        <v>14</v>
+      </c>
+      <c r="K690">
+        <v>16</v>
+      </c>
+      <c r="L690">
+        <v>19</v>
+      </c>
+      <c r="M690">
+        <v>21</v>
+      </c>
+      <c r="N690">
+        <v>22</v>
+      </c>
+      <c r="O690">
+        <v>24</v>
+      </c>
+      <c r="P690">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="691" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A691">
+        <v>3761</v>
+      </c>
+      <c r="B691">
+        <v>1</v>
+      </c>
+      <c r="C691">
+        <v>3</v>
+      </c>
+      <c r="D691">
+        <v>6</v>
+      </c>
+      <c r="E691">
+        <v>9</v>
+      </c>
+      <c r="F691">
+        <v>12</v>
+      </c>
+      <c r="G691">
+        <v>13</v>
+      </c>
+      <c r="H691">
+        <v>14</v>
+      </c>
+      <c r="I691">
+        <v>15</v>
+      </c>
+      <c r="J691">
+        <v>16</v>
+      </c>
+      <c r="K691">
+        <v>17</v>
+      </c>
+      <c r="L691">
+        <v>18</v>
+      </c>
+      <c r="M691">
+        <v>21</v>
+      </c>
+      <c r="N691">
+        <v>23</v>
+      </c>
+      <c r="O691">
+        <v>24</v>
+      </c>
+      <c r="P691">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="692" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A692">
+        <v>3762</v>
+      </c>
+      <c r="B692">
+        <v>1</v>
+      </c>
+      <c r="C692">
+        <v>2</v>
+      </c>
+      <c r="D692">
+        <v>3</v>
+      </c>
+      <c r="E692">
+        <v>4</v>
+      </c>
+      <c r="F692">
+        <v>5</v>
+      </c>
+      <c r="G692">
+        <v>6</v>
+      </c>
+      <c r="H692">
+        <v>9</v>
+      </c>
+      <c r="I692">
+        <v>10</v>
+      </c>
+      <c r="J692">
+        <v>13</v>
+      </c>
+      <c r="K692">
+        <v>16</v>
+      </c>
+      <c r="L692">
+        <v>18</v>
+      </c>
+      <c r="M692">
+        <v>21</v>
+      </c>
+      <c r="N692">
+        <v>22</v>
+      </c>
+      <c r="O692">
+        <v>23</v>
+      </c>
+      <c r="P692">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A693">
+        <v>3763</v>
+      </c>
+      <c r="B693">
+        <v>1</v>
+      </c>
+      <c r="C693">
+        <v>2</v>
+      </c>
+      <c r="D693">
+        <v>3</v>
+      </c>
+      <c r="E693">
+        <v>4</v>
+      </c>
+      <c r="F693">
+        <v>5</v>
+      </c>
+      <c r="G693">
+        <v>8</v>
+      </c>
+      <c r="H693">
+        <v>9</v>
+      </c>
+      <c r="I693">
+        <v>14</v>
+      </c>
+      <c r="J693">
+        <v>15</v>
+      </c>
+      <c r="K693">
+        <v>17</v>
+      </c>
+      <c r="L693">
+        <v>20</v>
+      </c>
+      <c r="M693">
+        <v>21</v>
+      </c>
+      <c r="N693">
+        <v>22</v>
+      </c>
+      <c r="O693">
+        <v>23</v>
+      </c>
+      <c r="P693">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -34754,16 +35141,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -34931,6 +35308,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -34941,17 +35328,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34971,6 +35347,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7DE3C5-E921-425B-A8CD-9FF0B7888FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EE7975-49DC-456C-9681-9030779CAFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1357" windowWidth="23610" windowHeight="9421" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="5423" yWindow="1530" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P693"/>
+  <dimension ref="A1:P694"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35135,12 +35135,72 @@
         <v>24</v>
       </c>
     </row>
+    <row r="694" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A694">
+        <v>3764</v>
+      </c>
+      <c r="B694">
+        <v>2</v>
+      </c>
+      <c r="C694">
+        <v>3</v>
+      </c>
+      <c r="D694">
+        <v>4</v>
+      </c>
+      <c r="E694">
+        <v>5</v>
+      </c>
+      <c r="F694">
+        <v>6</v>
+      </c>
+      <c r="G694">
+        <v>7</v>
+      </c>
+      <c r="H694">
+        <v>8</v>
+      </c>
+      <c r="I694">
+        <v>9</v>
+      </c>
+      <c r="J694">
+        <v>12</v>
+      </c>
+      <c r="K694">
+        <v>13</v>
+      </c>
+      <c r="L694">
+        <v>15</v>
+      </c>
+      <c r="M694">
+        <v>18</v>
+      </c>
+      <c r="N694">
+        <v>21</v>
+      </c>
+      <c r="O694">
+        <v>22</v>
+      </c>
+      <c r="P694">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35308,16 +35368,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -35328,6 +35378,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35347,17 +35408,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EE7975-49DC-456C-9681-9030779CAFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292EF899-CC2E-4B2B-8CEB-8CDF13A0608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5423" yWindow="1530" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="60600" yWindow="645" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,6 +156,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P694"/>
+  <dimension ref="A1:P696"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35185,22 +35187,112 @@
         <v>25</v>
       </c>
     </row>
+    <row r="695" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A695" s="5">
+        <v>3765</v>
+      </c>
+      <c r="B695" s="6">
+        <v>1</v>
+      </c>
+      <c r="C695" s="6">
+        <v>5</v>
+      </c>
+      <c r="D695" s="6">
+        <v>6</v>
+      </c>
+      <c r="E695" s="6">
+        <v>10</v>
+      </c>
+      <c r="F695" s="6">
+        <v>11</v>
+      </c>
+      <c r="G695" s="6">
+        <v>12</v>
+      </c>
+      <c r="H695" s="6">
+        <v>13</v>
+      </c>
+      <c r="I695" s="6">
+        <v>15</v>
+      </c>
+      <c r="J695" s="6">
+        <v>16</v>
+      </c>
+      <c r="K695" s="6">
+        <v>17</v>
+      </c>
+      <c r="L695" s="6">
+        <v>19</v>
+      </c>
+      <c r="M695" s="6">
+        <v>21</v>
+      </c>
+      <c r="N695" s="6">
+        <v>22</v>
+      </c>
+      <c r="O695" s="6">
+        <v>24</v>
+      </c>
+      <c r="P695" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="696" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A696" s="5">
+        <v>3766</v>
+      </c>
+      <c r="B696" s="6">
+        <v>1</v>
+      </c>
+      <c r="C696" s="6">
+        <v>2</v>
+      </c>
+      <c r="D696" s="6">
+        <v>3</v>
+      </c>
+      <c r="E696" s="6">
+        <v>5</v>
+      </c>
+      <c r="F696" s="6">
+        <v>8</v>
+      </c>
+      <c r="G696" s="6">
+        <v>9</v>
+      </c>
+      <c r="H696" s="6">
+        <v>11</v>
+      </c>
+      <c r="I696" s="6">
+        <v>13</v>
+      </c>
+      <c r="J696" s="6">
+        <v>14</v>
+      </c>
+      <c r="K696" s="6">
+        <v>16</v>
+      </c>
+      <c r="L696" s="6">
+        <v>17</v>
+      </c>
+      <c r="M696" s="6">
+        <v>19</v>
+      </c>
+      <c r="N696" s="6">
+        <v>21</v>
+      </c>
+      <c r="O696" s="6">
+        <v>23</v>
+      </c>
+      <c r="P696" s="6">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35368,6 +35460,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -35378,17 +35480,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35408,6 +35499,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>
